--- a/UK_Restock_Plan.xlsx
+++ b/UK_Restock_Plan.xlsx
@@ -75,7 +75,7 @@
     <t xml:space="preserve">Launch Assumptions (editable):</t>
   </si>
   <si>
-    <t xml:space="preserve">EDIT ME — set actual UK launch date</t>
+    <t xml:space="preserve">3 new UK retail partners launch in 6 weeks (from 2026-08-10) — edit if the date shifts</t>
   </si>
   <si>
     <t xml:space="preserve">Target Weeks of Cover at Launch</t>
@@ -1393,7 +1393,7 @@
       </c>
       <c r="B10" s="6" t="n">
         <f aca="false">'UK Restock Plan'!B4</f>
-        <v>46300</v>
+        <v>46286</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="B11" s="7" t="n">
         <f aca="false">'UK Restock Plan'!B7</f>
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="B13" s="9" t="n">
         <f aca="false">COUNTIF('UK Restock Plan'!V10:V18,"On Track")</f>
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="B14" s="9" t="n">
         <f aca="false">COUNTIF('UK Restock Plan'!V10:V18,"Expedite Required")</f>
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1563,7 +1563,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="13" t="n">
-        <v>46300</v>
+        <v>46286</v>
       </c>
       <c r="C4" s="14" t="s">
         <v>16</v>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B7" s="17" t="n">
         <f aca="false">($B$4-$B$6)/7</f>
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1745,15 +1745,15 @@
       </c>
       <c r="T10" s="22" t="str">
         <f aca="false">IF($N10=0,"No Order Needed",IF($R10&lt;=$B$7,"Sea",IF($S10&lt;=$B$7,"Air — Expedite","Air — Still At Risk")))</f>
-        <v>Sea</v>
+        <v>Air — Expedite</v>
       </c>
       <c r="U10" s="16" t="n">
         <f aca="false">IF($N10=0,"N/A",$B$4-IF($T10="Sea",$R10,$S10)*7)</f>
-        <v>46244</v>
+        <v>46258</v>
       </c>
       <c r="V10" s="22" t="str">
         <f aca="false">IF($N10=0,"No Restock Needed",IF($T10="Sea","On Track",IF($T10="Air — Expedite","Expedite Required","Critical — May Miss Launch")))</f>
-        <v>On Track</v>
+        <v>Expedite Required</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1835,15 +1835,15 @@
       </c>
       <c r="T11" s="22" t="str">
         <f aca="false">IF($N11=0,"No Order Needed",IF($R11&lt;=$B$7,"Sea",IF($S11&lt;=$B$7,"Air — Expedite","Air — Still At Risk")))</f>
-        <v>Sea</v>
+        <v>Air — Expedite</v>
       </c>
       <c r="U11" s="16" t="n">
         <f aca="false">IF($N11=0,"N/A",$B$4-IF($T11="Sea",$R11,$S11)*7)</f>
-        <v>46244</v>
+        <v>46258</v>
       </c>
       <c r="V11" s="22" t="str">
         <f aca="false">IF($N11=0,"No Restock Needed",IF($T11="Sea","On Track",IF($T11="Air — Expedite","Expedite Required","Critical — May Miss Launch")))</f>
-        <v>On Track</v>
+        <v>Expedite Required</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1925,15 +1925,15 @@
       </c>
       <c r="T12" s="22" t="str">
         <f aca="false">IF($N12=0,"No Order Needed",IF($R12&lt;=$B$7,"Sea",IF($S12&lt;=$B$7,"Air — Expedite","Air — Still At Risk")))</f>
-        <v>Sea</v>
+        <v>Air — Expedite</v>
       </c>
       <c r="U12" s="16" t="n">
         <f aca="false">IF($N12=0,"N/A",$B$4-IF($T12="Sea",$R12,$S12)*7)</f>
-        <v>46251</v>
+        <v>46261.5</v>
       </c>
       <c r="V12" s="22" t="str">
         <f aca="false">IF($N12=0,"No Restock Needed",IF($T12="Sea","On Track",IF($T12="Air — Expedite","Expedite Required","Critical — May Miss Launch")))</f>
-        <v>On Track</v>
+        <v>Expedite Required</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2015,15 +2015,15 @@
       </c>
       <c r="T13" s="22" t="str">
         <f aca="false">IF($N13=0,"No Order Needed",IF($R13&lt;=$B$7,"Sea",IF($S13&lt;=$B$7,"Air — Expedite","Air — Still At Risk")))</f>
-        <v>Sea</v>
+        <v>Air — Expedite</v>
       </c>
       <c r="U13" s="16" t="n">
         <f aca="false">IF($N13=0,"N/A",$B$4-IF($T13="Sea",$R13,$S13)*7)</f>
-        <v>46244</v>
+        <v>46258</v>
       </c>
       <c r="V13" s="22" t="str">
         <f aca="false">IF($N13=0,"No Restock Needed",IF($T13="Sea","On Track",IF($T13="Air — Expedite","Expedite Required","Critical — May Miss Launch")))</f>
-        <v>On Track</v>
+        <v>Expedite Required</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2105,15 +2105,15 @@
       </c>
       <c r="T14" s="22" t="str">
         <f aca="false">IF($N14=0,"No Order Needed",IF($R14&lt;=$B$7,"Sea",IF($S14&lt;=$B$7,"Air — Expedite","Air — Still At Risk")))</f>
-        <v>Sea</v>
+        <v>Air — Expedite</v>
       </c>
       <c r="U14" s="16" t="n">
         <f aca="false">IF($N14=0,"N/A",$B$4-IF($T14="Sea",$R14,$S14)*7)</f>
-        <v>46251</v>
+        <v>46266</v>
       </c>
       <c r="V14" s="22" t="str">
         <f aca="false">IF($N14=0,"No Restock Needed",IF($T14="Sea","On Track",IF($T14="Air — Expedite","Expedite Required","Critical — May Miss Launch")))</f>
-        <v>On Track</v>
+        <v>Expedite Required</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2195,15 +2195,15 @@
       </c>
       <c r="T15" s="22" t="str">
         <f aca="false">IF($N15=0,"No Order Needed",IF($R15&lt;=$B$7,"Sea",IF($S15&lt;=$B$7,"Air — Expedite","Air — Still At Risk")))</f>
-        <v>Sea</v>
+        <v>Air — Expedite</v>
       </c>
       <c r="U15" s="16" t="n">
         <f aca="false">IF($N15=0,"N/A",$B$4-IF($T15="Sea",$R15,$S15)*7)</f>
-        <v>46244</v>
+        <v>46258</v>
       </c>
       <c r="V15" s="22" t="str">
         <f aca="false">IF($N15=0,"No Restock Needed",IF($T15="Sea","On Track",IF($T15="Air — Expedite","Expedite Required","Critical — May Miss Launch")))</f>
-        <v>On Track</v>
+        <v>Expedite Required</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2285,15 +2285,15 @@
       </c>
       <c r="T16" s="22" t="str">
         <f aca="false">IF($N16=0,"No Order Needed",IF($R16&lt;=$B$7,"Sea",IF($S16&lt;=$B$7,"Air — Expedite","Air — Still At Risk")))</f>
-        <v>Sea</v>
+        <v>Air — Expedite</v>
       </c>
       <c r="U16" s="16" t="n">
         <f aca="false">IF($N16=0,"N/A",$B$4-IF($T16="Sea",$R16,$S16)*7)</f>
-        <v>46254.5</v>
+        <v>46265</v>
       </c>
       <c r="V16" s="22" t="str">
         <f aca="false">IF($N16=0,"No Restock Needed",IF($T16="Sea","On Track",IF($T16="Air — Expedite","Expedite Required","Critical — May Miss Launch")))</f>
-        <v>On Track</v>
+        <v>Expedite Required</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="U17" s="16" t="n">
         <f aca="false">IF($N17=0,"N/A",$B$4-IF($T17="Sea",$R17,$S17)*7)</f>
-        <v>46265</v>
+        <v>46251</v>
       </c>
       <c r="V17" s="22" t="str">
         <f aca="false">IF($N17=0,"No Restock Needed",IF($T17="Sea","On Track",IF($T17="Air — Expedite","Expedite Required","Critical — May Miss Launch")))</f>
@@ -2465,15 +2465,15 @@
       </c>
       <c r="T18" s="22" t="str">
         <f aca="false">IF($N18=0,"No Order Needed",IF($R18&lt;=$B$7,"Sea",IF($S18&lt;=$B$7,"Air — Expedite","Air — Still At Risk")))</f>
-        <v>Sea</v>
+        <v>Air — Expedite</v>
       </c>
       <c r="U18" s="16" t="n">
         <f aca="false">IF($N18=0,"N/A",$B$4-IF($T18="Sea",$R18,$S18)*7)</f>
-        <v>46244</v>
+        <v>46258</v>
       </c>
       <c r="V18" s="22" t="str">
         <f aca="false">IF($N18=0,"No Restock Needed",IF($T18="Sea","On Track",IF($T18="Air — Expedite","Expedite Required","Critical — May Miss Launch")))</f>
-        <v>On Track</v>
+        <v>Expedite Required</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/UK_Restock_Plan.xlsx
+++ b/UK_Restock_Plan.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="207">
   <si>
     <t xml:space="preserve">UK Restock Plan — Summary</t>
   </si>
@@ -45,6 +45,9 @@
     <t xml:space="preserve">Weeks Until Launch</t>
   </si>
   <si>
+    <t xml:space="preserve">Retail Partner Stocking Qty Entered (Units)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Total UK Restock Units Needed</t>
   </si>
   <si>
@@ -69,6 +72,9 @@
     <t xml:space="preserve">• See the UK Restock Plan tab to edit the Launch Date / Target Weeks of Cover assumptions — this Summary and every dependent formula recalculates from there.</t>
   </si>
   <si>
+    <t xml:space="preserve">• Get the initial stocking order quantities from the 3 new UK retail partners and enter them per SKU in UK Restock Plan column K as soon as they're known — until then, every recommended order quantity on this sheet reflects DTC demand only.</t>
+  </si>
+  <si>
     <t xml:space="preserve">UK Restock Plan</t>
   </si>
   <si>
@@ -81,7 +87,13 @@
     <t xml:space="preserve">Target Weeks of Cover at Launch</t>
   </si>
   <si>
-    <t xml:space="preserve">EDIT ME — desired buffer of stock at launch</t>
+    <t xml:space="preserve">EDIT ME — desired DTC buffer of stock at launch (retail partner stocking is separate, see column K below)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New UK Retail Partners Launching</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Informational — their per-SKU opening stocking orders go in column K (Retail Partner Launch Stocking Qty) once known</t>
   </si>
   <si>
     <t xml:space="preserve">Today's Date (reference)</t>
@@ -105,7 +117,8 @@
   </si>
   <si>
     <t xml:space="preserve">Weekly Sell-
-Through Rate</t>
+Through Rate
+(DTC only)</t>
   </si>
   <si>
     <t xml:space="preserve">Open PO Qty
@@ -124,6 +137,11 @@
 On-Hand at Launch</t>
   </si>
   <si>
+    <t xml:space="preserve">Retail Partner
+Launch Stocking
+Qty (Units)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Target Qty
 at Launch</t>
   </si>
@@ -178,7 +196,10 @@
     <t xml:space="preserve">• SKU, Product, Factory, and current UK inventory/coverage figures are linked live from Inventory &amp; Coverage — this sheet has no re-entered source data.</t>
   </si>
   <si>
-    <t xml:space="preserve">• Projected UK On-Hand at Launch assumes steady depletion at the current Weekly Sell-Through Rate between today and the Launch Date, plus any PO quantity already open to UK (column G) landing before launch. It does not assume the newly recommended order below arrives in time — that is what the lead-time/readiness columns to the right test.</t>
+    <t xml:space="preserve">• IMPORTANT GAP: Weekly Sell-Through Rate (column F) is the DTC-only rate from the source data. It does not include demand from the 3 new UK retail partners. Column K (Retail Partner Launch Stocking Qty) is where their opening stocking orders should be entered per SKU once known — it currently defaults to 0, so Target Qty at Launch and every recommendation to its right currently reflect DTC demand ONLY and likely understate what's actually needed for launch.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Projected UK On-Hand at Launch assumes steady depletion at the current (DTC-only) Weekly Sell-Through Rate between today and the Launch Date, plus any PO quantity already open to UK (column G) landing before launch. It does not assume the newly recommended order below arrives in time — that is what the lead-time/readiness columns to the right test.</t>
   </si>
   <si>
     <t xml:space="preserve">• Recommended Order Qty rounds the pre-MOQ need up to the factory's MOQ (a partial-MOQ need still requires ordering a full MOQ batch).</t>
@@ -190,7 +211,7 @@
     <t xml:space="preserve">• Order-By Date = Launch Date minus the recommended method's total lead time. If this date is already in the past, that order is overdue and should be placed immediately.</t>
   </si>
   <si>
-    <t xml:space="preserve">• Change the Launch Date or Target Weeks of Cover in B4/B5 and every recommendation on this sheet recalculates.</t>
+    <t xml:space="preserve">• Change the Launch Date, Target Weeks of Cover, or any Retail Partner Launch Stocking Qty and every recommendation on this sheet recalculates.</t>
   </si>
   <si>
     <t xml:space="preserve">PO Follow-Ups</t>
@@ -416,6 +437,10 @@
   <si>
     <t xml:space="preserve">Total
 Qty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weekly Sell-
+Through Rate</t>
   </si>
   <si>
     <t xml:space="preserve">Total Weeks
@@ -671,13 +696,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="#,##0"/>
     <numFmt numFmtId="168" formatCode="General"/>
-    <numFmt numFmtId="169" formatCode="0.00"/>
+    <numFmt numFmtId="169" formatCode="0"/>
+    <numFmt numFmtId="170" formatCode="0.00"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -837,7 +863,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="38">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -902,6 +928,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="169" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -930,7 +960,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -958,7 +992,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -970,7 +1004,7 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -978,7 +1012,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -997,12 +1031,12 @@
         <name val="Arial"/>
         <charset val="1"/>
         <family val="0"/>
-        <color rgb="FF9C0006"/>
+        <color rgb="FF9C6500"/>
         <sz val="10"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1011,12 +1045,12 @@
         <name val="Arial"/>
         <charset val="1"/>
         <family val="0"/>
-        <color rgb="FF9C6500"/>
+        <color rgb="FF9C0006"/>
         <sz val="10"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1307,7 +1341,7 @@
     <tabColor rgb="FF1F4E78"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
@@ -1378,115 +1412,151 @@
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
     </row>
-    <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
+    <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="str">
+        <f aca="false">"Retail Partner Demand: "&amp;IF('UK Restock Plan'!K20=0,"No opening stocking order quantities from the 3 new UK retail partners have been entered yet (UK Restock Plan column K) — restock quantities below currently reflect DTC demand only and are likely understated.","Retail partner stocking quantities are entered — restock quantities include "&amp;'UK Restock Plan'!K20&amp;" units of retail launch stock.")</f>
+        <v>Retail Partner Demand: No opening stocking order quantities from the 3 new UK retail partners have been entered yet (UK Restock Plan column K) — restock quantities below currently reflect DTC demand only and are likely understated.</v>
+      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="6" t="n">
+      <c r="B11" s="6" t="n">
         <f aca="false">'UK Restock Plan'!B4</f>
         <v>46286</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B11" s="7" t="n">
-        <f aca="false">'UK Restock Plan'!B7</f>
-        <v>6</v>
-      </c>
-    </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12" s="8" t="n">
-        <f aca="false">'UK Restock Plan'!N19</f>
-        <v>4600</v>
+        <v>5</v>
+      </c>
+      <c r="B12" s="7" t="n">
+        <f aca="false">'UK Restock Plan'!B8</f>
+        <v>5.85714285714286</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13" s="9" t="n">
-        <f aca="false">COUNTIF('UK Restock Plan'!V10:V18,"On Track")</f>
+        <v>6</v>
+      </c>
+      <c r="B13" s="8" t="n">
+        <f aca="false">'UK Restock Plan'!K20</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B14" s="9" t="n">
-        <f aca="false">COUNTIF('UK Restock Plan'!V10:V18,"Expedite Required")</f>
-        <v>9</v>
+        <v>7</v>
+      </c>
+      <c r="B14" s="8" t="n">
+        <f aca="false">'UK Restock Plan'!O20</f>
+        <v>4600</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B15" s="9" t="n">
-        <f aca="false">COUNTIF('UK Restock Plan'!V10:V18,"Critical — May Miss Launch")</f>
+        <f aca="false">COUNTIF('UK Restock Plan'!W11:W19,"On Track")</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="9" t="n">
+        <f aca="false">COUNTIF('UK Restock Plan'!W11:W19,"Expedite Required")</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B16" s="9" t="n">
+      <c r="B17" s="9" t="n">
+        <f aca="false">COUNTIF('UK Restock Plan'!W11:W19,"Critical — May Miss Launch")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18" s="9" t="n">
         <f aca="false">COUNTIF('PO Follow-Ups'!J6:J11,"Yes")</f>
         <v>3</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="22.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="11" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="11" t="s">
+    </row>
+    <row r="21" customFormat="false" ht="22.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+    </row>
+    <row r="23" customFormat="false" ht="22.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="11">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="A23:E23"/>
   </mergeCells>
-  <conditionalFormatting sqref="B15">
-    <cfRule type="cellIs" priority="2" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+  <conditionalFormatting sqref="B13">
+    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B17">
+    <cfRule type="cellIs" priority="3" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1506,7 +1576,7 @@
     <tabColor rgb="FFC00000"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:V27"/>
+  <dimension ref="A1:W29"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
@@ -1516,20 +1586,21 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="5" style="0" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="15" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="18" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="16" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="19" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="20"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1552,10 +1623,11 @@
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
+      <c r="W1" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1566,979 +1638,998 @@
         <v>46286</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B5" s="15" t="n">
         <v>10</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B6" s="16" t="n">
-        <f aca="true">TODAY()</f>
-        <v>46244</v>
+        <v>3</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="17" t="n">
+        <f aca="true">TODAY()</f>
+        <v>46245</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="17" t="n">
-        <f aca="false">($B$4-$B$6)/7</f>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E9" s="18" t="s">
+      <c r="B8" s="18" t="n">
+        <f aca="false">($B$4-$B$7)/7</f>
+        <v>5.85714285714286</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="F9" s="18" t="s">
+      <c r="B10" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="G9" s="18" t="s">
+      <c r="C10" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="H9" s="18" t="s">
+      <c r="D10" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="I9" s="18" t="s">
+      <c r="E10" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="J9" s="18" t="s">
+      <c r="F10" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="K9" s="18" t="s">
+      <c r="G10" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="L9" s="18" t="s">
+      <c r="H10" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="M9" s="18" t="s">
+      <c r="I10" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="N9" s="18" t="s">
+      <c r="J10" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="O9" s="18" t="s">
+      <c r="K10" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="P9" s="18" t="s">
+      <c r="L10" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="Q9" s="18" t="s">
+      <c r="M10" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="R9" s="18" t="s">
+      <c r="N10" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="S9" s="18" t="s">
+      <c r="O10" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="T9" s="18" t="s">
+      <c r="P10" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="U9" s="18" t="s">
+      <c r="Q10" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="V9" s="18" t="s">
+      <c r="R10" s="19" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="str">
+      <c r="S10" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="T10" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="U10" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="V10" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="W10" s="19" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="20" t="str">
         <f aca="false">'Inventory &amp; Coverage'!A8</f>
         <v>HN-RB-300</v>
       </c>
-      <c r="B10" s="19" t="str">
+      <c r="B11" s="20" t="str">
         <f aca="false">'Inventory &amp; Coverage'!B8</f>
         <v>Recovery Balm 300ml</v>
       </c>
-      <c r="C10" s="19" t="str">
+      <c r="C11" s="20" t="str">
         <f aca="false">'Inventory &amp; Coverage'!D8</f>
         <v>Factory A</v>
       </c>
-      <c r="D10" s="19" t="str">
-        <f aca="false">IFERROR(INDEX('Reference Data'!$B$22:$B$27,MATCH($C10,'Reference Data'!$A$22:$A$27,0)),"N/A")</f>
+      <c r="D11" s="20" t="str">
+        <f aca="false">IFERROR(INDEX('Reference Data'!$B$22:$B$27,MATCH($C11,'Reference Data'!$A$22:$A$27,0)),"N/A")</f>
         <v>Shenzhen</v>
       </c>
-      <c r="E10" s="20" t="n">
+      <c r="E11" s="21" t="n">
         <f aca="false">'Inventory &amp; Coverage'!F8</f>
         <v>35</v>
       </c>
-      <c r="F10" s="20" t="n">
+      <c r="F11" s="21" t="n">
         <f aca="false">'Inventory &amp; Coverage'!I8</f>
         <v>75</v>
       </c>
-      <c r="G10" s="20" t="n">
+      <c r="G11" s="21" t="n">
         <f aca="false">'Inventory &amp; Coverage'!O8</f>
         <v>0</v>
       </c>
-      <c r="H10" s="21" t="n">
+      <c r="H11" s="22" t="n">
         <f aca="false">'Inventory &amp; Coverage'!L8</f>
         <v>0.466666666666667</v>
       </c>
-      <c r="I10" s="22" t="str">
+      <c r="I11" s="23" t="str">
         <f aca="false">'Inventory &amp; Coverage'!M8</f>
         <v>High Risk</v>
       </c>
-      <c r="J10" s="20" t="n">
-        <f aca="false">MAX($E10-$F10*$B$7,0)+$G10</f>
+      <c r="J11" s="21" t="n">
+        <f aca="false">MAX($E11-$F11*$B$8,0)+$G11</f>
         <v>0</v>
       </c>
-      <c r="K10" s="20" t="n">
-        <f aca="false">$F10*$B$5</f>
+      <c r="K11" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="21" t="n">
+        <f aca="false">$F11*$B$5+$K11</f>
         <v>750</v>
       </c>
-      <c r="L10" s="20" t="n">
-        <f aca="false">MAX($K10-$J10,0)</f>
+      <c r="M11" s="21" t="n">
+        <f aca="false">MAX($L11-$J11,0)</f>
         <v>750</v>
       </c>
-      <c r="M10" s="20" t="n">
-        <f aca="false">IFERROR(INDEX('Reference Data'!$F$22:$F$27,MATCH($C10,'Reference Data'!$A$22:$A$27,0)),"N/A")</f>
+      <c r="N11" s="21" t="n">
+        <f aca="false">IFERROR(INDEX('Reference Data'!$F$22:$F$27,MATCH($C11,'Reference Data'!$A$22:$A$27,0)),"N/A")</f>
         <v>500</v>
       </c>
-      <c r="N10" s="20" t="n">
-        <f aca="false">IF($L10&lt;=0,0,MAX($L10,$M10))</f>
+      <c r="O11" s="21" t="n">
+        <f aca="false">IF($M11&lt;=0,0,MAX($M11,$N11))</f>
         <v>750</v>
       </c>
-      <c r="O10" s="21" t="n">
-        <f aca="false">IFERROR(INDEX('Reference Data'!$G$22:$G$27,MATCH($C10,'Reference Data'!$A$22:$A$27,0)),"N/A")</f>
+      <c r="P11" s="22" t="n">
+        <f aca="false">IFERROR(INDEX('Reference Data'!$G$22:$G$27,MATCH($C11,'Reference Data'!$A$22:$A$27,0)),"N/A")</f>
         <v>3</v>
       </c>
-      <c r="P10" s="23" t="n">
-        <f aca="false">IFERROR(INDEX('Reference Data'!$C$31:$C$45,MATCH($D10&amp;"|UK",'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
+      <c r="Q11" s="25" t="n">
+        <f aca="false">IFERROR(INDEX('Reference Data'!$C$31:$C$45,MATCH($D11&amp;"|UK",'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
         <v>5</v>
       </c>
-      <c r="Q10" s="23" t="n">
-        <f aca="false">IFERROR(INDEX('Reference Data'!$E$31:$E$45,MATCH($D10&amp;"|UK",'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
+      <c r="R11" s="25" t="n">
+        <f aca="false">IFERROR(INDEX('Reference Data'!$E$31:$E$45,MATCH($D11&amp;"|UK",'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
         <v>1</v>
       </c>
-      <c r="R10" s="23" t="n">
-        <f aca="false">$O10+$P10</f>
+      <c r="S11" s="25" t="n">
+        <f aca="false">$P11+$Q11</f>
         <v>8</v>
       </c>
-      <c r="S10" s="23" t="n">
-        <f aca="false">$O10+$Q10</f>
+      <c r="T11" s="25" t="n">
+        <f aca="false">$P11+$R11</f>
         <v>4</v>
       </c>
-      <c r="T10" s="22" t="str">
-        <f aca="false">IF($N10=0,"No Order Needed",IF($R10&lt;=$B$7,"Sea",IF($S10&lt;=$B$7,"Air — Expedite","Air — Still At Risk")))</f>
+      <c r="U11" s="23" t="str">
+        <f aca="false">IF($O11=0,"No Order Needed",IF($S11&lt;=$B$8,"Sea",IF($T11&lt;=$B$8,"Air — Expedite","Air — Still At Risk")))</f>
         <v>Air — Expedite</v>
       </c>
-      <c r="U10" s="16" t="n">
-        <f aca="false">IF($N10=0,"N/A",$B$4-IF($T10="Sea",$R10,$S10)*7)</f>
+      <c r="V11" s="17" t="n">
+        <f aca="false">IF($O11=0,"N/A",$B$4-IF($U11="Sea",$S11,$T11)*7)</f>
         <v>46258</v>
       </c>
-      <c r="V10" s="22" t="str">
-        <f aca="false">IF($N10=0,"No Restock Needed",IF($T10="Sea","On Track",IF($T10="Air — Expedite","Expedite Required","Critical — May Miss Launch")))</f>
+      <c r="W11" s="23" t="str">
+        <f aca="false">IF($O11=0,"No Restock Needed",IF($U11="Sea","On Track",IF($U11="Air — Expedite","Expedite Required","Critical — May Miss Launch")))</f>
         <v>Expedite Required</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="str">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="20" t="str">
         <f aca="false">'Inventory &amp; Coverage'!A9</f>
         <v>HN-FS-050</v>
       </c>
-      <c r="B11" s="19" t="str">
+      <c r="B12" s="20" t="str">
         <f aca="false">'Inventory &amp; Coverage'!B9</f>
         <v>Face Serum 50ml</v>
       </c>
-      <c r="C11" s="19" t="str">
+      <c r="C12" s="20" t="str">
         <f aca="false">'Inventory &amp; Coverage'!D9</f>
         <v>Factory A</v>
       </c>
-      <c r="D11" s="19" t="str">
-        <f aca="false">IFERROR(INDEX('Reference Data'!$B$22:$B$27,MATCH($C11,'Reference Data'!$A$22:$A$27,0)),"N/A")</f>
+      <c r="D12" s="20" t="str">
+        <f aca="false">IFERROR(INDEX('Reference Data'!$B$22:$B$27,MATCH($C12,'Reference Data'!$A$22:$A$27,0)),"N/A")</f>
         <v>Shenzhen</v>
       </c>
-      <c r="E11" s="20" t="n">
+      <c r="E12" s="21" t="n">
         <f aca="false">'Inventory &amp; Coverage'!F9</f>
         <v>20</v>
       </c>
-      <c r="F11" s="20" t="n">
+      <c r="F12" s="21" t="n">
         <f aca="false">'Inventory &amp; Coverage'!I9</f>
         <v>45</v>
       </c>
-      <c r="G11" s="20" t="n">
+      <c r="G12" s="21" t="n">
         <f aca="false">'Inventory &amp; Coverage'!O9</f>
         <v>0</v>
       </c>
-      <c r="H11" s="21" t="n">
+      <c r="H12" s="22" t="n">
         <f aca="false">'Inventory &amp; Coverage'!L9</f>
         <v>0.444444444444444</v>
       </c>
-      <c r="I11" s="22" t="str">
+      <c r="I12" s="23" t="str">
         <f aca="false">'Inventory &amp; Coverage'!M9</f>
         <v>High Risk</v>
       </c>
-      <c r="J11" s="20" t="n">
-        <f aca="false">MAX($E11-$F11*$B$7,0)+$G11</f>
+      <c r="J12" s="21" t="n">
+        <f aca="false">MAX($E12-$F12*$B$8,0)+$G12</f>
         <v>0</v>
       </c>
-      <c r="K11" s="20" t="n">
-        <f aca="false">$F11*$B$5</f>
+      <c r="K12" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="21" t="n">
+        <f aca="false">$F12*$B$5+$K12</f>
         <v>450</v>
       </c>
-      <c r="L11" s="20" t="n">
-        <f aca="false">MAX($K11-$J11,0)</f>
+      <c r="M12" s="21" t="n">
+        <f aca="false">MAX($L12-$J12,0)</f>
         <v>450</v>
       </c>
-      <c r="M11" s="20" t="n">
-        <f aca="false">IFERROR(INDEX('Reference Data'!$F$22:$F$27,MATCH($C11,'Reference Data'!$A$22:$A$27,0)),"N/A")</f>
+      <c r="N12" s="21" t="n">
+        <f aca="false">IFERROR(INDEX('Reference Data'!$F$22:$F$27,MATCH($C12,'Reference Data'!$A$22:$A$27,0)),"N/A")</f>
         <v>500</v>
       </c>
-      <c r="N11" s="20" t="n">
-        <f aca="false">IF($L11&lt;=0,0,MAX($L11,$M11))</f>
+      <c r="O12" s="21" t="n">
+        <f aca="false">IF($M12&lt;=0,0,MAX($M12,$N12))</f>
         <v>500</v>
       </c>
-      <c r="O11" s="21" t="n">
-        <f aca="false">IFERROR(INDEX('Reference Data'!$G$22:$G$27,MATCH($C11,'Reference Data'!$A$22:$A$27,0)),"N/A")</f>
+      <c r="P12" s="22" t="n">
+        <f aca="false">IFERROR(INDEX('Reference Data'!$G$22:$G$27,MATCH($C12,'Reference Data'!$A$22:$A$27,0)),"N/A")</f>
         <v>3</v>
       </c>
-      <c r="P11" s="23" t="n">
-        <f aca="false">IFERROR(INDEX('Reference Data'!$C$31:$C$45,MATCH($D11&amp;"|UK",'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
+      <c r="Q12" s="25" t="n">
+        <f aca="false">IFERROR(INDEX('Reference Data'!$C$31:$C$45,MATCH($D12&amp;"|UK",'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
         <v>5</v>
       </c>
-      <c r="Q11" s="23" t="n">
-        <f aca="false">IFERROR(INDEX('Reference Data'!$E$31:$E$45,MATCH($D11&amp;"|UK",'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
+      <c r="R12" s="25" t="n">
+        <f aca="false">IFERROR(INDEX('Reference Data'!$E$31:$E$45,MATCH($D12&amp;"|UK",'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
         <v>1</v>
       </c>
-      <c r="R11" s="23" t="n">
-        <f aca="false">$O11+$P11</f>
+      <c r="S12" s="25" t="n">
+        <f aca="false">$P12+$Q12</f>
         <v>8</v>
       </c>
-      <c r="S11" s="23" t="n">
-        <f aca="false">$O11+$Q11</f>
+      <c r="T12" s="25" t="n">
+        <f aca="false">$P12+$R12</f>
         <v>4</v>
       </c>
-      <c r="T11" s="22" t="str">
-        <f aca="false">IF($N11=0,"No Order Needed",IF($R11&lt;=$B$7,"Sea",IF($S11&lt;=$B$7,"Air — Expedite","Air — Still At Risk")))</f>
+      <c r="U12" s="23" t="str">
+        <f aca="false">IF($O12=0,"No Order Needed",IF($S12&lt;=$B$8,"Sea",IF($T12&lt;=$B$8,"Air — Expedite","Air — Still At Risk")))</f>
         <v>Air — Expedite</v>
       </c>
-      <c r="U11" s="16" t="n">
-        <f aca="false">IF($N11=0,"N/A",$B$4-IF($T11="Sea",$R11,$S11)*7)</f>
+      <c r="V12" s="17" t="n">
+        <f aca="false">IF($O12=0,"N/A",$B$4-IF($U12="Sea",$S12,$T12)*7)</f>
         <v>46258</v>
       </c>
-      <c r="V11" s="22" t="str">
-        <f aca="false">IF($N11=0,"No Restock Needed",IF($T11="Sea","On Track",IF($T11="Air — Expedite","Expedite Required","Critical — May Miss Launch")))</f>
+      <c r="W12" s="23" t="str">
+        <f aca="false">IF($O12=0,"No Restock Needed",IF($U12="Sea","On Track",IF($U12="Air — Expedite","Expedite Required","Critical — May Miss Launch")))</f>
         <v>Expedite Required</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="str">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="20" t="str">
         <f aca="false">'Inventory &amp; Coverage'!A10</f>
         <v>HN-BW-200</v>
       </c>
-      <c r="B12" s="19" t="str">
+      <c r="B13" s="20" t="str">
         <f aca="false">'Inventory &amp; Coverage'!B10</f>
         <v>Body Wash 200ml</v>
       </c>
-      <c r="C12" s="19" t="str">
+      <c r="C13" s="20" t="str">
         <f aca="false">'Inventory &amp; Coverage'!D10</f>
         <v>Factory B</v>
       </c>
-      <c r="D12" s="19" t="str">
-        <f aca="false">IFERROR(INDEX('Reference Data'!$B$22:$B$27,MATCH($C12,'Reference Data'!$A$22:$A$27,0)),"N/A")</f>
+      <c r="D13" s="20" t="str">
+        <f aca="false">IFERROR(INDEX('Reference Data'!$B$22:$B$27,MATCH($C13,'Reference Data'!$A$22:$A$27,0)),"N/A")</f>
         <v>Chiang Mai</v>
       </c>
-      <c r="E12" s="20" t="n">
+      <c r="E13" s="21" t="n">
         <f aca="false">'Inventory &amp; Coverage'!F10</f>
         <v>50</v>
       </c>
-      <c r="F12" s="20" t="n">
+      <c r="F13" s="21" t="n">
         <f aca="false">'Inventory &amp; Coverage'!I10</f>
         <v>55</v>
       </c>
-      <c r="G12" s="20" t="n">
+      <c r="G13" s="21" t="n">
         <f aca="false">'Inventory &amp; Coverage'!O10</f>
         <v>0</v>
       </c>
-      <c r="H12" s="21" t="n">
+      <c r="H13" s="22" t="n">
         <f aca="false">'Inventory &amp; Coverage'!L10</f>
         <v>0.909090909090909</v>
       </c>
-      <c r="I12" s="22" t="str">
+      <c r="I13" s="23" t="str">
         <f aca="false">'Inventory &amp; Coverage'!M10</f>
         <v>High Risk</v>
       </c>
-      <c r="J12" s="20" t="n">
-        <f aca="false">MAX($E12-$F12*$B$7,0)+$G12</f>
+      <c r="J13" s="21" t="n">
+        <f aca="false">MAX($E13-$F13*$B$8,0)+$G13</f>
         <v>0</v>
       </c>
-      <c r="K12" s="20" t="n">
-        <f aca="false">$F12*$B$5</f>
+      <c r="K13" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="21" t="n">
+        <f aca="false">$F13*$B$5+$K13</f>
         <v>550</v>
       </c>
-      <c r="L12" s="20" t="n">
-        <f aca="false">MAX($K12-$J12,0)</f>
+      <c r="M13" s="21" t="n">
+        <f aca="false">MAX($L13-$J13,0)</f>
         <v>550</v>
       </c>
-      <c r="M12" s="20" t="n">
-        <f aca="false">IFERROR(INDEX('Reference Data'!$F$22:$F$27,MATCH($C12,'Reference Data'!$A$22:$A$27,0)),"N/A")</f>
+      <c r="N13" s="21" t="n">
+        <f aca="false">IFERROR(INDEX('Reference Data'!$F$22:$F$27,MATCH($C13,'Reference Data'!$A$22:$A$27,0)),"N/A")</f>
         <v>400</v>
       </c>
-      <c r="N12" s="20" t="n">
-        <f aca="false">IF($L12&lt;=0,0,MAX($L12,$M12))</f>
+      <c r="O13" s="21" t="n">
+        <f aca="false">IF($M13&lt;=0,0,MAX($M13,$N13))</f>
         <v>550</v>
       </c>
-      <c r="O12" s="21" t="n">
-        <f aca="false">IFERROR(INDEX('Reference Data'!$G$22:$G$27,MATCH($C12,'Reference Data'!$A$22:$A$27,0)),"N/A")</f>
+      <c r="P13" s="22" t="n">
+        <f aca="false">IFERROR(INDEX('Reference Data'!$G$22:$G$27,MATCH($C13,'Reference Data'!$A$22:$A$27,0)),"N/A")</f>
         <v>2.5</v>
       </c>
-      <c r="P12" s="23" t="n">
-        <f aca="false">IFERROR(INDEX('Reference Data'!$C$31:$C$45,MATCH($D12&amp;"|UK",'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
+      <c r="Q13" s="25" t="n">
+        <f aca="false">IFERROR(INDEX('Reference Data'!$C$31:$C$45,MATCH($D13&amp;"|UK",'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
         <v>4.5</v>
       </c>
-      <c r="Q12" s="23" t="n">
-        <f aca="false">IFERROR(INDEX('Reference Data'!$E$31:$E$45,MATCH($D12&amp;"|UK",'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
+      <c r="R13" s="25" t="n">
+        <f aca="false">IFERROR(INDEX('Reference Data'!$E$31:$E$45,MATCH($D13&amp;"|UK",'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
         <v>1</v>
       </c>
-      <c r="R12" s="23" t="n">
-        <f aca="false">$O12+$P12</f>
+      <c r="S13" s="25" t="n">
+        <f aca="false">$P13+$Q13</f>
         <v>7</v>
       </c>
-      <c r="S12" s="23" t="n">
-        <f aca="false">$O12+$Q12</f>
+      <c r="T13" s="25" t="n">
+        <f aca="false">$P13+$R13</f>
         <v>3.5</v>
       </c>
-      <c r="T12" s="22" t="str">
-        <f aca="false">IF($N12=0,"No Order Needed",IF($R12&lt;=$B$7,"Sea",IF($S12&lt;=$B$7,"Air — Expedite","Air — Still At Risk")))</f>
+      <c r="U13" s="23" t="str">
+        <f aca="false">IF($O13=0,"No Order Needed",IF($S13&lt;=$B$8,"Sea",IF($T13&lt;=$B$8,"Air — Expedite","Air — Still At Risk")))</f>
         <v>Air — Expedite</v>
       </c>
-      <c r="U12" s="16" t="n">
-        <f aca="false">IF($N12=0,"N/A",$B$4-IF($T12="Sea",$R12,$S12)*7)</f>
+      <c r="V13" s="17" t="n">
+        <f aca="false">IF($O13=0,"N/A",$B$4-IF($U13="Sea",$S13,$T13)*7)</f>
         <v>46261.5</v>
       </c>
-      <c r="V12" s="22" t="str">
-        <f aca="false">IF($N12=0,"No Restock Needed",IF($T12="Sea","On Track",IF($T12="Air — Expedite","Expedite Required","Critical — May Miss Launch")))</f>
+      <c r="W13" s="23" t="str">
+        <f aca="false">IF($O13=0,"No Restock Needed",IF($U13="Sea","On Track",IF($U13="Air — Expedite","Expedite Required","Critical — May Miss Launch")))</f>
         <v>Expedite Required</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="19" t="str">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="20" t="str">
         <f aca="false">'Inventory &amp; Coverage'!A11</f>
         <v>HN-HM-100</v>
       </c>
-      <c r="B13" s="19" t="str">
+      <c r="B14" s="20" t="str">
         <f aca="false">'Inventory &amp; Coverage'!B11</f>
         <v>Hair Mask 100ml</v>
       </c>
-      <c r="C13" s="19" t="str">
+      <c r="C14" s="20" t="str">
         <f aca="false">'Inventory &amp; Coverage'!D11</f>
         <v>Factory C</v>
       </c>
-      <c r="D13" s="19" t="str">
-        <f aca="false">IFERROR(INDEX('Reference Data'!$B$22:$B$27,MATCH($C13,'Reference Data'!$A$22:$A$27,0)),"N/A")</f>
+      <c r="D14" s="20" t="str">
+        <f aca="false">IFERROR(INDEX('Reference Data'!$B$22:$B$27,MATCH($C14,'Reference Data'!$A$22:$A$27,0)),"N/A")</f>
         <v>Jakarta</v>
       </c>
-      <c r="E13" s="20" t="n">
+      <c r="E14" s="21" t="n">
         <f aca="false">'Inventory &amp; Coverage'!F11</f>
         <v>25</v>
       </c>
-      <c r="F13" s="20" t="n">
+      <c r="F14" s="21" t="n">
         <f aca="false">'Inventory &amp; Coverage'!I11</f>
         <v>30</v>
       </c>
-      <c r="G13" s="20" t="n">
+      <c r="G14" s="21" t="n">
         <f aca="false">'Inventory &amp; Coverage'!O11</f>
         <v>0</v>
       </c>
-      <c r="H13" s="21" t="n">
+      <c r="H14" s="22" t="n">
         <f aca="false">'Inventory &amp; Coverage'!L11</f>
         <v>0.833333333333333</v>
       </c>
-      <c r="I13" s="22" t="str">
+      <c r="I14" s="23" t="str">
         <f aca="false">'Inventory &amp; Coverage'!M11</f>
         <v>High Risk</v>
       </c>
-      <c r="J13" s="20" t="n">
-        <f aca="false">MAX($E13-$F13*$B$7,0)+$G13</f>
+      <c r="J14" s="21" t="n">
+        <f aca="false">MAX($E14-$F14*$B$8,0)+$G14</f>
         <v>0</v>
       </c>
-      <c r="K13" s="20" t="n">
-        <f aca="false">$F13*$B$5</f>
+      <c r="K14" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="21" t="n">
+        <f aca="false">$F14*$B$5+$K14</f>
         <v>300</v>
       </c>
-      <c r="L13" s="20" t="n">
-        <f aca="false">MAX($K13-$J13,0)</f>
+      <c r="M14" s="21" t="n">
+        <f aca="false">MAX($L14-$J14,0)</f>
         <v>300</v>
       </c>
-      <c r="M13" s="20" t="n">
-        <f aca="false">IFERROR(INDEX('Reference Data'!$F$22:$F$27,MATCH($C13,'Reference Data'!$A$22:$A$27,0)),"N/A")</f>
+      <c r="N14" s="21" t="n">
+        <f aca="false">IFERROR(INDEX('Reference Data'!$F$22:$F$27,MATCH($C14,'Reference Data'!$A$22:$A$27,0)),"N/A")</f>
         <v>300</v>
       </c>
-      <c r="N13" s="20" t="n">
-        <f aca="false">IF($L13&lt;=0,0,MAX($L13,$M13))</f>
+      <c r="O14" s="21" t="n">
+        <f aca="false">IF($M14&lt;=0,0,MAX($M14,$N14))</f>
         <v>300</v>
       </c>
-      <c r="O13" s="21" t="n">
-        <f aca="false">IFERROR(INDEX('Reference Data'!$G$22:$G$27,MATCH($C13,'Reference Data'!$A$22:$A$27,0)),"N/A")</f>
+      <c r="P14" s="22" t="n">
+        <f aca="false">IFERROR(INDEX('Reference Data'!$G$22:$G$27,MATCH($C14,'Reference Data'!$A$22:$A$27,0)),"N/A")</f>
         <v>3</v>
       </c>
-      <c r="P13" s="23" t="n">
-        <f aca="false">IFERROR(INDEX('Reference Data'!$C$31:$C$45,MATCH($D13&amp;"|UK",'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
+      <c r="Q14" s="25" t="n">
+        <f aca="false">IFERROR(INDEX('Reference Data'!$C$31:$C$45,MATCH($D14&amp;"|UK",'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
         <v>5</v>
       </c>
-      <c r="Q13" s="23" t="n">
-        <f aca="false">IFERROR(INDEX('Reference Data'!$E$31:$E$45,MATCH($D13&amp;"|UK",'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
+      <c r="R14" s="25" t="n">
+        <f aca="false">IFERROR(INDEX('Reference Data'!$E$31:$E$45,MATCH($D14&amp;"|UK",'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
         <v>1</v>
       </c>
-      <c r="R13" s="23" t="n">
-        <f aca="false">$O13+$P13</f>
+      <c r="S14" s="25" t="n">
+        <f aca="false">$P14+$Q14</f>
         <v>8</v>
       </c>
-      <c r="S13" s="23" t="n">
-        <f aca="false">$O13+$Q13</f>
+      <c r="T14" s="25" t="n">
+        <f aca="false">$P14+$R14</f>
         <v>4</v>
       </c>
-      <c r="T13" s="22" t="str">
-        <f aca="false">IF($N13=0,"No Order Needed",IF($R13&lt;=$B$7,"Sea",IF($S13&lt;=$B$7,"Air — Expedite","Air — Still At Risk")))</f>
+      <c r="U14" s="23" t="str">
+        <f aca="false">IF($O14=0,"No Order Needed",IF($S14&lt;=$B$8,"Sea",IF($T14&lt;=$B$8,"Air — Expedite","Air — Still At Risk")))</f>
         <v>Air — Expedite</v>
       </c>
-      <c r="U13" s="16" t="n">
-        <f aca="false">IF($N13=0,"N/A",$B$4-IF($T13="Sea",$R13,$S13)*7)</f>
+      <c r="V14" s="17" t="n">
+        <f aca="false">IF($O14=0,"N/A",$B$4-IF($U14="Sea",$S14,$T14)*7)</f>
         <v>46258</v>
       </c>
-      <c r="V13" s="22" t="str">
-        <f aca="false">IF($N13=0,"No Restock Needed",IF($T13="Sea","On Track",IF($T13="Air — Expedite","Expedite Required","Critical — May Miss Launch")))</f>
+      <c r="W14" s="23" t="str">
+        <f aca="false">IF($O14=0,"No Restock Needed",IF($U14="Sea","On Track",IF($U14="Air — Expedite","Expedite Required","Critical — May Miss Launch")))</f>
         <v>Expedite Required</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="19" t="str">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="20" t="str">
         <f aca="false">'Inventory &amp; Coverage'!A12</f>
         <v>HN-LB-250</v>
       </c>
-      <c r="B14" s="19" t="str">
+      <c r="B15" s="20" t="str">
         <f aca="false">'Inventory &amp; Coverage'!B12</f>
         <v>Lip Balm 3-Pack</v>
       </c>
-      <c r="C14" s="19" t="str">
+      <c r="C15" s="20" t="str">
         <f aca="false">'Inventory &amp; Coverage'!D12</f>
         <v>Factory D</v>
       </c>
-      <c r="D14" s="19" t="str">
-        <f aca="false">IFERROR(INDEX('Reference Data'!$B$22:$B$27,MATCH($C14,'Reference Data'!$A$22:$A$27,0)),"N/A")</f>
+      <c r="D15" s="20" t="str">
+        <f aca="false">IFERROR(INDEX('Reference Data'!$B$22:$B$27,MATCH($C15,'Reference Data'!$A$22:$A$27,0)),"N/A")</f>
         <v>Taipei</v>
       </c>
-      <c r="E14" s="20" t="n">
+      <c r="E15" s="21" t="n">
         <f aca="false">'Inventory &amp; Coverage'!F12</f>
         <v>40</v>
       </c>
-      <c r="F14" s="20" t="n">
+      <c r="F15" s="21" t="n">
         <f aca="false">'Inventory &amp; Coverage'!I12</f>
         <v>60</v>
       </c>
-      <c r="G14" s="20" t="n">
+      <c r="G15" s="21" t="n">
         <f aca="false">'Inventory &amp; Coverage'!O12</f>
         <v>0</v>
       </c>
-      <c r="H14" s="21" t="n">
+      <c r="H15" s="22" t="n">
         <f aca="false">'Inventory &amp; Coverage'!L12</f>
         <v>0.666666666666667</v>
       </c>
-      <c r="I14" s="22" t="str">
+      <c r="I15" s="23" t="str">
         <f aca="false">'Inventory &amp; Coverage'!M12</f>
         <v>High Risk</v>
       </c>
-      <c r="J14" s="20" t="n">
-        <f aca="false">MAX($E14-$F14*$B$7,0)+$G14</f>
+      <c r="J15" s="21" t="n">
+        <f aca="false">MAX($E15-$F15*$B$8,0)+$G15</f>
         <v>0</v>
       </c>
-      <c r="K14" s="20" t="n">
-        <f aca="false">$F14*$B$5</f>
+      <c r="K15" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="21" t="n">
+        <f aca="false">$F15*$B$5+$K15</f>
         <v>600</v>
       </c>
-      <c r="L14" s="20" t="n">
-        <f aca="false">MAX($K14-$J14,0)</f>
+      <c r="M15" s="21" t="n">
+        <f aca="false">MAX($L15-$J15,0)</f>
         <v>600</v>
       </c>
-      <c r="M14" s="20" t="n">
-        <f aca="false">IFERROR(INDEX('Reference Data'!$F$22:$F$27,MATCH($C14,'Reference Data'!$A$22:$A$27,0)),"N/A")</f>
+      <c r="N15" s="21" t="n">
+        <f aca="false">IFERROR(INDEX('Reference Data'!$F$22:$F$27,MATCH($C15,'Reference Data'!$A$22:$A$27,0)),"N/A")</f>
         <v>1000</v>
       </c>
-      <c r="N14" s="20" t="n">
-        <f aca="false">IF($L14&lt;=0,0,MAX($L14,$M14))</f>
+      <c r="O15" s="21" t="n">
+        <f aca="false">IF($M15&lt;=0,0,MAX($M15,$N15))</f>
         <v>1000</v>
       </c>
-      <c r="O14" s="21" t="n">
-        <f aca="false">IFERROR(INDEX('Reference Data'!$G$22:$G$27,MATCH($C14,'Reference Data'!$A$22:$A$27,0)),"N/A")</f>
+      <c r="P15" s="22" t="n">
+        <f aca="false">IFERROR(INDEX('Reference Data'!$G$22:$G$27,MATCH($C15,'Reference Data'!$A$22:$A$27,0)),"N/A")</f>
         <v>2</v>
       </c>
-      <c r="P14" s="23" t="n">
-        <f aca="false">IFERROR(INDEX('Reference Data'!$C$31:$C$45,MATCH($D14&amp;"|UK",'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
+      <c r="Q15" s="25" t="n">
+        <f aca="false">IFERROR(INDEX('Reference Data'!$C$31:$C$45,MATCH($D15&amp;"|UK",'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
         <v>5</v>
       </c>
-      <c r="Q14" s="23" t="n">
-        <f aca="false">IFERROR(INDEX('Reference Data'!$E$31:$E$45,MATCH($D14&amp;"|UK",'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
+      <c r="R15" s="25" t="n">
+        <f aca="false">IFERROR(INDEX('Reference Data'!$E$31:$E$45,MATCH($D15&amp;"|UK",'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
         <v>0.857142857142857</v>
       </c>
-      <c r="R14" s="23" t="n">
-        <f aca="false">$O14+$P14</f>
+      <c r="S15" s="25" t="n">
+        <f aca="false">$P15+$Q15</f>
         <v>7</v>
       </c>
-      <c r="S14" s="23" t="n">
-        <f aca="false">$O14+$Q14</f>
+      <c r="T15" s="25" t="n">
+        <f aca="false">$P15+$R15</f>
         <v>2.85714285714286</v>
       </c>
-      <c r="T14" s="22" t="str">
-        <f aca="false">IF($N14=0,"No Order Needed",IF($R14&lt;=$B$7,"Sea",IF($S14&lt;=$B$7,"Air — Expedite","Air — Still At Risk")))</f>
+      <c r="U15" s="23" t="str">
+        <f aca="false">IF($O15=0,"No Order Needed",IF($S15&lt;=$B$8,"Sea",IF($T15&lt;=$B$8,"Air — Expedite","Air — Still At Risk")))</f>
         <v>Air — Expedite</v>
       </c>
-      <c r="U14" s="16" t="n">
-        <f aca="false">IF($N14=0,"N/A",$B$4-IF($T14="Sea",$R14,$S14)*7)</f>
+      <c r="V15" s="17" t="n">
+        <f aca="false">IF($O15=0,"N/A",$B$4-IF($U15="Sea",$S15,$T15)*7)</f>
         <v>46266</v>
       </c>
-      <c r="V14" s="22" t="str">
-        <f aca="false">IF($N14=0,"No Restock Needed",IF($T14="Sea","On Track",IF($T14="Air — Expedite","Expedite Required","Critical — May Miss Launch")))</f>
+      <c r="W15" s="23" t="str">
+        <f aca="false">IF($O15=0,"No Restock Needed",IF($U15="Sea","On Track",IF($U15="Air — Expedite","Expedite Required","Critical — May Miss Launch")))</f>
         <v>Expedite Required</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="19" t="str">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="20" t="str">
         <f aca="false">'Inventory &amp; Coverage'!A13</f>
         <v>HN-SM-150</v>
       </c>
-      <c r="B15" s="19" t="str">
+      <c r="B16" s="20" t="str">
         <f aca="false">'Inventory &amp; Coverage'!B13</f>
         <v>Scalp Mist 150ml</v>
       </c>
-      <c r="C15" s="19" t="str">
+      <c r="C16" s="20" t="str">
         <f aca="false">'Inventory &amp; Coverage'!D13</f>
         <v>Factory C</v>
       </c>
-      <c r="D15" s="19" t="str">
-        <f aca="false">IFERROR(INDEX('Reference Data'!$B$22:$B$27,MATCH($C15,'Reference Data'!$A$22:$A$27,0)),"N/A")</f>
+      <c r="D16" s="20" t="str">
+        <f aca="false">IFERROR(INDEX('Reference Data'!$B$22:$B$27,MATCH($C16,'Reference Data'!$A$22:$A$27,0)),"N/A")</f>
         <v>Jakarta</v>
       </c>
-      <c r="E15" s="20" t="n">
+      <c r="E16" s="21" t="n">
         <f aca="false">'Inventory &amp; Coverage'!F13</f>
         <v>10</v>
       </c>
-      <c r="F15" s="20" t="n">
+      <c r="F16" s="21" t="n">
         <f aca="false">'Inventory &amp; Coverage'!I13</f>
         <v>20</v>
       </c>
-      <c r="G15" s="20" t="n">
+      <c r="G16" s="21" t="n">
         <f aca="false">'Inventory &amp; Coverage'!O13</f>
         <v>0</v>
       </c>
-      <c r="H15" s="21" t="n">
+      <c r="H16" s="22" t="n">
         <f aca="false">'Inventory &amp; Coverage'!L13</f>
         <v>0.5</v>
       </c>
-      <c r="I15" s="22" t="str">
+      <c r="I16" s="23" t="str">
         <f aca="false">'Inventory &amp; Coverage'!M13</f>
         <v>High Risk</v>
       </c>
-      <c r="J15" s="20" t="n">
-        <f aca="false">MAX($E15-$F15*$B$7,0)+$G15</f>
+      <c r="J16" s="21" t="n">
+        <f aca="false">MAX($E16-$F16*$B$8,0)+$G16</f>
         <v>0</v>
       </c>
-      <c r="K15" s="20" t="n">
-        <f aca="false">$F15*$B$5</f>
+      <c r="K16" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="21" t="n">
+        <f aca="false">$F16*$B$5+$K16</f>
         <v>200</v>
       </c>
-      <c r="L15" s="20" t="n">
-        <f aca="false">MAX($K15-$J15,0)</f>
+      <c r="M16" s="21" t="n">
+        <f aca="false">MAX($L16-$J16,0)</f>
         <v>200</v>
       </c>
-      <c r="M15" s="20" t="n">
-        <f aca="false">IFERROR(INDEX('Reference Data'!$F$22:$F$27,MATCH($C15,'Reference Data'!$A$22:$A$27,0)),"N/A")</f>
+      <c r="N16" s="21" t="n">
+        <f aca="false">IFERROR(INDEX('Reference Data'!$F$22:$F$27,MATCH($C16,'Reference Data'!$A$22:$A$27,0)),"N/A")</f>
         <v>300</v>
       </c>
-      <c r="N15" s="20" t="n">
-        <f aca="false">IF($L15&lt;=0,0,MAX($L15,$M15))</f>
+      <c r="O16" s="21" t="n">
+        <f aca="false">IF($M16&lt;=0,0,MAX($M16,$N16))</f>
         <v>300</v>
       </c>
-      <c r="O15" s="21" t="n">
-        <f aca="false">IFERROR(INDEX('Reference Data'!$G$22:$G$27,MATCH($C15,'Reference Data'!$A$22:$A$27,0)),"N/A")</f>
+      <c r="P16" s="22" t="n">
+        <f aca="false">IFERROR(INDEX('Reference Data'!$G$22:$G$27,MATCH($C16,'Reference Data'!$A$22:$A$27,0)),"N/A")</f>
         <v>3</v>
       </c>
-      <c r="P15" s="23" t="n">
-        <f aca="false">IFERROR(INDEX('Reference Data'!$C$31:$C$45,MATCH($D15&amp;"|UK",'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
+      <c r="Q16" s="25" t="n">
+        <f aca="false">IFERROR(INDEX('Reference Data'!$C$31:$C$45,MATCH($D16&amp;"|UK",'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
         <v>5</v>
       </c>
-      <c r="Q15" s="23" t="n">
-        <f aca="false">IFERROR(INDEX('Reference Data'!$E$31:$E$45,MATCH($D15&amp;"|UK",'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
+      <c r="R16" s="25" t="n">
+        <f aca="false">IFERROR(INDEX('Reference Data'!$E$31:$E$45,MATCH($D16&amp;"|UK",'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
         <v>1</v>
       </c>
-      <c r="R15" s="23" t="n">
-        <f aca="false">$O15+$P15</f>
+      <c r="S16" s="25" t="n">
+        <f aca="false">$P16+$Q16</f>
         <v>8</v>
       </c>
-      <c r="S15" s="23" t="n">
-        <f aca="false">$O15+$Q15</f>
+      <c r="T16" s="25" t="n">
+        <f aca="false">$P16+$R16</f>
         <v>4</v>
       </c>
-      <c r="T15" s="22" t="str">
-        <f aca="false">IF($N15=0,"No Order Needed",IF($R15&lt;=$B$7,"Sea",IF($S15&lt;=$B$7,"Air — Expedite","Air — Still At Risk")))</f>
+      <c r="U16" s="23" t="str">
+        <f aca="false">IF($O16=0,"No Order Needed",IF($S16&lt;=$B$8,"Sea",IF($T16&lt;=$B$8,"Air — Expedite","Air — Still At Risk")))</f>
         <v>Air — Expedite</v>
       </c>
-      <c r="U15" s="16" t="n">
-        <f aca="false">IF($N15=0,"N/A",$B$4-IF($T15="Sea",$R15,$S15)*7)</f>
+      <c r="V16" s="17" t="n">
+        <f aca="false">IF($O16=0,"N/A",$B$4-IF($U16="Sea",$S16,$T16)*7)</f>
         <v>46258</v>
       </c>
-      <c r="V15" s="22" t="str">
-        <f aca="false">IF($N15=0,"No Restock Needed",IF($T15="Sea","On Track",IF($T15="Air — Expedite","Expedite Required","Critical — May Miss Launch")))</f>
+      <c r="W16" s="23" t="str">
+        <f aca="false">IF($O16=0,"No Restock Needed",IF($U16="Sea","On Track",IF($U16="Air — Expedite","Expedite Required","Critical — May Miss Launch")))</f>
         <v>Expedite Required</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="19" t="str">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="20" t="str">
         <f aca="false">'Inventory &amp; Coverage'!A14</f>
         <v>HN-EO-030</v>
       </c>
-      <c r="B16" s="19" t="str">
+      <c r="B17" s="20" t="str">
         <f aca="false">'Inventory &amp; Coverage'!B14</f>
         <v>Essential Oil Blend 30ml</v>
       </c>
-      <c r="C16" s="19" t="str">
+      <c r="C17" s="20" t="str">
         <f aca="false">'Inventory &amp; Coverage'!D14</f>
         <v>Factory E</v>
       </c>
-      <c r="D16" s="19" t="str">
-        <f aca="false">IFERROR(INDEX('Reference Data'!$B$22:$B$27,MATCH($C16,'Reference Data'!$A$22:$A$27,0)),"N/A")</f>
+      <c r="D17" s="20" t="str">
+        <f aca="false">IFERROR(INDEX('Reference Data'!$B$22:$B$27,MATCH($C17,'Reference Data'!$A$22:$A$27,0)),"N/A")</f>
         <v>Chiang Mai</v>
       </c>
-      <c r="E16" s="20" t="n">
+      <c r="E17" s="21" t="n">
         <f aca="false">'Inventory &amp; Coverage'!F14</f>
         <v>8</v>
       </c>
-      <c r="F16" s="20" t="n">
+      <c r="F17" s="21" t="n">
         <f aca="false">'Inventory &amp; Coverage'!I14</f>
         <v>15</v>
       </c>
-      <c r="G16" s="20" t="n">
+      <c r="G17" s="21" t="n">
         <f aca="false">'Inventory &amp; Coverage'!O14</f>
         <v>0</v>
       </c>
-      <c r="H16" s="21" t="n">
+      <c r="H17" s="22" t="n">
         <f aca="false">'Inventory &amp; Coverage'!L14</f>
         <v>0.533333333333333</v>
       </c>
-      <c r="I16" s="22" t="str">
+      <c r="I17" s="23" t="str">
         <f aca="false">'Inventory &amp; Coverage'!M14</f>
         <v>High Risk</v>
       </c>
-      <c r="J16" s="20" t="n">
-        <f aca="false">MAX($E16-$F16*$B$7,0)+$G16</f>
+      <c r="J17" s="21" t="n">
+        <f aca="false">MAX($E17-$F17*$B$8,0)+$G17</f>
         <v>0</v>
       </c>
-      <c r="K16" s="20" t="n">
-        <f aca="false">$F16*$B$5</f>
+      <c r="K17" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="21" t="n">
+        <f aca="false">$F17*$B$5+$K17</f>
         <v>150</v>
       </c>
-      <c r="L16" s="20" t="n">
-        <f aca="false">MAX($K16-$J16,0)</f>
+      <c r="M17" s="21" t="n">
+        <f aca="false">MAX($L17-$J17,0)</f>
         <v>150</v>
       </c>
-      <c r="M16" s="20" t="n">
-        <f aca="false">IFERROR(INDEX('Reference Data'!$F$22:$F$27,MATCH($C16,'Reference Data'!$A$22:$A$27,0)),"N/A")</f>
+      <c r="N17" s="21" t="n">
+        <f aca="false">IFERROR(INDEX('Reference Data'!$F$22:$F$27,MATCH($C17,'Reference Data'!$A$22:$A$27,0)),"N/A")</f>
         <v>200</v>
       </c>
-      <c r="N16" s="20" t="n">
-        <f aca="false">IF($L16&lt;=0,0,MAX($L16,$M16))</f>
+      <c r="O17" s="21" t="n">
+        <f aca="false">IF($M17&lt;=0,0,MAX($M17,$N17))</f>
         <v>200</v>
       </c>
-      <c r="O16" s="21" t="n">
-        <f aca="false">IFERROR(INDEX('Reference Data'!$G$22:$G$27,MATCH($C16,'Reference Data'!$A$22:$A$27,0)),"N/A")</f>
+      <c r="P17" s="22" t="n">
+        <f aca="false">IFERROR(INDEX('Reference Data'!$G$22:$G$27,MATCH($C17,'Reference Data'!$A$22:$A$27,0)),"N/A")</f>
         <v>2</v>
       </c>
-      <c r="P16" s="23" t="n">
-        <f aca="false">IFERROR(INDEX('Reference Data'!$C$31:$C$45,MATCH($D16&amp;"|UK",'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
+      <c r="Q17" s="25" t="n">
+        <f aca="false">IFERROR(INDEX('Reference Data'!$C$31:$C$45,MATCH($D17&amp;"|UK",'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
         <v>4.5</v>
       </c>
-      <c r="Q16" s="23" t="n">
-        <f aca="false">IFERROR(INDEX('Reference Data'!$E$31:$E$45,MATCH($D16&amp;"|UK",'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
+      <c r="R17" s="25" t="n">
+        <f aca="false">IFERROR(INDEX('Reference Data'!$E$31:$E$45,MATCH($D17&amp;"|UK",'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
         <v>1</v>
       </c>
-      <c r="R16" s="23" t="n">
-        <f aca="false">$O16+$P16</f>
+      <c r="S17" s="25" t="n">
+        <f aca="false">$P17+$Q17</f>
         <v>6.5</v>
       </c>
-      <c r="S16" s="23" t="n">
-        <f aca="false">$O16+$Q16</f>
+      <c r="T17" s="25" t="n">
+        <f aca="false">$P17+$R17</f>
         <v>3</v>
       </c>
-      <c r="T16" s="22" t="str">
-        <f aca="false">IF($N16=0,"No Order Needed",IF($R16&lt;=$B$7,"Sea",IF($S16&lt;=$B$7,"Air — Expedite","Air — Still At Risk")))</f>
+      <c r="U17" s="23" t="str">
+        <f aca="false">IF($O17=0,"No Order Needed",IF($S17&lt;=$B$8,"Sea",IF($T17&lt;=$B$8,"Air — Expedite","Air — Still At Risk")))</f>
         <v>Air — Expedite</v>
       </c>
-      <c r="U16" s="16" t="n">
-        <f aca="false">IF($N16=0,"N/A",$B$4-IF($T16="Sea",$R16,$S16)*7)</f>
+      <c r="V17" s="17" t="n">
+        <f aca="false">IF($O17=0,"N/A",$B$4-IF($U17="Sea",$S17,$T17)*7)</f>
         <v>46265</v>
       </c>
-      <c r="V16" s="22" t="str">
-        <f aca="false">IF($N16=0,"No Restock Needed",IF($T16="Sea","On Track",IF($T16="Air — Expedite","Expedite Required","Critical — May Miss Launch")))</f>
+      <c r="W17" s="23" t="str">
+        <f aca="false">IF($O17=0,"No Restock Needed",IF($U17="Sea","On Track",IF($U17="Air — Expedite","Expedite Required","Critical — May Miss Launch")))</f>
         <v>Expedite Required</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="19" t="str">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="20" t="str">
         <f aca="false">'Inventory &amp; Coverage'!A15</f>
         <v>HN-BC-400</v>
       </c>
-      <c r="B17" s="19" t="str">
+      <c r="B18" s="20" t="str">
         <f aca="false">'Inventory &amp; Coverage'!B15</f>
         <v>Bath Crystals 400g</v>
       </c>
-      <c r="C17" s="19" t="str">
+      <c r="C18" s="20" t="str">
         <f aca="false">'Inventory &amp; Coverage'!D15</f>
         <v>Factory F</v>
       </c>
-      <c r="D17" s="19" t="str">
-        <f aca="false">IFERROR(INDEX('Reference Data'!$B$22:$B$27,MATCH($C17,'Reference Data'!$A$22:$A$27,0)),"N/A")</f>
+      <c r="D18" s="20" t="str">
+        <f aca="false">IFERROR(INDEX('Reference Data'!$B$22:$B$27,MATCH($C18,'Reference Data'!$A$22:$A$27,0)),"N/A")</f>
         <v>Ho Chi Minh City</v>
       </c>
-      <c r="E17" s="20" t="n">
+      <c r="E18" s="21" t="n">
         <f aca="false">'Inventory &amp; Coverage'!F15</f>
         <v>15</v>
       </c>
-      <c r="F17" s="20" t="n">
+      <c r="F18" s="21" t="n">
         <f aca="false">'Inventory &amp; Coverage'!I15</f>
         <v>25</v>
       </c>
-      <c r="G17" s="20" t="n">
+      <c r="G18" s="21" t="n">
         <f aca="false">'Inventory &amp; Coverage'!O15</f>
         <v>0</v>
       </c>
-      <c r="H17" s="21" t="n">
+      <c r="H18" s="22" t="n">
         <f aca="false">'Inventory &amp; Coverage'!L15</f>
         <v>0.6</v>
       </c>
-      <c r="I17" s="22" t="str">
+      <c r="I18" s="23" t="str">
         <f aca="false">'Inventory &amp; Coverage'!M15</f>
         <v>High Risk</v>
       </c>
-      <c r="J17" s="20" t="n">
-        <f aca="false">MAX($E17-$F17*$B$7,0)+$G17</f>
+      <c r="J18" s="21" t="n">
+        <f aca="false">MAX($E18-$F18*$B$8,0)+$G18</f>
         <v>0</v>
       </c>
-      <c r="K17" s="20" t="n">
-        <f aca="false">$F17*$B$5</f>
+      <c r="K18" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="21" t="n">
+        <f aca="false">$F18*$B$5+$K18</f>
         <v>250</v>
       </c>
-      <c r="L17" s="20" t="n">
-        <f aca="false">MAX($K17-$J17,0)</f>
+      <c r="M18" s="21" t="n">
+        <f aca="false">MAX($L18-$J18,0)</f>
         <v>250</v>
       </c>
-      <c r="M17" s="20" t="n">
-        <f aca="false">IFERROR(INDEX('Reference Data'!$F$22:$F$27,MATCH($C17,'Reference Data'!$A$22:$A$27,0)),"N/A")</f>
+      <c r="N18" s="21" t="n">
+        <f aca="false">IFERROR(INDEX('Reference Data'!$F$22:$F$27,MATCH($C18,'Reference Data'!$A$22:$A$27,0)),"N/A")</f>
         <v>500</v>
       </c>
-      <c r="N17" s="20" t="n">
-        <f aca="false">IF($L17&lt;=0,0,MAX($L17,$M17))</f>
+      <c r="O18" s="21" t="n">
+        <f aca="false">IF($M18&lt;=0,0,MAX($M18,$N18))</f>
         <v>500</v>
       </c>
-      <c r="O17" s="21" t="n">
-        <f aca="false">IFERROR(INDEX('Reference Data'!$G$22:$G$27,MATCH($C17,'Reference Data'!$A$22:$A$27,0)),"N/A")</f>
+      <c r="P18" s="22" t="n">
+        <f aca="false">IFERROR(INDEX('Reference Data'!$G$22:$G$27,MATCH($C18,'Reference Data'!$A$22:$A$27,0)),"N/A")</f>
         <v>4</v>
       </c>
-      <c r="P17" s="23" t="n">
-        <f aca="false">IFERROR(INDEX('Reference Data'!$C$31:$C$45,MATCH($D17&amp;"|UK",'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
+      <c r="Q18" s="25" t="n">
+        <f aca="false">IFERROR(INDEX('Reference Data'!$C$31:$C$45,MATCH($D18&amp;"|UK",'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
         <v>5</v>
       </c>
-      <c r="Q17" s="23" t="n">
-        <f aca="false">IFERROR(INDEX('Reference Data'!$E$31:$E$45,MATCH($D17&amp;"|UK",'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
+      <c r="R18" s="25" t="n">
+        <f aca="false">IFERROR(INDEX('Reference Data'!$E$31:$E$45,MATCH($D18&amp;"|UK",'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
         <v>1</v>
       </c>
-      <c r="R17" s="23" t="n">
-        <f aca="false">$O17+$P17</f>
+      <c r="S18" s="25" t="n">
+        <f aca="false">$P18+$Q18</f>
         <v>9</v>
       </c>
-      <c r="S17" s="23" t="n">
-        <f aca="false">$O17+$Q17</f>
+      <c r="T18" s="25" t="n">
+        <f aca="false">$P18+$R18</f>
         <v>5</v>
       </c>
-      <c r="T17" s="22" t="str">
-        <f aca="false">IF($N17=0,"No Order Needed",IF($R17&lt;=$B$7,"Sea",IF($S17&lt;=$B$7,"Air — Expedite","Air — Still At Risk")))</f>
+      <c r="U18" s="23" t="str">
+        <f aca="false">IF($O18=0,"No Order Needed",IF($S18&lt;=$B$8,"Sea",IF($T18&lt;=$B$8,"Air — Expedite","Air — Still At Risk")))</f>
         <v>Air — Expedite</v>
       </c>
-      <c r="U17" s="16" t="n">
-        <f aca="false">IF($N17=0,"N/A",$B$4-IF($T17="Sea",$R17,$S17)*7)</f>
+      <c r="V18" s="17" t="n">
+        <f aca="false">IF($O18=0,"N/A",$B$4-IF($U18="Sea",$S18,$T18)*7)</f>
         <v>46251</v>
       </c>
-      <c r="V17" s="22" t="str">
-        <f aca="false">IF($N17=0,"No Restock Needed",IF($T17="Sea","On Track",IF($T17="Air — Expedite","Expedite Required","Critical — May Miss Launch")))</f>
+      <c r="W18" s="23" t="str">
+        <f aca="false">IF($O18=0,"No Restock Needed",IF($U18="Sea","On Track",IF($U18="Air — Expedite","Expedite Required","Critical — May Miss Launch")))</f>
         <v>Expedite Required</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="19" t="str">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="20" t="str">
         <f aca="false">'Inventory &amp; Coverage'!A16</f>
         <v>HN-NC-075</v>
       </c>
-      <c r="B18" s="19" t="str">
+      <c r="B19" s="20" t="str">
         <f aca="false">'Inventory &amp; Coverage'!B16</f>
         <v>Night Cream 75ml</v>
       </c>
-      <c r="C18" s="19" t="str">
+      <c r="C19" s="20" t="str">
         <f aca="false">'Inventory &amp; Coverage'!D16</f>
         <v>Factory A</v>
       </c>
-      <c r="D18" s="19" t="str">
-        <f aca="false">IFERROR(INDEX('Reference Data'!$B$22:$B$27,MATCH($C18,'Reference Data'!$A$22:$A$27,0)),"N/A")</f>
+      <c r="D19" s="20" t="str">
+        <f aca="false">IFERROR(INDEX('Reference Data'!$B$22:$B$27,MATCH($C19,'Reference Data'!$A$22:$A$27,0)),"N/A")</f>
         <v>Shenzhen</v>
       </c>
-      <c r="E18" s="20" t="n">
+      <c r="E19" s="21" t="n">
         <f aca="false">'Inventory &amp; Coverage'!F16</f>
         <v>18</v>
       </c>
-      <c r="F18" s="20" t="n">
+      <c r="F19" s="21" t="n">
         <f aca="false">'Inventory &amp; Coverage'!I16</f>
         <v>40</v>
       </c>
-      <c r="G18" s="20" t="n">
+      <c r="G19" s="21" t="n">
         <f aca="false">'Inventory &amp; Coverage'!O16</f>
         <v>0</v>
       </c>
-      <c r="H18" s="21" t="n">
+      <c r="H19" s="22" t="n">
         <f aca="false">'Inventory &amp; Coverage'!L16</f>
         <v>0.45</v>
       </c>
-      <c r="I18" s="22" t="str">
+      <c r="I19" s="23" t="str">
         <f aca="false">'Inventory &amp; Coverage'!M16</f>
         <v>High Risk</v>
       </c>
-      <c r="J18" s="20" t="n">
-        <f aca="false">MAX($E18-$F18*$B$7,0)+$G18</f>
+      <c r="J19" s="21" t="n">
+        <f aca="false">MAX($E19-$F19*$B$8,0)+$G19</f>
         <v>0</v>
       </c>
-      <c r="K18" s="20" t="n">
-        <f aca="false">$F18*$B$5</f>
+      <c r="K19" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="21" t="n">
+        <f aca="false">$F19*$B$5+$K19</f>
         <v>400</v>
       </c>
-      <c r="L18" s="20" t="n">
-        <f aca="false">MAX($K18-$J18,0)</f>
+      <c r="M19" s="21" t="n">
+        <f aca="false">MAX($L19-$J19,0)</f>
         <v>400</v>
       </c>
-      <c r="M18" s="20" t="n">
-        <f aca="false">IFERROR(INDEX('Reference Data'!$F$22:$F$27,MATCH($C18,'Reference Data'!$A$22:$A$27,0)),"N/A")</f>
+      <c r="N19" s="21" t="n">
+        <f aca="false">IFERROR(INDEX('Reference Data'!$F$22:$F$27,MATCH($C19,'Reference Data'!$A$22:$A$27,0)),"N/A")</f>
         <v>500</v>
       </c>
-      <c r="N18" s="20" t="n">
-        <f aca="false">IF($L18&lt;=0,0,MAX($L18,$M18))</f>
+      <c r="O19" s="21" t="n">
+        <f aca="false">IF($M19&lt;=0,0,MAX($M19,$N19))</f>
         <v>500</v>
       </c>
-      <c r="O18" s="21" t="n">
-        <f aca="false">IFERROR(INDEX('Reference Data'!$G$22:$G$27,MATCH($C18,'Reference Data'!$A$22:$A$27,0)),"N/A")</f>
+      <c r="P19" s="22" t="n">
+        <f aca="false">IFERROR(INDEX('Reference Data'!$G$22:$G$27,MATCH($C19,'Reference Data'!$A$22:$A$27,0)),"N/A")</f>
         <v>3</v>
       </c>
-      <c r="P18" s="23" t="n">
-        <f aca="false">IFERROR(INDEX('Reference Data'!$C$31:$C$45,MATCH($D18&amp;"|UK",'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
+      <c r="Q19" s="25" t="n">
+        <f aca="false">IFERROR(INDEX('Reference Data'!$C$31:$C$45,MATCH($D19&amp;"|UK",'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
         <v>5</v>
       </c>
-      <c r="Q18" s="23" t="n">
-        <f aca="false">IFERROR(INDEX('Reference Data'!$E$31:$E$45,MATCH($D18&amp;"|UK",'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
+      <c r="R19" s="25" t="n">
+        <f aca="false">IFERROR(INDEX('Reference Data'!$E$31:$E$45,MATCH($D19&amp;"|UK",'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
         <v>1</v>
       </c>
-      <c r="R18" s="23" t="n">
-        <f aca="false">$O18+$P18</f>
+      <c r="S19" s="25" t="n">
+        <f aca="false">$P19+$Q19</f>
         <v>8</v>
       </c>
-      <c r="S18" s="23" t="n">
-        <f aca="false">$O18+$Q18</f>
+      <c r="T19" s="25" t="n">
+        <f aca="false">$P19+$R19</f>
         <v>4</v>
       </c>
-      <c r="T18" s="22" t="str">
-        <f aca="false">IF($N18=0,"No Order Needed",IF($R18&lt;=$B$7,"Sea",IF($S18&lt;=$B$7,"Air — Expedite","Air — Still At Risk")))</f>
+      <c r="U19" s="23" t="str">
+        <f aca="false">IF($O19=0,"No Order Needed",IF($S19&lt;=$B$8,"Sea",IF($T19&lt;=$B$8,"Air — Expedite","Air — Still At Risk")))</f>
         <v>Air — Expedite</v>
       </c>
-      <c r="U18" s="16" t="n">
-        <f aca="false">IF($N18=0,"N/A",$B$4-IF($T18="Sea",$R18,$S18)*7)</f>
+      <c r="V19" s="17" t="n">
+        <f aca="false">IF($O19=0,"N/A",$B$4-IF($U19="Sea",$S19,$T19)*7)</f>
         <v>46258</v>
       </c>
-      <c r="V18" s="22" t="str">
-        <f aca="false">IF($N18=0,"No Restock Needed",IF($T18="Sea","On Track",IF($T18="Air — Expedite","Expedite Required","Critical — May Miss Launch")))</f>
+      <c r="W19" s="23" t="str">
+        <f aca="false">IF($O19=0,"No Restock Needed",IF($U19="Sea","On Track",IF($U19="Air — Expedite","Expedite Required","Critical — May Miss Launch")))</f>
         <v>Expedite Required</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="B19" s="25"/>
-      <c r="C19" s="25"/>
-      <c r="D19" s="25"/>
-      <c r="E19" s="25"/>
-      <c r="F19" s="25"/>
-      <c r="G19" s="25"/>
-      <c r="H19" s="25"/>
-      <c r="I19" s="25"/>
-      <c r="J19" s="25"/>
-      <c r="K19" s="25"/>
-      <c r="L19" s="25"/>
-      <c r="M19" s="25"/>
-      <c r="N19" s="20" t="n">
-        <f aca="false">SUM(N10:N18)</f>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" s="27"/>
+      <c r="C20" s="27"/>
+      <c r="D20" s="27"/>
+      <c r="E20" s="27"/>
+      <c r="F20" s="27"/>
+      <c r="G20" s="27"/>
+      <c r="H20" s="27"/>
+      <c r="I20" s="27"/>
+      <c r="J20" s="27"/>
+      <c r="K20" s="21" t="n">
+        <f aca="false">SUM(K11:K19)</f>
+        <v>0</v>
+      </c>
+      <c r="L20" s="27"/>
+      <c r="M20" s="27"/>
+      <c r="N20" s="27"/>
+      <c r="O20" s="21" t="n">
+        <f aca="false">SUM(O11:O19)</f>
         <v>4600</v>
       </c>
-      <c r="O19" s="25"/>
-      <c r="P19" s="25"/>
-      <c r="Q19" s="25"/>
-      <c r="R19" s="25"/>
-      <c r="S19" s="25"/>
-      <c r="T19" s="25"/>
-      <c r="U19" s="25"/>
-      <c r="V19" s="25"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="B22" s="11"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="11"/>
-      <c r="H22" s="11"/>
-      <c r="I22" s="11"/>
-      <c r="J22" s="11"/>
-      <c r="K22" s="11"/>
-      <c r="L22" s="11"/>
-      <c r="M22" s="11"/>
-      <c r="N22" s="11"/>
-      <c r="O22" s="11"/>
-      <c r="P22" s="11"/>
-      <c r="Q22" s="11"/>
-      <c r="R22" s="11"/>
-      <c r="S22" s="11"/>
-      <c r="T22" s="11"/>
-      <c r="U22" s="11"/>
-      <c r="V22" s="11"/>
+      <c r="P20" s="27"/>
+      <c r="Q20" s="27"/>
+      <c r="R20" s="27"/>
+      <c r="S20" s="27"/>
+      <c r="T20" s="27"/>
+      <c r="U20" s="27"/>
+      <c r="V20" s="27"/>
+      <c r="W20" s="27"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="10" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -2561,10 +2652,11 @@
       <c r="T23" s="11"/>
       <c r="U23" s="11"/>
       <c r="V23" s="11"/>
+      <c r="W23" s="11"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -2587,10 +2679,11 @@
       <c r="T24" s="11"/>
       <c r="U24" s="11"/>
       <c r="V24" s="11"/>
+      <c r="W24" s="11"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -2613,10 +2706,11 @@
       <c r="T25" s="11"/>
       <c r="U25" s="11"/>
       <c r="V25" s="11"/>
+      <c r="W25" s="11"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -2639,10 +2733,11 @@
       <c r="T26" s="11"/>
       <c r="U26" s="11"/>
       <c r="V26" s="11"/>
+      <c r="W26" s="11"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -2665,37 +2760,98 @@
       <c r="T27" s="11"/>
       <c r="U27" s="11"/>
       <c r="V27" s="11"/>
+      <c r="W27" s="11"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="11"/>
+      <c r="J28" s="11"/>
+      <c r="K28" s="11"/>
+      <c r="L28" s="11"/>
+      <c r="M28" s="11"/>
+      <c r="N28" s="11"/>
+      <c r="O28" s="11"/>
+      <c r="P28" s="11"/>
+      <c r="Q28" s="11"/>
+      <c r="R28" s="11"/>
+      <c r="S28" s="11"/>
+      <c r="T28" s="11"/>
+      <c r="U28" s="11"/>
+      <c r="V28" s="11"/>
+      <c r="W28" s="11"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="11"/>
+      <c r="J29" s="11"/>
+      <c r="K29" s="11"/>
+      <c r="L29" s="11"/>
+      <c r="M29" s="11"/>
+      <c r="N29" s="11"/>
+      <c r="O29" s="11"/>
+      <c r="P29" s="11"/>
+      <c r="Q29" s="11"/>
+      <c r="R29" s="11"/>
+      <c r="S29" s="11"/>
+      <c r="T29" s="11"/>
+      <c r="U29" s="11"/>
+      <c r="V29" s="11"/>
+      <c r="W29" s="11"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A1:V1"/>
-    <mergeCell ref="A22:V22"/>
-    <mergeCell ref="A23:V23"/>
-    <mergeCell ref="A24:V24"/>
-    <mergeCell ref="A25:V25"/>
-    <mergeCell ref="A26:V26"/>
-    <mergeCell ref="A27:V27"/>
+  <mergeCells count="8">
+    <mergeCell ref="A1:W1"/>
+    <mergeCell ref="A23:W23"/>
+    <mergeCell ref="A24:W24"/>
+    <mergeCell ref="A25:W25"/>
+    <mergeCell ref="A26:W26"/>
+    <mergeCell ref="A27:W27"/>
+    <mergeCell ref="A28:W28"/>
+    <mergeCell ref="A29:W29"/>
   </mergeCells>
-  <conditionalFormatting sqref="I10:I18">
-    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+  <conditionalFormatting sqref="I11:I19">
+    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>"High Risk"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>"Medium Risk"</formula>
     </cfRule>
     <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>"Low Risk"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V10:V18">
+  <conditionalFormatting sqref="W11:W19">
     <cfRule type="cellIs" priority="5" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>"On Track"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="6" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="cellIs" priority="6" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>"Expedite Required"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="7" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="cellIs" priority="7" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>"Critical — May Miss Launch"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K11:K19">
+    <cfRule type="cellIs" priority="8" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2733,7 +2889,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2749,7 +2905,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -2764,351 +2920,351 @@
       <c r="L3" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="F5" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="G5" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="H5" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="I5" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="J5" s="18" t="s">
+      <c r="A5" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="K5" s="18" t="s">
+      <c r="B5" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="L5" s="18" t="s">
+      <c r="F5" s="19" t="s">
         <v>59</v>
       </c>
+      <c r="G5" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="H5" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="I5" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="J5" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="K5" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="L5" s="19" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="19" t="str">
+      <c r="A6" s="20" t="str">
         <f aca="false">'Purchase Orders'!A6</f>
         <v>PO-410</v>
       </c>
-      <c r="B6" s="19" t="str">
+      <c r="B6" s="20" t="str">
         <f aca="false">'Purchase Orders'!B6</f>
         <v>Factory A</v>
       </c>
-      <c r="C6" s="19" t="str">
+      <c r="C6" s="20" t="str">
         <f aca="false">'Purchase Orders'!D6</f>
         <v>HN-RB-300</v>
       </c>
-      <c r="D6" s="19" t="str">
+      <c r="D6" s="20" t="str">
         <f aca="false">'Purchase Orders'!E6</f>
         <v>Recovery Balm 300ml</v>
       </c>
-      <c r="E6" s="20" t="n">
+      <c r="E6" s="21" t="n">
         <f aca="false">'Purchase Orders'!F6</f>
         <v>500</v>
       </c>
-      <c r="F6" s="19" t="str">
+      <c r="F6" s="20" t="str">
         <f aca="false">'Purchase Orders'!G6</f>
         <v>In production — on track</v>
       </c>
-      <c r="G6" s="22" t="str">
+      <c r="G6" s="23" t="str">
         <f aca="false">'Purchase Orders'!O6</f>
         <v>Low Risk</v>
       </c>
-      <c r="H6" s="22" t="str">
+      <c r="H6" s="23" t="str">
         <f aca="false">'Purchase Orders'!H6</f>
         <v>HK</v>
       </c>
-      <c r="I6" s="22" t="str">
+      <c r="I6" s="23" t="str">
         <f aca="false">IF(IFERROR(INDEX('Inventory &amp; Coverage'!$M$8:$M$16,MATCH($C6,'Inventory &amp; Coverage'!$A$8:$A$16,0)),"")="High Risk","Yes — UK Critical SKU","No")</f>
         <v>Yes — UK Critical SKU</v>
       </c>
-      <c r="J6" s="22" t="str">
+      <c r="J6" s="23" t="str">
         <f aca="false">IF($G6="Low Risk","No","Yes")</f>
         <v>No</v>
       </c>
-      <c r="K6" s="19" t="str">
+      <c r="K6" s="20" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH("delayed",$F6)),"Contact factory for a revised production timeline. If this is a UK-critical SKU, evaluate air freight or a backup factory to recover schedule.",IF(ISNUMBER(SEARCH("Unconfirmed",$F6)),"Escalate to factory immediately — no confirmation received. Confirm the production slot or reallocate the PO to a backup factory.",IF(ISNUMBER(SEARCH("Completed",$F6)),"Issue shipping instructions now. Goods are finished and awaiting dispatch — assign a destination and carrier immediately to avoid storage delays.",IF(ISNUMBER(SEARCH("on track",$F6)),"No follow-up needed — monitor for on-time delivery.","Review PO status manually."))))</f>
         <v>No follow-up needed — monitor for on-time delivery.</v>
       </c>
-      <c r="L6" s="22" t="str">
+      <c r="L6" s="23" t="str">
         <f aca="false">IF(AND($G6&lt;&gt;"Low Risk",$I6="Yes — UK Critical SKU"),"Urgent — UK Launch Impact",IF($G6="High Risk","High",IF($G6="Medium Risk","Medium","Low")))</f>
         <v>Low</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="str">
+      <c r="A7" s="20" t="str">
         <f aca="false">'Purchase Orders'!A7</f>
         <v>PO-411</v>
       </c>
-      <c r="B7" s="19" t="str">
+      <c r="B7" s="20" t="str">
         <f aca="false">'Purchase Orders'!B7</f>
         <v>Factory A</v>
       </c>
-      <c r="C7" s="19" t="str">
+      <c r="C7" s="20" t="str">
         <f aca="false">'Purchase Orders'!D7</f>
         <v>HN-NC-075</v>
       </c>
-      <c r="D7" s="19" t="str">
+      <c r="D7" s="20" t="str">
         <f aca="false">'Purchase Orders'!E7</f>
         <v>Night Cream 75ml</v>
       </c>
-      <c r="E7" s="20" t="n">
+      <c r="E7" s="21" t="n">
         <f aca="false">'Purchase Orders'!F7</f>
         <v>500</v>
       </c>
-      <c r="F7" s="19" t="str">
+      <c r="F7" s="20" t="str">
         <f aca="false">'Purchase Orders'!G7</f>
         <v>In production — on track</v>
       </c>
-      <c r="G7" s="22" t="str">
+      <c r="G7" s="23" t="str">
         <f aca="false">'Purchase Orders'!O7</f>
         <v>Low Risk</v>
       </c>
-      <c r="H7" s="22" t="str">
+      <c r="H7" s="23" t="str">
         <f aca="false">'Purchase Orders'!H7</f>
         <v>US</v>
       </c>
-      <c r="I7" s="22" t="str">
+      <c r="I7" s="23" t="str">
         <f aca="false">IF(IFERROR(INDEX('Inventory &amp; Coverage'!$M$8:$M$16,MATCH($C7,'Inventory &amp; Coverage'!$A$8:$A$16,0)),"")="High Risk","Yes — UK Critical SKU","No")</f>
         <v>Yes — UK Critical SKU</v>
       </c>
-      <c r="J7" s="22" t="str">
+      <c r="J7" s="23" t="str">
         <f aca="false">IF($G7="Low Risk","No","Yes")</f>
         <v>No</v>
       </c>
-      <c r="K7" s="19" t="str">
+      <c r="K7" s="20" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH("delayed",$F7)),"Contact factory for a revised production timeline. If this is a UK-critical SKU, evaluate air freight or a backup factory to recover schedule.",IF(ISNUMBER(SEARCH("Unconfirmed",$F7)),"Escalate to factory immediately — no confirmation received. Confirm the production slot or reallocate the PO to a backup factory.",IF(ISNUMBER(SEARCH("Completed",$F7)),"Issue shipping instructions now. Goods are finished and awaiting dispatch — assign a destination and carrier immediately to avoid storage delays.",IF(ISNUMBER(SEARCH("on track",$F7)),"No follow-up needed — monitor for on-time delivery.","Review PO status manually."))))</f>
         <v>No follow-up needed — monitor for on-time delivery.</v>
       </c>
-      <c r="L7" s="22" t="str">
+      <c r="L7" s="23" t="str">
         <f aca="false">IF(AND($G7&lt;&gt;"Low Risk",$I7="Yes — UK Critical SKU"),"Urgent — UK Launch Impact",IF($G7="High Risk","High",IF($G7="Medium Risk","Medium","Low")))</f>
         <v>Low</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="str">
+      <c r="A8" s="20" t="str">
         <f aca="false">'Purchase Orders'!A8</f>
         <v>PO-412</v>
       </c>
-      <c r="B8" s="19" t="str">
+      <c r="B8" s="20" t="str">
         <f aca="false">'Purchase Orders'!B8</f>
         <v>Factory C</v>
       </c>
-      <c r="C8" s="19" t="str">
+      <c r="C8" s="20" t="str">
         <f aca="false">'Purchase Orders'!D8</f>
         <v>HN-HM-100</v>
       </c>
-      <c r="D8" s="19" t="str">
+      <c r="D8" s="20" t="str">
         <f aca="false">'Purchase Orders'!E8</f>
         <v>Hair Mask 100ml</v>
       </c>
-      <c r="E8" s="20" t="n">
+      <c r="E8" s="21" t="n">
         <f aca="false">'Purchase Orders'!F8</f>
         <v>300</v>
       </c>
-      <c r="F8" s="19" t="str">
+      <c r="F8" s="20" t="str">
         <f aca="false">'Purchase Orders'!G8</f>
         <v>Production delayed — raw material shortage</v>
       </c>
-      <c r="G8" s="22" t="str">
+      <c r="G8" s="23" t="str">
         <f aca="false">'Purchase Orders'!O8</f>
         <v>High Risk</v>
       </c>
-      <c r="H8" s="22" t="str">
+      <c r="H8" s="23" t="str">
         <f aca="false">'Purchase Orders'!H8</f>
         <v>Unknown</v>
       </c>
-      <c r="I8" s="22" t="str">
+      <c r="I8" s="23" t="str">
         <f aca="false">IF(IFERROR(INDEX('Inventory &amp; Coverage'!$M$8:$M$16,MATCH($C8,'Inventory &amp; Coverage'!$A$8:$A$16,0)),"")="High Risk","Yes — UK Critical SKU","No")</f>
         <v>Yes — UK Critical SKU</v>
       </c>
-      <c r="J8" s="22" t="str">
+      <c r="J8" s="23" t="str">
         <f aca="false">IF($G8="Low Risk","No","Yes")</f>
         <v>Yes</v>
       </c>
-      <c r="K8" s="19" t="str">
+      <c r="K8" s="20" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH("delayed",$F8)),"Contact factory for a revised production timeline. If this is a UK-critical SKU, evaluate air freight or a backup factory to recover schedule.",IF(ISNUMBER(SEARCH("Unconfirmed",$F8)),"Escalate to factory immediately — no confirmation received. Confirm the production slot or reallocate the PO to a backup factory.",IF(ISNUMBER(SEARCH("Completed",$F8)),"Issue shipping instructions now. Goods are finished and awaiting dispatch — assign a destination and carrier immediately to avoid storage delays.",IF(ISNUMBER(SEARCH("on track",$F8)),"No follow-up needed — monitor for on-time delivery.","Review PO status manually."))))</f>
         <v>Contact factory for a revised production timeline. If this is a UK-critical SKU, evaluate air freight or a backup factory to recover schedule.</v>
       </c>
-      <c r="L8" s="22" t="str">
+      <c r="L8" s="23" t="str">
         <f aca="false">IF(AND($G8&lt;&gt;"Low Risk",$I8="Yes — UK Critical SKU"),"Urgent — UK Launch Impact",IF($G8="High Risk","High",IF($G8="Medium Risk","Medium","Low")))</f>
         <v>Urgent — UK Launch Impact</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="str">
+      <c r="A9" s="20" t="str">
         <f aca="false">'Purchase Orders'!A9</f>
         <v>PO-413</v>
       </c>
-      <c r="B9" s="19" t="str">
+      <c r="B9" s="20" t="str">
         <f aca="false">'Purchase Orders'!B9</f>
         <v>Factory D</v>
       </c>
-      <c r="C9" s="19" t="str">
+      <c r="C9" s="20" t="str">
         <f aca="false">'Purchase Orders'!D9</f>
         <v>HN-LB-250</v>
       </c>
-      <c r="D9" s="19" t="str">
+      <c r="D9" s="20" t="str">
         <f aca="false">'Purchase Orders'!E9</f>
         <v>Lip Balm 3-Pack</v>
       </c>
-      <c r="E9" s="20" t="n">
+      <c r="E9" s="21" t="n">
         <f aca="false">'Purchase Orders'!F9</f>
         <v>1000</v>
       </c>
-      <c r="F9" s="19" t="str">
+      <c r="F9" s="20" t="str">
         <f aca="false">'Purchase Orders'!G9</f>
         <v>Completed — ready for pickup</v>
       </c>
-      <c r="G9" s="22" t="str">
+      <c r="G9" s="23" t="str">
         <f aca="false">'Purchase Orders'!O9</f>
         <v>Medium Risk</v>
       </c>
-      <c r="H9" s="22" t="str">
+      <c r="H9" s="23" t="str">
         <f aca="false">'Purchase Orders'!H9</f>
         <v>Unknown</v>
       </c>
-      <c r="I9" s="22" t="str">
+      <c r="I9" s="23" t="str">
         <f aca="false">IF(IFERROR(INDEX('Inventory &amp; Coverage'!$M$8:$M$16,MATCH($C9,'Inventory &amp; Coverage'!$A$8:$A$16,0)),"")="High Risk","Yes — UK Critical SKU","No")</f>
         <v>Yes — UK Critical SKU</v>
       </c>
-      <c r="J9" s="22" t="str">
+      <c r="J9" s="23" t="str">
         <f aca="false">IF($G9="Low Risk","No","Yes")</f>
         <v>Yes</v>
       </c>
-      <c r="K9" s="19" t="str">
+      <c r="K9" s="20" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH("delayed",$F9)),"Contact factory for a revised production timeline. If this is a UK-critical SKU, evaluate air freight or a backup factory to recover schedule.",IF(ISNUMBER(SEARCH("Unconfirmed",$F9)),"Escalate to factory immediately — no confirmation received. Confirm the production slot or reallocate the PO to a backup factory.",IF(ISNUMBER(SEARCH("Completed",$F9)),"Issue shipping instructions now. Goods are finished and awaiting dispatch — assign a destination and carrier immediately to avoid storage delays.",IF(ISNUMBER(SEARCH("on track",$F9)),"No follow-up needed — monitor for on-time delivery.","Review PO status manually."))))</f>
         <v>Issue shipping instructions now. Goods are finished and awaiting dispatch — assign a destination and carrier immediately to avoid storage delays.</v>
       </c>
-      <c r="L9" s="22" t="str">
+      <c r="L9" s="23" t="str">
         <f aca="false">IF(AND($G9&lt;&gt;"Low Risk",$I9="Yes — UK Critical SKU"),"Urgent — UK Launch Impact",IF($G9="High Risk","High",IF($G9="Medium Risk","Medium","Low")))</f>
         <v>Urgent — UK Launch Impact</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="str">
+      <c r="A10" s="20" t="str">
         <f aca="false">'Purchase Orders'!A10</f>
         <v>PO-414</v>
       </c>
-      <c r="B10" s="19" t="str">
+      <c r="B10" s="20" t="str">
         <f aca="false">'Purchase Orders'!B10</f>
         <v>Factory E</v>
       </c>
-      <c r="C10" s="19" t="str">
+      <c r="C10" s="20" t="str">
         <f aca="false">'Purchase Orders'!D10</f>
         <v>HN-EO-030</v>
       </c>
-      <c r="D10" s="19" t="str">
+      <c r="D10" s="20" t="str">
         <f aca="false">'Purchase Orders'!E10</f>
         <v>Essential Oil Blend 30ml</v>
       </c>
-      <c r="E10" s="20" t="n">
+      <c r="E10" s="21" t="n">
         <f aca="false">'Purchase Orders'!F10</f>
         <v>200</v>
       </c>
-      <c r="F10" s="19" t="str">
+      <c r="F10" s="20" t="str">
         <f aca="false">'Purchase Orders'!G10</f>
         <v>Unconfirmed — awaiting factory response (4 days)</v>
       </c>
-      <c r="G10" s="22" t="str">
+      <c r="G10" s="23" t="str">
         <f aca="false">'Purchase Orders'!O10</f>
         <v>High Risk</v>
       </c>
-      <c r="H10" s="22" t="str">
+      <c r="H10" s="23" t="str">
         <f aca="false">'Purchase Orders'!H10</f>
         <v>Unknown</v>
       </c>
-      <c r="I10" s="22" t="str">
+      <c r="I10" s="23" t="str">
         <f aca="false">IF(IFERROR(INDEX('Inventory &amp; Coverage'!$M$8:$M$16,MATCH($C10,'Inventory &amp; Coverage'!$A$8:$A$16,0)),"")="High Risk","Yes — UK Critical SKU","No")</f>
         <v>Yes — UK Critical SKU</v>
       </c>
-      <c r="J10" s="22" t="str">
+      <c r="J10" s="23" t="str">
         <f aca="false">IF($G10="Low Risk","No","Yes")</f>
         <v>Yes</v>
       </c>
-      <c r="K10" s="19" t="str">
+      <c r="K10" s="20" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH("delayed",$F10)),"Contact factory for a revised production timeline. If this is a UK-critical SKU, evaluate air freight or a backup factory to recover schedule.",IF(ISNUMBER(SEARCH("Unconfirmed",$F10)),"Escalate to factory immediately — no confirmation received. Confirm the production slot or reallocate the PO to a backup factory.",IF(ISNUMBER(SEARCH("Completed",$F10)),"Issue shipping instructions now. Goods are finished and awaiting dispatch — assign a destination and carrier immediately to avoid storage delays.",IF(ISNUMBER(SEARCH("on track",$F10)),"No follow-up needed — monitor for on-time delivery.","Review PO status manually."))))</f>
         <v>Escalate to factory immediately — no confirmation received. Confirm the production slot or reallocate the PO to a backup factory.</v>
       </c>
-      <c r="L10" s="22" t="str">
+      <c r="L10" s="23" t="str">
         <f aca="false">IF(AND($G10&lt;&gt;"Low Risk",$I10="Yes — UK Critical SKU"),"Urgent — UK Launch Impact",IF($G10="High Risk","High",IF($G10="Medium Risk","Medium","Low")))</f>
         <v>Urgent — UK Launch Impact</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="str">
+      <c r="A11" s="20" t="str">
         <f aca="false">'Purchase Orders'!A11</f>
         <v>PO-415</v>
       </c>
-      <c r="B11" s="19" t="str">
+      <c r="B11" s="20" t="str">
         <f aca="false">'Purchase Orders'!B11</f>
         <v>Factory F</v>
       </c>
-      <c r="C11" s="19" t="str">
+      <c r="C11" s="20" t="str">
         <f aca="false">'Purchase Orders'!D11</f>
         <v>HN-BC-400</v>
       </c>
-      <c r="D11" s="19" t="str">
+      <c r="D11" s="20" t="str">
         <f aca="false">'Purchase Orders'!E11</f>
         <v>Bath Crystals 400g</v>
       </c>
-      <c r="E11" s="20" t="n">
+      <c r="E11" s="21" t="n">
         <f aca="false">'Purchase Orders'!F11</f>
         <v>500</v>
       </c>
-      <c r="F11" s="19" t="str">
+      <c r="F11" s="20" t="str">
         <f aca="false">'Purchase Orders'!G11</f>
         <v>In production — on track</v>
       </c>
-      <c r="G11" s="22" t="str">
+      <c r="G11" s="23" t="str">
         <f aca="false">'Purchase Orders'!O11</f>
         <v>Low Risk</v>
       </c>
-      <c r="H11" s="22" t="str">
+      <c r="H11" s="23" t="str">
         <f aca="false">'Purchase Orders'!H11</f>
         <v>US</v>
       </c>
-      <c r="I11" s="22" t="str">
+      <c r="I11" s="23" t="str">
         <f aca="false">IF(IFERROR(INDEX('Inventory &amp; Coverage'!$M$8:$M$16,MATCH($C11,'Inventory &amp; Coverage'!$A$8:$A$16,0)),"")="High Risk","Yes — UK Critical SKU","No")</f>
         <v>Yes — UK Critical SKU</v>
       </c>
-      <c r="J11" s="22" t="str">
+      <c r="J11" s="23" t="str">
         <f aca="false">IF($G11="Low Risk","No","Yes")</f>
         <v>No</v>
       </c>
-      <c r="K11" s="19" t="str">
+      <c r="K11" s="20" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH("delayed",$F11)),"Contact factory for a revised production timeline. If this is a UK-critical SKU, evaluate air freight or a backup factory to recover schedule.",IF(ISNUMBER(SEARCH("Unconfirmed",$F11)),"Escalate to factory immediately — no confirmation received. Confirm the production slot or reallocate the PO to a backup factory.",IF(ISNUMBER(SEARCH("Completed",$F11)),"Issue shipping instructions now. Goods are finished and awaiting dispatch — assign a destination and carrier immediately to avoid storage delays.",IF(ISNUMBER(SEARCH("on track",$F11)),"No follow-up needed — monitor for on-time delivery.","Review PO status manually."))))</f>
         <v>No follow-up needed — monitor for on-time delivery.</v>
       </c>
-      <c r="L11" s="22" t="str">
+      <c r="L11" s="23" t="str">
         <f aca="false">IF(AND($G11&lt;&gt;"Low Risk",$I11="Yes — UK Critical SKU"),"Urgent — UK Launch Impact",IF($G11="High Risk","High",IF($G11="Medium Risk","Medium","Low")))</f>
         <v>Low</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -3124,7 +3280,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -3140,7 +3296,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -3156,7 +3312,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -3180,10 +3336,10 @@
     <mergeCell ref="A17:L17"/>
   </mergeCells>
   <conditionalFormatting sqref="G6:G11">
-    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>"High Risk"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>"Medium Risk"</formula>
     </cfRule>
     <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
@@ -3191,7 +3347,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J6:J11">
-    <cfRule type="cellIs" priority="5" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="cellIs" priority="5" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>"Yes"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3236,7 +3392,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3256,7 +3412,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -3275,428 +3431,428 @@
       <c r="P3" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="G5" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="H5" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="I5" s="18" t="s">
-        <v>66</v>
-      </c>
-      <c r="J5" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="K5" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="L5" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="M5" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="N5" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="O5" s="18" t="s">
+      <c r="A5" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="G5" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="H5" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="I5" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="P5" s="18" t="s">
+      <c r="J5" s="19" t="s">
         <v>73</v>
       </c>
+      <c r="K5" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="L5" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="M5" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="N5" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="O5" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="P5" s="19" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="26" t="s">
-        <v>74</v>
-      </c>
-      <c r="B6" s="26" t="s">
-        <v>75</v>
-      </c>
-      <c r="C6" s="19" t="str">
+      <c r="A6" s="28" t="s">
+        <v>80</v>
+      </c>
+      <c r="B6" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="C6" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$B$22:$B$27,MATCH(B6,'Reference Data'!$A$22:$A$27,0)),"N/A")</f>
         <v>Shenzhen</v>
       </c>
-      <c r="D6" s="26" t="s">
-        <v>76</v>
-      </c>
-      <c r="E6" s="19" t="str">
+      <c r="D6" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="E6" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$B$10:$B$18,MATCH(D6,'Reference Data'!$A$10:$A$18,0)),"N/A")</f>
         <v>Recovery Balm 300ml</v>
       </c>
-      <c r="F6" s="27" t="n">
+      <c r="F6" s="29" t="n">
         <v>500</v>
       </c>
-      <c r="G6" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="H6" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="I6" s="28" t="s">
-        <v>79</v>
-      </c>
-      <c r="J6" s="26" t="s">
-        <v>80</v>
-      </c>
-      <c r="K6" s="29" t="n">
+      <c r="G6" s="28" t="s">
+        <v>83</v>
+      </c>
+      <c r="H6" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="I6" s="30" t="s">
+        <v>85</v>
+      </c>
+      <c r="J6" s="28" t="s">
+        <v>86</v>
+      </c>
+      <c r="K6" s="31" t="n">
         <v>3.5</v>
       </c>
-      <c r="L6" s="30" t="n">
+      <c r="L6" s="32" t="n">
         <f aca="false">IFERROR(INDEX('Reference Data'!$C$31:$C$45,MATCH($C6&amp;"|"&amp;$H6,'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
         <v>0.285714285714286</v>
       </c>
-      <c r="M6" s="30" t="n">
+      <c r="M6" s="32" t="n">
         <f aca="false">IFERROR(INDEX('Reference Data'!$E$31:$E$45,MATCH($C6&amp;"|"&amp;$H6,'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
         <v>0.142857142857143</v>
       </c>
-      <c r="N6" s="30" t="n">
+      <c r="N6" s="32" t="n">
         <f aca="false">IF(I6="Air",M6,IF(I6="Sea",L6,"N/A"))</f>
         <v>0.285714285714286</v>
       </c>
-      <c r="O6" s="22" t="str">
+      <c r="O6" s="23" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH("delayed",G6)),"High Risk",IF(ISNUMBER(SEARCH("Unconfirmed",G6)),"High Risk",IF(ISNUMBER(SEARCH("Completed",G6)),"Medium Risk",IF(ISNUMBER(SEARCH("on track",G6)),"Low Risk","Review"))))</f>
         <v>Low Risk</v>
       </c>
-      <c r="P6" s="22" t="str">
+      <c r="P6" s="23" t="str">
         <f aca="false">IF(H6="UK","Yes","No")</f>
         <v>No</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="28" t="s">
+        <v>87</v>
+      </c>
+      <c r="B7" s="28" t="s">
         <v>81</v>
       </c>
-      <c r="B7" s="26" t="s">
-        <v>75</v>
-      </c>
-      <c r="C7" s="19" t="str">
+      <c r="C7" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$B$22:$B$27,MATCH(B7,'Reference Data'!$A$22:$A$27,0)),"N/A")</f>
         <v>Shenzhen</v>
       </c>
-      <c r="D7" s="26" t="s">
-        <v>82</v>
-      </c>
-      <c r="E7" s="19" t="str">
+      <c r="D7" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="E7" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$B$10:$B$18,MATCH(D7,'Reference Data'!$A$10:$A$18,0)),"N/A")</f>
         <v>Night Cream 75ml</v>
       </c>
-      <c r="F7" s="27" t="n">
+      <c r="F7" s="29" t="n">
         <v>500</v>
       </c>
-      <c r="G7" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="H7" s="28" t="s">
+      <c r="G7" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="I7" s="28" t="s">
-        <v>79</v>
-      </c>
-      <c r="J7" s="26" t="s">
-        <v>84</v>
-      </c>
-      <c r="K7" s="29" t="n">
+      <c r="H7" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="I7" s="30" t="s">
+        <v>85</v>
+      </c>
+      <c r="J7" s="28" t="s">
+        <v>90</v>
+      </c>
+      <c r="K7" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="L7" s="30" t="n">
+      <c r="L7" s="32" t="n">
         <f aca="false">IFERROR(INDEX('Reference Data'!$C$31:$C$45,MATCH($C7&amp;"|"&amp;$H7,'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
         <v>3</v>
       </c>
-      <c r="M7" s="30" t="n">
+      <c r="M7" s="32" t="n">
         <f aca="false">IFERROR(INDEX('Reference Data'!$E$31:$E$45,MATCH($C7&amp;"|"&amp;$H7,'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
         <v>0.714285714285714</v>
       </c>
-      <c r="N7" s="30" t="n">
+      <c r="N7" s="32" t="n">
         <f aca="false">IF(I7="Air",M7,IF(I7="Sea",L7,"N/A"))</f>
         <v>3</v>
       </c>
-      <c r="O7" s="22" t="str">
+      <c r="O7" s="23" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH("delayed",G7)),"High Risk",IF(ISNUMBER(SEARCH("Unconfirmed",G7)),"High Risk",IF(ISNUMBER(SEARCH("Completed",G7)),"Medium Risk",IF(ISNUMBER(SEARCH("on track",G7)),"Low Risk","Review"))))</f>
         <v>Low Risk</v>
       </c>
-      <c r="P7" s="22" t="str">
+      <c r="P7" s="23" t="str">
         <f aca="false">IF(H7="UK","Yes","No")</f>
         <v>No</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="26" t="s">
-        <v>85</v>
-      </c>
-      <c r="B8" s="26" t="s">
-        <v>86</v>
-      </c>
-      <c r="C8" s="19" t="str">
+      <c r="A8" s="28" t="s">
+        <v>91</v>
+      </c>
+      <c r="B8" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="C8" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$B$22:$B$27,MATCH(B8,'Reference Data'!$A$22:$A$27,0)),"N/A")</f>
         <v>Jakarta</v>
       </c>
-      <c r="D8" s="26" t="s">
-        <v>87</v>
-      </c>
-      <c r="E8" s="19" t="str">
+      <c r="D8" s="28" t="s">
+        <v>93</v>
+      </c>
+      <c r="E8" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$B$10:$B$18,MATCH(D8,'Reference Data'!$A$10:$A$18,0)),"N/A")</f>
         <v>Hair Mask 100ml</v>
       </c>
-      <c r="F8" s="27" t="n">
+      <c r="F8" s="29" t="n">
         <v>300</v>
       </c>
-      <c r="G8" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="H8" s="28" t="s">
-        <v>89</v>
-      </c>
-      <c r="I8" s="28" t="s">
-        <v>89</v>
-      </c>
-      <c r="J8" s="26" t="s">
-        <v>90</v>
-      </c>
-      <c r="K8" s="28" t="s">
-        <v>89</v>
-      </c>
-      <c r="L8" s="30" t="str">
+      <c r="G8" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="H8" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="I8" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="J8" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="K8" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="L8" s="32" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$C$31:$C$45,MATCH($C8&amp;"|"&amp;$H8,'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="M8" s="30" t="str">
+      <c r="M8" s="32" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$E$31:$E$45,MATCH($C8&amp;"|"&amp;$H8,'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="N8" s="30" t="str">
+      <c r="N8" s="32" t="str">
         <f aca="false">IF(I8="Air",M8,IF(I8="Sea",L8,"N/A"))</f>
         <v>N/A</v>
       </c>
-      <c r="O8" s="22" t="str">
+      <c r="O8" s="23" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH("delayed",G8)),"High Risk",IF(ISNUMBER(SEARCH("Unconfirmed",G8)),"High Risk",IF(ISNUMBER(SEARCH("Completed",G8)),"Medium Risk",IF(ISNUMBER(SEARCH("on track",G8)),"Low Risk","Review"))))</f>
         <v>High Risk</v>
       </c>
-      <c r="P8" s="22" t="str">
+      <c r="P8" s="23" t="str">
         <f aca="false">IF(H8="UK","Yes","No")</f>
         <v>No</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="26" t="s">
-        <v>91</v>
-      </c>
-      <c r="B9" s="26" t="s">
-        <v>92</v>
-      </c>
-      <c r="C9" s="19" t="str">
+      <c r="A9" s="28" t="s">
+        <v>97</v>
+      </c>
+      <c r="B9" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="C9" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$B$22:$B$27,MATCH(B9,'Reference Data'!$A$22:$A$27,0)),"N/A")</f>
         <v>Taipei</v>
       </c>
-      <c r="D9" s="26" t="s">
-        <v>93</v>
-      </c>
-      <c r="E9" s="19" t="str">
+      <c r="D9" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="E9" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$B$10:$B$18,MATCH(D9,'Reference Data'!$A$10:$A$18,0)),"N/A")</f>
         <v>Lip Balm 3-Pack</v>
       </c>
-      <c r="F9" s="27" t="n">
+      <c r="F9" s="29" t="n">
         <v>1000</v>
       </c>
-      <c r="G9" s="26" t="s">
-        <v>94</v>
-      </c>
-      <c r="H9" s="28" t="s">
-        <v>89</v>
-      </c>
-      <c r="I9" s="28" t="s">
-        <v>89</v>
-      </c>
-      <c r="J9" s="26" t="s">
+      <c r="G9" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="H9" s="30" t="s">
         <v>95</v>
       </c>
-      <c r="K9" s="28" t="s">
-        <v>89</v>
-      </c>
-      <c r="L9" s="30" t="str">
+      <c r="I9" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="J9" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="K9" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="L9" s="32" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$C$31:$C$45,MATCH($C9&amp;"|"&amp;$H9,'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="M9" s="30" t="str">
+      <c r="M9" s="32" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$E$31:$E$45,MATCH($C9&amp;"|"&amp;$H9,'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="N9" s="30" t="str">
+      <c r="N9" s="32" t="str">
         <f aca="false">IF(I9="Air",M9,IF(I9="Sea",L9,"N/A"))</f>
         <v>N/A</v>
       </c>
-      <c r="O9" s="22" t="str">
+      <c r="O9" s="23" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH("delayed",G9)),"High Risk",IF(ISNUMBER(SEARCH("Unconfirmed",G9)),"High Risk",IF(ISNUMBER(SEARCH("Completed",G9)),"Medium Risk",IF(ISNUMBER(SEARCH("on track",G9)),"Low Risk","Review"))))</f>
         <v>Medium Risk</v>
       </c>
-      <c r="P9" s="22" t="str">
+      <c r="P9" s="23" t="str">
         <f aca="false">IF(H9="UK","Yes","No")</f>
         <v>No</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="26" t="s">
-        <v>96</v>
-      </c>
-      <c r="B10" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="C10" s="19" t="str">
+      <c r="A10" s="28" t="s">
+        <v>102</v>
+      </c>
+      <c r="B10" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="C10" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$B$22:$B$27,MATCH(B10,'Reference Data'!$A$22:$A$27,0)),"N/A")</f>
         <v>Chiang Mai</v>
       </c>
-      <c r="D10" s="26" t="s">
-        <v>98</v>
-      </c>
-      <c r="E10" s="19" t="str">
+      <c r="D10" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="E10" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$B$10:$B$18,MATCH(D10,'Reference Data'!$A$10:$A$18,0)),"N/A")</f>
         <v>Essential Oil Blend 30ml</v>
       </c>
-      <c r="F10" s="27" t="n">
+      <c r="F10" s="29" t="n">
         <v>200</v>
       </c>
-      <c r="G10" s="26" t="s">
-        <v>99</v>
-      </c>
-      <c r="H10" s="28" t="s">
-        <v>89</v>
-      </c>
-      <c r="I10" s="28" t="s">
-        <v>89</v>
-      </c>
-      <c r="J10" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="K10" s="28" t="s">
-        <v>89</v>
-      </c>
-      <c r="L10" s="30" t="str">
+      <c r="G10" s="28" t="s">
+        <v>105</v>
+      </c>
+      <c r="H10" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="I10" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="J10" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="K10" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="L10" s="32" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$C$31:$C$45,MATCH($C10&amp;"|"&amp;$H10,'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="M10" s="30" t="str">
+      <c r="M10" s="32" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$E$31:$E$45,MATCH($C10&amp;"|"&amp;$H10,'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="N10" s="30" t="str">
+      <c r="N10" s="32" t="str">
         <f aca="false">IF(I10="Air",M10,IF(I10="Sea",L10,"N/A"))</f>
         <v>N/A</v>
       </c>
-      <c r="O10" s="22" t="str">
+      <c r="O10" s="23" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH("delayed",G10)),"High Risk",IF(ISNUMBER(SEARCH("Unconfirmed",G10)),"High Risk",IF(ISNUMBER(SEARCH("Completed",G10)),"Medium Risk",IF(ISNUMBER(SEARCH("on track",G10)),"Low Risk","Review"))))</f>
         <v>High Risk</v>
       </c>
-      <c r="P10" s="22" t="str">
+      <c r="P10" s="23" t="str">
         <f aca="false">IF(H10="UK","Yes","No")</f>
         <v>No</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="26" t="s">
-        <v>100</v>
-      </c>
-      <c r="B11" s="26" t="s">
-        <v>101</v>
-      </c>
-      <c r="C11" s="19" t="str">
+      <c r="A11" s="28" t="s">
+        <v>106</v>
+      </c>
+      <c r="B11" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="C11" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$B$22:$B$27,MATCH(B11,'Reference Data'!$A$22:$A$27,0)),"N/A")</f>
         <v>Ho Chi Minh City</v>
       </c>
-      <c r="D11" s="26" t="s">
-        <v>102</v>
-      </c>
-      <c r="E11" s="19" t="str">
+      <c r="D11" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="E11" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$B$10:$B$18,MATCH(D11,'Reference Data'!$A$10:$A$18,0)),"N/A")</f>
         <v>Bath Crystals 400g</v>
       </c>
-      <c r="F11" s="27" t="n">
+      <c r="F11" s="29" t="n">
         <v>500</v>
       </c>
-      <c r="G11" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="H11" s="28" t="s">
+      <c r="G11" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="I11" s="28" t="s">
-        <v>79</v>
-      </c>
-      <c r="J11" s="26" t="s">
-        <v>103</v>
-      </c>
-      <c r="K11" s="29" t="n">
+      <c r="H11" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="I11" s="30" t="s">
+        <v>85</v>
+      </c>
+      <c r="J11" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="K11" s="31" t="n">
         <v>6</v>
       </c>
-      <c r="L11" s="30" t="n">
+      <c r="L11" s="32" t="n">
         <f aca="false">IFERROR(INDEX('Reference Data'!$C$31:$C$45,MATCH($C11&amp;"|"&amp;$H11,'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
         <v>3.5</v>
       </c>
-      <c r="M11" s="30" t="n">
+      <c r="M11" s="32" t="n">
         <f aca="false">IFERROR(INDEX('Reference Data'!$E$31:$E$45,MATCH($C11&amp;"|"&amp;$H11,'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
         <v>0.714285714285714</v>
       </c>
-      <c r="N11" s="30" t="n">
+      <c r="N11" s="32" t="n">
         <f aca="false">IF(I11="Air",M11,IF(I11="Sea",L11,"N/A"))</f>
         <v>3.5</v>
       </c>
-      <c r="O11" s="22" t="str">
+      <c r="O11" s="23" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH("delayed",G11)),"High Risk",IF(ISNUMBER(SEARCH("Unconfirmed",G11)),"High Risk",IF(ISNUMBER(SEARCH("Completed",G11)),"Medium Risk",IF(ISNUMBER(SEARCH("on track",G11)),"Low Risk","Review"))))</f>
         <v>Low Risk</v>
       </c>
-      <c r="P11" s="22" t="str">
+      <c r="P11" s="23" t="str">
         <f aca="false">IF(H11="UK","Yes","No")</f>
         <v>No</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="B12" s="25"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="25"/>
-      <c r="F12" s="31" t="n">
+      <c r="A12" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" s="27"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="27"/>
+      <c r="F12" s="33" t="n">
         <f aca="false">SUM(F6:F11)</f>
         <v>3000</v>
       </c>
-      <c r="G12" s="25"/>
-      <c r="H12" s="25"/>
-      <c r="I12" s="25"/>
-      <c r="J12" s="25"/>
-      <c r="K12" s="25"/>
-      <c r="L12" s="25"/>
-      <c r="M12" s="25"/>
-      <c r="N12" s="25"/>
-      <c r="O12" s="25"/>
-      <c r="P12" s="25"/>
+      <c r="G12" s="27"/>
+      <c r="H12" s="27"/>
+      <c r="I12" s="27"/>
+      <c r="J12" s="27"/>
+      <c r="K12" s="27"/>
+      <c r="L12" s="27"/>
+      <c r="M12" s="27"/>
+      <c r="N12" s="27"/>
+      <c r="O12" s="27"/>
+      <c r="P12" s="27"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -3716,7 +3872,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -3736,7 +3892,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -3756,7 +3912,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -3784,10 +3940,10 @@
     <mergeCell ref="A18:P18"/>
   </mergeCells>
   <conditionalFormatting sqref="O6:O11">
-    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>"High Risk"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>"Medium Risk"</formula>
     </cfRule>
     <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
@@ -3831,7 +3987,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3850,12 +4006,12 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="B4" s="15" t="n">
         <v>4</v>
@@ -3863,620 +4019,620 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B5" s="15" t="n">
         <v>8</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="D7" s="18" t="s">
-        <v>114</v>
-      </c>
-      <c r="E7" s="18" t="s">
-        <v>115</v>
-      </c>
-      <c r="F7" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="G7" s="18" t="s">
-        <v>117</v>
-      </c>
-      <c r="H7" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="I7" s="18" t="s">
+      <c r="A7" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="J7" s="18" t="s">
+      <c r="C7" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="K7" s="18" t="s">
+      <c r="D7" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="L7" s="18" t="s">
+      <c r="E7" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="M7" s="18" t="s">
+      <c r="F7" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="N7" s="18" t="s">
+      <c r="G7" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="O7" s="18" t="s">
-        <v>26</v>
+      <c r="H7" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="I7" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="J7" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="K7" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="L7" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="M7" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="N7" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="O7" s="19" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="26" t="s">
-        <v>76</v>
-      </c>
-      <c r="B8" s="19" t="str">
+      <c r="A8" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="B8" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$B$10:$B$18,MATCH($A8,'Reference Data'!$A$10:$A$18,0)),"N/A")</f>
         <v>Recovery Balm 300ml</v>
       </c>
-      <c r="C8" s="19" t="str">
+      <c r="C8" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$C$10:$C$18,MATCH($A8,'Reference Data'!$A$10:$A$18,0)),"N/A")</f>
         <v>Body Care</v>
       </c>
-      <c r="D8" s="19" t="str">
+      <c r="D8" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$D$10:$D$18,MATCH($A8,'Reference Data'!$A$10:$A$18,0)),"N/A")</f>
         <v>Factory A</v>
       </c>
-      <c r="E8" s="27" t="n">
+      <c r="E8" s="29" t="n">
         <v>220</v>
       </c>
-      <c r="F8" s="27" t="n">
+      <c r="F8" s="29" t="n">
         <v>35</v>
       </c>
-      <c r="G8" s="27" t="n">
+      <c r="G8" s="29" t="n">
         <v>110</v>
       </c>
-      <c r="H8" s="20" t="n">
+      <c r="H8" s="21" t="n">
         <f aca="false">SUM(E8:G8)</f>
         <v>365</v>
       </c>
-      <c r="I8" s="27" t="n">
+      <c r="I8" s="29" t="n">
         <v>75</v>
       </c>
-      <c r="J8" s="21" t="n">
+      <c r="J8" s="22" t="n">
         <f aca="false">IFERROR(H8/I8,"N/A")</f>
         <v>4.86666666666667</v>
       </c>
-      <c r="K8" s="22" t="str">
+      <c r="K8" s="23" t="str">
         <f aca="false">IF(J8&lt;$B$4,"High Risk",IF(J8&lt;$B$5,"Medium Risk","Low Risk"))</f>
         <v>Medium Risk</v>
       </c>
-      <c r="L8" s="21" t="n">
+      <c r="L8" s="22" t="n">
         <f aca="false">IFERROR(F8/I8,"N/A")</f>
         <v>0.466666666666667</v>
       </c>
-      <c r="M8" s="22" t="str">
+      <c r="M8" s="23" t="str">
         <f aca="false">IF(L8&lt;$B$4,"High Risk",IF(L8&lt;$B$5,"Medium Risk","Low Risk"))</f>
         <v>High Risk</v>
       </c>
-      <c r="N8" s="20" t="n">
+      <c r="N8" s="21" t="n">
         <f aca="false">SUMIF('Purchase Orders'!$D$6:$D$11,$A8,'Purchase Orders'!$F$6:$F$11)</f>
         <v>500</v>
       </c>
-      <c r="O8" s="20" t="n">
+      <c r="O8" s="21" t="n">
         <f aca="false">SUMIFS('Purchase Orders'!$F$6:$F$11,'Purchase Orders'!$D$6:$D$11,$A8,'Purchase Orders'!$H$6:$H$11,"UK")</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="26" t="s">
-        <v>124</v>
-      </c>
-      <c r="B9" s="19" t="str">
+      <c r="A9" s="28" t="s">
+        <v>131</v>
+      </c>
+      <c r="B9" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$B$10:$B$18,MATCH($A9,'Reference Data'!$A$10:$A$18,0)),"N/A")</f>
         <v>Face Serum 50ml</v>
       </c>
-      <c r="C9" s="19" t="str">
+      <c r="C9" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$C$10:$C$18,MATCH($A9,'Reference Data'!$A$10:$A$18,0)),"N/A")</f>
         <v>Skincare</v>
       </c>
-      <c r="D9" s="19" t="str">
+      <c r="D9" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$D$10:$D$18,MATCH($A9,'Reference Data'!$A$10:$A$18,0)),"N/A")</f>
         <v>Factory A</v>
       </c>
-      <c r="E9" s="27" t="n">
+      <c r="E9" s="29" t="n">
         <v>150</v>
       </c>
-      <c r="F9" s="27" t="n">
+      <c r="F9" s="29" t="n">
         <v>20</v>
       </c>
-      <c r="G9" s="27" t="n">
+      <c r="G9" s="29" t="n">
         <v>75</v>
       </c>
-      <c r="H9" s="20" t="n">
+      <c r="H9" s="21" t="n">
         <f aca="false">SUM(E9:G9)</f>
         <v>245</v>
       </c>
-      <c r="I9" s="27" t="n">
+      <c r="I9" s="29" t="n">
         <v>45</v>
       </c>
-      <c r="J9" s="21" t="n">
+      <c r="J9" s="22" t="n">
         <f aca="false">IFERROR(H9/I9,"N/A")</f>
         <v>5.44444444444445</v>
       </c>
-      <c r="K9" s="22" t="str">
+      <c r="K9" s="23" t="str">
         <f aca="false">IF(J9&lt;$B$4,"High Risk",IF(J9&lt;$B$5,"Medium Risk","Low Risk"))</f>
         <v>Medium Risk</v>
       </c>
-      <c r="L9" s="21" t="n">
+      <c r="L9" s="22" t="n">
         <f aca="false">IFERROR(F9/I9,"N/A")</f>
         <v>0.444444444444444</v>
       </c>
-      <c r="M9" s="22" t="str">
+      <c r="M9" s="23" t="str">
         <f aca="false">IF(L9&lt;$B$4,"High Risk",IF(L9&lt;$B$5,"Medium Risk","Low Risk"))</f>
         <v>High Risk</v>
       </c>
-      <c r="N9" s="20" t="n">
+      <c r="N9" s="21" t="n">
         <f aca="false">SUMIF('Purchase Orders'!$D$6:$D$11,$A9,'Purchase Orders'!$F$6:$F$11)</f>
         <v>0</v>
       </c>
-      <c r="O9" s="20" t="n">
+      <c r="O9" s="21" t="n">
         <f aca="false">SUMIFS('Purchase Orders'!$F$6:$F$11,'Purchase Orders'!$D$6:$D$11,$A9,'Purchase Orders'!$H$6:$H$11,"UK")</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="26" t="s">
-        <v>125</v>
-      </c>
-      <c r="B10" s="19" t="str">
+      <c r="A10" s="28" t="s">
+        <v>132</v>
+      </c>
+      <c r="B10" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$B$10:$B$18,MATCH($A10,'Reference Data'!$A$10:$A$18,0)),"N/A")</f>
         <v>Body Wash 200ml</v>
       </c>
-      <c r="C10" s="19" t="str">
+      <c r="C10" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$C$10:$C$18,MATCH($A10,'Reference Data'!$A$10:$A$18,0)),"N/A")</f>
         <v>Body Care</v>
       </c>
-      <c r="D10" s="19" t="str">
+      <c r="D10" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$D$10:$D$18,MATCH($A10,'Reference Data'!$A$10:$A$18,0)),"N/A")</f>
         <v>Factory B</v>
       </c>
-      <c r="E10" s="27" t="n">
+      <c r="E10" s="29" t="n">
         <v>180</v>
       </c>
-      <c r="F10" s="27" t="n">
+      <c r="F10" s="29" t="n">
         <v>50</v>
       </c>
-      <c r="G10" s="27" t="n">
+      <c r="G10" s="29" t="n">
         <v>60</v>
       </c>
-      <c r="H10" s="20" t="n">
+      <c r="H10" s="21" t="n">
         <f aca="false">SUM(E10:G10)</f>
         <v>290</v>
       </c>
-      <c r="I10" s="27" t="n">
+      <c r="I10" s="29" t="n">
         <v>55</v>
       </c>
-      <c r="J10" s="21" t="n">
+      <c r="J10" s="22" t="n">
         <f aca="false">IFERROR(H10/I10,"N/A")</f>
         <v>5.27272727272727</v>
       </c>
-      <c r="K10" s="22" t="str">
+      <c r="K10" s="23" t="str">
         <f aca="false">IF(J10&lt;$B$4,"High Risk",IF(J10&lt;$B$5,"Medium Risk","Low Risk"))</f>
         <v>Medium Risk</v>
       </c>
-      <c r="L10" s="21" t="n">
+      <c r="L10" s="22" t="n">
         <f aca="false">IFERROR(F10/I10,"N/A")</f>
         <v>0.909090909090909</v>
       </c>
-      <c r="M10" s="22" t="str">
+      <c r="M10" s="23" t="str">
         <f aca="false">IF(L10&lt;$B$4,"High Risk",IF(L10&lt;$B$5,"Medium Risk","Low Risk"))</f>
         <v>High Risk</v>
       </c>
-      <c r="N10" s="20" t="n">
+      <c r="N10" s="21" t="n">
         <f aca="false">SUMIF('Purchase Orders'!$D$6:$D$11,$A10,'Purchase Orders'!$F$6:$F$11)</f>
         <v>0</v>
       </c>
-      <c r="O10" s="20" t="n">
+      <c r="O10" s="21" t="n">
         <f aca="false">SUMIFS('Purchase Orders'!$F$6:$F$11,'Purchase Orders'!$D$6:$D$11,$A10,'Purchase Orders'!$H$6:$H$11,"UK")</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="26" t="s">
-        <v>87</v>
-      </c>
-      <c r="B11" s="19" t="str">
+      <c r="A11" s="28" t="s">
+        <v>93</v>
+      </c>
+      <c r="B11" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$B$10:$B$18,MATCH($A11,'Reference Data'!$A$10:$A$18,0)),"N/A")</f>
         <v>Hair Mask 100ml</v>
       </c>
-      <c r="C11" s="19" t="str">
+      <c r="C11" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$C$10:$C$18,MATCH($A11,'Reference Data'!$A$10:$A$18,0)),"N/A")</f>
         <v>Hair Care</v>
       </c>
-      <c r="D11" s="19" t="str">
+      <c r="D11" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$D$10:$D$18,MATCH($A11,'Reference Data'!$A$10:$A$18,0)),"N/A")</f>
         <v>Factory C</v>
       </c>
-      <c r="E11" s="27" t="n">
+      <c r="E11" s="29" t="n">
         <v>90</v>
       </c>
-      <c r="F11" s="27" t="n">
+      <c r="F11" s="29" t="n">
         <v>25</v>
       </c>
-      <c r="G11" s="27" t="n">
+      <c r="G11" s="29" t="n">
         <v>45</v>
       </c>
-      <c r="H11" s="20" t="n">
+      <c r="H11" s="21" t="n">
         <f aca="false">SUM(E11:G11)</f>
         <v>160</v>
       </c>
-      <c r="I11" s="27" t="n">
+      <c r="I11" s="29" t="n">
         <v>30</v>
       </c>
-      <c r="J11" s="21" t="n">
+      <c r="J11" s="22" t="n">
         <f aca="false">IFERROR(H11/I11,"N/A")</f>
         <v>5.33333333333333</v>
       </c>
-      <c r="K11" s="22" t="str">
+      <c r="K11" s="23" t="str">
         <f aca="false">IF(J11&lt;$B$4,"High Risk",IF(J11&lt;$B$5,"Medium Risk","Low Risk"))</f>
         <v>Medium Risk</v>
       </c>
-      <c r="L11" s="21" t="n">
+      <c r="L11" s="22" t="n">
         <f aca="false">IFERROR(F11/I11,"N/A")</f>
         <v>0.833333333333333</v>
       </c>
-      <c r="M11" s="22" t="str">
+      <c r="M11" s="23" t="str">
         <f aca="false">IF(L11&lt;$B$4,"High Risk",IF(L11&lt;$B$5,"Medium Risk","Low Risk"))</f>
         <v>High Risk</v>
       </c>
-      <c r="N11" s="20" t="n">
+      <c r="N11" s="21" t="n">
         <f aca="false">SUMIF('Purchase Orders'!$D$6:$D$11,$A11,'Purchase Orders'!$F$6:$F$11)</f>
         <v>300</v>
       </c>
-      <c r="O11" s="20" t="n">
+      <c r="O11" s="21" t="n">
         <f aca="false">SUMIFS('Purchase Orders'!$F$6:$F$11,'Purchase Orders'!$D$6:$D$11,$A11,'Purchase Orders'!$H$6:$H$11,"UK")</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="26" t="s">
-        <v>93</v>
-      </c>
-      <c r="B12" s="19" t="str">
+      <c r="A12" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="B12" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$B$10:$B$18,MATCH($A12,'Reference Data'!$A$10:$A$18,0)),"N/A")</f>
         <v>Lip Balm 3-Pack</v>
       </c>
-      <c r="C12" s="19" t="str">
+      <c r="C12" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$C$10:$C$18,MATCH($A12,'Reference Data'!$A$10:$A$18,0)),"N/A")</f>
         <v>Skincare</v>
       </c>
-      <c r="D12" s="19" t="str">
+      <c r="D12" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$D$10:$D$18,MATCH($A12,'Reference Data'!$A$10:$A$18,0)),"N/A")</f>
         <v>Factory D</v>
       </c>
-      <c r="E12" s="27" t="n">
+      <c r="E12" s="29" t="n">
         <v>300</v>
       </c>
-      <c r="F12" s="27" t="n">
+      <c r="F12" s="29" t="n">
         <v>40</v>
       </c>
-      <c r="G12" s="27" t="n">
+      <c r="G12" s="29" t="n">
         <v>80</v>
       </c>
-      <c r="H12" s="20" t="n">
+      <c r="H12" s="21" t="n">
         <f aca="false">SUM(E12:G12)</f>
         <v>420</v>
       </c>
-      <c r="I12" s="27" t="n">
+      <c r="I12" s="29" t="n">
         <v>60</v>
       </c>
-      <c r="J12" s="21" t="n">
+      <c r="J12" s="22" t="n">
         <f aca="false">IFERROR(H12/I12,"N/A")</f>
         <v>7</v>
       </c>
-      <c r="K12" s="22" t="str">
+      <c r="K12" s="23" t="str">
         <f aca="false">IF(J12&lt;$B$4,"High Risk",IF(J12&lt;$B$5,"Medium Risk","Low Risk"))</f>
         <v>Medium Risk</v>
       </c>
-      <c r="L12" s="21" t="n">
+      <c r="L12" s="22" t="n">
         <f aca="false">IFERROR(F12/I12,"N/A")</f>
         <v>0.666666666666667</v>
       </c>
-      <c r="M12" s="22" t="str">
+      <c r="M12" s="23" t="str">
         <f aca="false">IF(L12&lt;$B$4,"High Risk",IF(L12&lt;$B$5,"Medium Risk","Low Risk"))</f>
         <v>High Risk</v>
       </c>
-      <c r="N12" s="20" t="n">
+      <c r="N12" s="21" t="n">
         <f aca="false">SUMIF('Purchase Orders'!$D$6:$D$11,$A12,'Purchase Orders'!$F$6:$F$11)</f>
         <v>1000</v>
       </c>
-      <c r="O12" s="20" t="n">
+      <c r="O12" s="21" t="n">
         <f aca="false">SUMIFS('Purchase Orders'!$F$6:$F$11,'Purchase Orders'!$D$6:$D$11,$A12,'Purchase Orders'!$H$6:$H$11,"UK")</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="26" t="s">
-        <v>126</v>
-      </c>
-      <c r="B13" s="19" t="str">
+      <c r="A13" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="B13" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$B$10:$B$18,MATCH($A13,'Reference Data'!$A$10:$A$18,0)),"N/A")</f>
         <v>Scalp Mist 150ml</v>
       </c>
-      <c r="C13" s="19" t="str">
+      <c r="C13" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$C$10:$C$18,MATCH($A13,'Reference Data'!$A$10:$A$18,0)),"N/A")</f>
         <v>Hair Care</v>
       </c>
-      <c r="D13" s="19" t="str">
+      <c r="D13" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$D$10:$D$18,MATCH($A13,'Reference Data'!$A$10:$A$18,0)),"N/A")</f>
         <v>Factory C</v>
       </c>
-      <c r="E13" s="27" t="n">
+      <c r="E13" s="29" t="n">
         <v>70</v>
       </c>
-      <c r="F13" s="27" t="n">
+      <c r="F13" s="29" t="n">
         <v>10</v>
       </c>
-      <c r="G13" s="27" t="n">
+      <c r="G13" s="29" t="n">
         <v>30</v>
       </c>
-      <c r="H13" s="20" t="n">
+      <c r="H13" s="21" t="n">
         <f aca="false">SUM(E13:G13)</f>
         <v>110</v>
       </c>
-      <c r="I13" s="27" t="n">
+      <c r="I13" s="29" t="n">
         <v>20</v>
       </c>
-      <c r="J13" s="21" t="n">
+      <c r="J13" s="22" t="n">
         <f aca="false">IFERROR(H13/I13,"N/A")</f>
         <v>5.5</v>
       </c>
-      <c r="K13" s="22" t="str">
+      <c r="K13" s="23" t="str">
         <f aca="false">IF(J13&lt;$B$4,"High Risk",IF(J13&lt;$B$5,"Medium Risk","Low Risk"))</f>
         <v>Medium Risk</v>
       </c>
-      <c r="L13" s="21" t="n">
+      <c r="L13" s="22" t="n">
         <f aca="false">IFERROR(F13/I13,"N/A")</f>
         <v>0.5</v>
       </c>
-      <c r="M13" s="22" t="str">
+      <c r="M13" s="23" t="str">
         <f aca="false">IF(L13&lt;$B$4,"High Risk",IF(L13&lt;$B$5,"Medium Risk","Low Risk"))</f>
         <v>High Risk</v>
       </c>
-      <c r="N13" s="20" t="n">
+      <c r="N13" s="21" t="n">
         <f aca="false">SUMIF('Purchase Orders'!$D$6:$D$11,$A13,'Purchase Orders'!$F$6:$F$11)</f>
         <v>0</v>
       </c>
-      <c r="O13" s="20" t="n">
+      <c r="O13" s="21" t="n">
         <f aca="false">SUMIFS('Purchase Orders'!$F$6:$F$11,'Purchase Orders'!$D$6:$D$11,$A13,'Purchase Orders'!$H$6:$H$11,"UK")</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="26" t="s">
-        <v>98</v>
-      </c>
-      <c r="B14" s="19" t="str">
+      <c r="A14" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="B14" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$B$10:$B$18,MATCH($A14,'Reference Data'!$A$10:$A$18,0)),"N/A")</f>
         <v>Essential Oil Blend 30ml</v>
       </c>
-      <c r="C14" s="19" t="str">
+      <c r="C14" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$C$10:$C$18,MATCH($A14,'Reference Data'!$A$10:$A$18,0)),"N/A")</f>
         <v>Wellness</v>
       </c>
-      <c r="D14" s="19" t="str">
+      <c r="D14" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$D$10:$D$18,MATCH($A14,'Reference Data'!$A$10:$A$18,0)),"N/A")</f>
         <v>Factory E</v>
       </c>
-      <c r="E14" s="27" t="n">
+      <c r="E14" s="29" t="n">
         <v>45</v>
       </c>
-      <c r="F14" s="27" t="n">
+      <c r="F14" s="29" t="n">
         <v>8</v>
       </c>
-      <c r="G14" s="27" t="n">
+      <c r="G14" s="29" t="n">
         <v>20</v>
       </c>
-      <c r="H14" s="20" t="n">
+      <c r="H14" s="21" t="n">
         <f aca="false">SUM(E14:G14)</f>
         <v>73</v>
       </c>
-      <c r="I14" s="27" t="n">
+      <c r="I14" s="29" t="n">
         <v>15</v>
       </c>
-      <c r="J14" s="21" t="n">
+      <c r="J14" s="22" t="n">
         <f aca="false">IFERROR(H14/I14,"N/A")</f>
         <v>4.86666666666667</v>
       </c>
-      <c r="K14" s="22" t="str">
+      <c r="K14" s="23" t="str">
         <f aca="false">IF(J14&lt;$B$4,"High Risk",IF(J14&lt;$B$5,"Medium Risk","Low Risk"))</f>
         <v>Medium Risk</v>
       </c>
-      <c r="L14" s="21" t="n">
+      <c r="L14" s="22" t="n">
         <f aca="false">IFERROR(F14/I14,"N/A")</f>
         <v>0.533333333333333</v>
       </c>
-      <c r="M14" s="22" t="str">
+      <c r="M14" s="23" t="str">
         <f aca="false">IF(L14&lt;$B$4,"High Risk",IF(L14&lt;$B$5,"Medium Risk","Low Risk"))</f>
         <v>High Risk</v>
       </c>
-      <c r="N14" s="20" t="n">
+      <c r="N14" s="21" t="n">
         <f aca="false">SUMIF('Purchase Orders'!$D$6:$D$11,$A14,'Purchase Orders'!$F$6:$F$11)</f>
         <v>200</v>
       </c>
-      <c r="O14" s="20" t="n">
+      <c r="O14" s="21" t="n">
         <f aca="false">SUMIFS('Purchase Orders'!$F$6:$F$11,'Purchase Orders'!$D$6:$D$11,$A14,'Purchase Orders'!$H$6:$H$11,"UK")</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="26" t="s">
-        <v>102</v>
-      </c>
-      <c r="B15" s="19" t="str">
+      <c r="A15" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="B15" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$B$10:$B$18,MATCH($A15,'Reference Data'!$A$10:$A$18,0)),"N/A")</f>
         <v>Bath Crystals 400g</v>
       </c>
-      <c r="C15" s="19" t="str">
+      <c r="C15" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$C$10:$C$18,MATCH($A15,'Reference Data'!$A$10:$A$18,0)),"N/A")</f>
         <v>Body Care</v>
       </c>
-      <c r="D15" s="19" t="str">
+      <c r="D15" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$D$10:$D$18,MATCH($A15,'Reference Data'!$A$10:$A$18,0)),"N/A")</f>
         <v>Factory F</v>
       </c>
-      <c r="E15" s="27" t="n">
+      <c r="E15" s="29" t="n">
         <v>60</v>
       </c>
-      <c r="F15" s="27" t="n">
+      <c r="F15" s="29" t="n">
         <v>15</v>
       </c>
-      <c r="G15" s="27" t="n">
+      <c r="G15" s="29" t="n">
         <v>25</v>
       </c>
-      <c r="H15" s="20" t="n">
+      <c r="H15" s="21" t="n">
         <f aca="false">SUM(E15:G15)</f>
         <v>100</v>
       </c>
-      <c r="I15" s="27" t="n">
+      <c r="I15" s="29" t="n">
         <v>25</v>
       </c>
-      <c r="J15" s="21" t="n">
+      <c r="J15" s="22" t="n">
         <f aca="false">IFERROR(H15/I15,"N/A")</f>
         <v>4</v>
       </c>
-      <c r="K15" s="22" t="str">
+      <c r="K15" s="23" t="str">
         <f aca="false">IF(J15&lt;$B$4,"High Risk",IF(J15&lt;$B$5,"Medium Risk","Low Risk"))</f>
         <v>Medium Risk</v>
       </c>
-      <c r="L15" s="21" t="n">
+      <c r="L15" s="22" t="n">
         <f aca="false">IFERROR(F15/I15,"N/A")</f>
         <v>0.6</v>
       </c>
-      <c r="M15" s="22" t="str">
+      <c r="M15" s="23" t="str">
         <f aca="false">IF(L15&lt;$B$4,"High Risk",IF(L15&lt;$B$5,"Medium Risk","Low Risk"))</f>
         <v>High Risk</v>
       </c>
-      <c r="N15" s="20" t="n">
+      <c r="N15" s="21" t="n">
         <f aca="false">SUMIF('Purchase Orders'!$D$6:$D$11,$A15,'Purchase Orders'!$F$6:$F$11)</f>
         <v>500</v>
       </c>
-      <c r="O15" s="20" t="n">
+      <c r="O15" s="21" t="n">
         <f aca="false">SUMIFS('Purchase Orders'!$F$6:$F$11,'Purchase Orders'!$D$6:$D$11,$A15,'Purchase Orders'!$H$6:$H$11,"UK")</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="26" t="s">
-        <v>82</v>
-      </c>
-      <c r="B16" s="19" t="str">
+      <c r="A16" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="B16" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$B$10:$B$18,MATCH($A16,'Reference Data'!$A$10:$A$18,0)),"N/A")</f>
         <v>Night Cream 75ml</v>
       </c>
-      <c r="C16" s="19" t="str">
+      <c r="C16" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$C$10:$C$18,MATCH($A16,'Reference Data'!$A$10:$A$18,0)),"N/A")</f>
         <v>Skincare</v>
       </c>
-      <c r="D16" s="19" t="str">
+      <c r="D16" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$D$10:$D$18,MATCH($A16,'Reference Data'!$A$10:$A$18,0)),"N/A")</f>
         <v>Factory A</v>
       </c>
-      <c r="E16" s="27" t="n">
+      <c r="E16" s="29" t="n">
         <v>130</v>
       </c>
-      <c r="F16" s="27" t="n">
+      <c r="F16" s="29" t="n">
         <v>18</v>
       </c>
-      <c r="G16" s="27" t="n">
+      <c r="G16" s="29" t="n">
         <v>55</v>
       </c>
-      <c r="H16" s="20" t="n">
+      <c r="H16" s="21" t="n">
         <f aca="false">SUM(E16:G16)</f>
         <v>203</v>
       </c>
-      <c r="I16" s="27" t="n">
+      <c r="I16" s="29" t="n">
         <v>40</v>
       </c>
-      <c r="J16" s="21" t="n">
+      <c r="J16" s="22" t="n">
         <f aca="false">IFERROR(H16/I16,"N/A")</f>
         <v>5.075</v>
       </c>
-      <c r="K16" s="22" t="str">
+      <c r="K16" s="23" t="str">
         <f aca="false">IF(J16&lt;$B$4,"High Risk",IF(J16&lt;$B$5,"Medium Risk","Low Risk"))</f>
         <v>Medium Risk</v>
       </c>
-      <c r="L16" s="21" t="n">
+      <c r="L16" s="22" t="n">
         <f aca="false">IFERROR(F16/I16,"N/A")</f>
         <v>0.45</v>
       </c>
-      <c r="M16" s="22" t="str">
+      <c r="M16" s="23" t="str">
         <f aca="false">IF(L16&lt;$B$4,"High Risk",IF(L16&lt;$B$5,"Medium Risk","Low Risk"))</f>
         <v>High Risk</v>
       </c>
-      <c r="N16" s="20" t="n">
+      <c r="N16" s="21" t="n">
         <f aca="false">SUMIF('Purchase Orders'!$D$6:$D$11,$A16,'Purchase Orders'!$F$6:$F$11)</f>
         <v>500</v>
       </c>
-      <c r="O16" s="20" t="n">
+      <c r="O16" s="21" t="n">
         <f aca="false">SUMIFS('Purchase Orders'!$F$6:$F$11,'Purchase Orders'!$D$6:$D$11,$A16,'Purchase Orders'!$H$6:$H$11,"UK")</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="B17" s="25"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="20" t="n">
+      <c r="A17" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" s="27"/>
+      <c r="C17" s="27"/>
+      <c r="D17" s="27"/>
+      <c r="E17" s="21" t="n">
         <f aca="false">SUM(E8:E16)</f>
         <v>1245</v>
       </c>
-      <c r="F17" s="20" t="n">
+      <c r="F17" s="21" t="n">
         <f aca="false">SUM(F8:F16)</f>
         <v>221</v>
       </c>
-      <c r="G17" s="20" t="n">
+      <c r="G17" s="21" t="n">
         <f aca="false">SUM(G8:G16)</f>
         <v>500</v>
       </c>
-      <c r="H17" s="20" t="n">
+      <c r="H17" s="21" t="n">
         <f aca="false">SUM(H8:H16)</f>
         <v>1966</v>
       </c>
-      <c r="I17" s="25"/>
-      <c r="J17" s="25"/>
-      <c r="K17" s="25"/>
-      <c r="L17" s="25"/>
-      <c r="M17" s="25"/>
-      <c r="N17" s="20" t="n">
+      <c r="I17" s="27"/>
+      <c r="J17" s="27"/>
+      <c r="K17" s="27"/>
+      <c r="L17" s="27"/>
+      <c r="M17" s="27"/>
+      <c r="N17" s="21" t="n">
         <f aca="false">SUM(N8:N16)</f>
         <v>3000</v>
       </c>
-      <c r="O17" s="20" t="n">
+      <c r="O17" s="21" t="n">
         <f aca="false">SUM(O8:O16)</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -4495,7 +4651,7 @@
     </row>
     <row r="21" customFormat="false" ht="22.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -4514,7 +4670,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -4533,7 +4689,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -4559,10 +4715,10 @@
     <mergeCell ref="A23:O23"/>
   </mergeCells>
   <conditionalFormatting sqref="K8:K16">
-    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>"High Risk"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>"Medium Risk"</formula>
     </cfRule>
     <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
@@ -4570,10 +4726,10 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M8:M16">
-    <cfRule type="cellIs" priority="5" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="cellIs" priority="5" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>"High Risk"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="6" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="cellIs" priority="6" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>"Medium Risk"</formula>
     </cfRule>
     <cfRule type="cellIs" priority="7" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
@@ -4610,7 +4766,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4622,7 +4778,7 @@
     </row>
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -4633,52 +4789,52 @@
       <c r="H3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18" t="s">
-        <v>133</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>135</v>
+      <c r="A4" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="26" t="s">
-        <v>83</v>
-      </c>
-      <c r="B5" s="26" t="s">
-        <v>136</v>
-      </c>
-      <c r="C5" s="26" t="s">
-        <v>137</v>
+      <c r="A5" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="B5" s="28" t="s">
+        <v>143</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="26" t="s">
-        <v>138</v>
-      </c>
-      <c r="B6" s="26" t="s">
-        <v>138</v>
-      </c>
-      <c r="C6" s="26" t="s">
-        <v>139</v>
+      <c r="A6" s="28" t="s">
+        <v>145</v>
+      </c>
+      <c r="B6" s="28" t="s">
+        <v>145</v>
+      </c>
+      <c r="C6" s="28" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="26" t="s">
-        <v>78</v>
-      </c>
-      <c r="B7" s="26" t="s">
-        <v>140</v>
-      </c>
-      <c r="C7" s="26" t="s">
-        <v>141</v>
+      <c r="A7" s="28" t="s">
+        <v>84</v>
+      </c>
+      <c r="B7" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="C7" s="28" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -4689,148 +4845,148 @@
       <c r="H8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="D9" s="18" t="s">
-        <v>143</v>
+      <c r="A9" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="26" t="s">
-        <v>76</v>
-      </c>
-      <c r="B10" s="26" t="s">
-        <v>144</v>
-      </c>
-      <c r="C10" s="26" t="s">
-        <v>145</v>
-      </c>
-      <c r="D10" s="26" t="s">
-        <v>75</v>
+      <c r="A10" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="B10" s="28" t="s">
+        <v>151</v>
+      </c>
+      <c r="C10" s="28" t="s">
+        <v>152</v>
+      </c>
+      <c r="D10" s="28" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="26" t="s">
-        <v>124</v>
-      </c>
-      <c r="B11" s="26" t="s">
-        <v>146</v>
-      </c>
-      <c r="C11" s="26" t="s">
-        <v>147</v>
-      </c>
-      <c r="D11" s="26" t="s">
-        <v>75</v>
+      <c r="A11" s="28" t="s">
+        <v>131</v>
+      </c>
+      <c r="B11" s="28" t="s">
+        <v>153</v>
+      </c>
+      <c r="C11" s="28" t="s">
+        <v>154</v>
+      </c>
+      <c r="D11" s="28" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="26" t="s">
-        <v>125</v>
-      </c>
-      <c r="B12" s="26" t="s">
-        <v>148</v>
-      </c>
-      <c r="C12" s="26" t="s">
-        <v>145</v>
-      </c>
-      <c r="D12" s="26" t="s">
-        <v>149</v>
+      <c r="A12" s="28" t="s">
+        <v>132</v>
+      </c>
+      <c r="B12" s="28" t="s">
+        <v>155</v>
+      </c>
+      <c r="C12" s="28" t="s">
+        <v>152</v>
+      </c>
+      <c r="D12" s="28" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="26" t="s">
-        <v>87</v>
-      </c>
-      <c r="B13" s="26" t="s">
-        <v>150</v>
-      </c>
-      <c r="C13" s="26" t="s">
-        <v>151</v>
-      </c>
-      <c r="D13" s="26" t="s">
-        <v>86</v>
+      <c r="A13" s="28" t="s">
+        <v>93</v>
+      </c>
+      <c r="B13" s="28" t="s">
+        <v>157</v>
+      </c>
+      <c r="C13" s="28" t="s">
+        <v>158</v>
+      </c>
+      <c r="D13" s="28" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="26" t="s">
-        <v>93</v>
-      </c>
-      <c r="B14" s="26" t="s">
+      <c r="A14" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="B14" s="28" t="s">
+        <v>159</v>
+      </c>
+      <c r="C14" s="28" t="s">
+        <v>154</v>
+      </c>
+      <c r="D14" s="28" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="B15" s="28" t="s">
+        <v>160</v>
+      </c>
+      <c r="C15" s="28" t="s">
+        <v>158</v>
+      </c>
+      <c r="D15" s="28" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="B16" s="28" t="s">
+        <v>161</v>
+      </c>
+      <c r="C16" s="28" t="s">
+        <v>162</v>
+      </c>
+      <c r="D16" s="28" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="B17" s="28" t="s">
+        <v>163</v>
+      </c>
+      <c r="C17" s="28" t="s">
         <v>152</v>
       </c>
-      <c r="C14" s="26" t="s">
-        <v>147</v>
-      </c>
-      <c r="D14" s="26" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="26" t="s">
-        <v>126</v>
-      </c>
-      <c r="B15" s="26" t="s">
-        <v>153</v>
-      </c>
-      <c r="C15" s="26" t="s">
-        <v>151</v>
-      </c>
-      <c r="D15" s="26" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="26" t="s">
-        <v>98</v>
-      </c>
-      <c r="B16" s="26" t="s">
+      <c r="D17" s="28" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="B18" s="28" t="s">
+        <v>164</v>
+      </c>
+      <c r="C18" s="28" t="s">
         <v>154</v>
       </c>
-      <c r="C16" s="26" t="s">
-        <v>155</v>
-      </c>
-      <c r="D16" s="26" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="26" t="s">
-        <v>102</v>
-      </c>
-      <c r="B17" s="26" t="s">
-        <v>156</v>
-      </c>
-      <c r="C17" s="26" t="s">
-        <v>145</v>
-      </c>
-      <c r="D17" s="26" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="26" t="s">
-        <v>82</v>
-      </c>
-      <c r="B18" s="26" t="s">
-        <v>157</v>
-      </c>
-      <c r="C18" s="26" t="s">
-        <v>147</v>
-      </c>
-      <c r="D18" s="26" t="s">
-        <v>75</v>
+      <c r="D18" s="28" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -4841,190 +4997,190 @@
       <c r="H20" s="3"/>
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="B21" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="C21" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="D21" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="E21" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="F21" s="18" t="s">
-        <v>162</v>
-      </c>
-      <c r="G21" s="18" t="s">
-        <v>163</v>
-      </c>
-      <c r="H21" s="18" t="s">
-        <v>53</v>
+      <c r="A21" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="C21" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="D21" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="E21" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="F21" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="G21" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="H21" s="19" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="26" t="s">
-        <v>75</v>
-      </c>
-      <c r="B22" s="26" t="s">
-        <v>164</v>
-      </c>
-      <c r="C22" s="26" t="s">
-        <v>165</v>
-      </c>
-      <c r="D22" s="26" t="s">
-        <v>166</v>
-      </c>
-      <c r="E22" s="26" t="s">
-        <v>167</v>
-      </c>
-      <c r="F22" s="27" t="n">
+      <c r="A22" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="B22" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="C22" s="28" t="s">
+        <v>172</v>
+      </c>
+      <c r="D22" s="28" t="s">
+        <v>173</v>
+      </c>
+      <c r="E22" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="F22" s="29" t="n">
         <v>500</v>
       </c>
-      <c r="G22" s="32" t="n">
+      <c r="G22" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="H22" s="26" t="s">
-        <v>168</v>
+      <c r="H22" s="28" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="26" t="s">
-        <v>149</v>
-      </c>
-      <c r="B23" s="26" t="s">
-        <v>169</v>
-      </c>
-      <c r="C23" s="26" t="s">
-        <v>170</v>
-      </c>
-      <c r="D23" s="26" t="s">
-        <v>125</v>
-      </c>
-      <c r="E23" s="26" t="s">
-        <v>171</v>
-      </c>
-      <c r="F23" s="27" t="n">
+      <c r="A23" s="28" t="s">
+        <v>156</v>
+      </c>
+      <c r="B23" s="28" t="s">
+        <v>176</v>
+      </c>
+      <c r="C23" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="D23" s="28" t="s">
+        <v>132</v>
+      </c>
+      <c r="E23" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="F23" s="29" t="n">
         <v>400</v>
       </c>
-      <c r="G23" s="32" t="n">
+      <c r="G23" s="34" t="n">
         <v>2.5</v>
       </c>
-      <c r="H23" s="26" t="s">
-        <v>172</v>
+      <c r="H23" s="28" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="26" t="s">
-        <v>86</v>
-      </c>
-      <c r="B24" s="26" t="s">
-        <v>173</v>
-      </c>
-      <c r="C24" s="26" t="s">
-        <v>174</v>
-      </c>
-      <c r="D24" s="26" t="s">
-        <v>175</v>
-      </c>
-      <c r="E24" s="26" t="s">
+      <c r="A24" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="B24" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="C24" s="28" t="s">
+        <v>181</v>
+      </c>
+      <c r="D24" s="28" t="s">
+        <v>182</v>
+      </c>
+      <c r="E24" s="28" t="s">
+        <v>183</v>
+      </c>
+      <c r="F24" s="29" t="n">
+        <v>300</v>
+      </c>
+      <c r="G24" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="H24" s="28" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="B25" s="28" t="s">
+        <v>185</v>
+      </c>
+      <c r="C25" s="28" t="s">
+        <v>186</v>
+      </c>
+      <c r="D25" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="E25" s="28" t="s">
+        <v>187</v>
+      </c>
+      <c r="F25" s="29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G25" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="H25" s="28" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="B26" s="28" t="s">
         <v>176</v>
       </c>
-      <c r="F24" s="27" t="n">
-        <v>300</v>
-      </c>
-      <c r="G24" s="32" t="n">
-        <v>3</v>
-      </c>
-      <c r="H24" s="26" t="s">
+      <c r="C26" s="28" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="26" t="s">
-        <v>92</v>
-      </c>
-      <c r="B25" s="26" t="s">
-        <v>178</v>
-      </c>
-      <c r="C25" s="26" t="s">
-        <v>179</v>
-      </c>
-      <c r="D25" s="26" t="s">
-        <v>93</v>
-      </c>
-      <c r="E25" s="26" t="s">
-        <v>180</v>
-      </c>
-      <c r="F25" s="27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G25" s="32" t="n">
+      <c r="D26" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="E26" s="28" t="s">
+        <v>189</v>
+      </c>
+      <c r="F26" s="29" t="n">
+        <v>200</v>
+      </c>
+      <c r="G26" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="H25" s="26" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="B26" s="26" t="s">
-        <v>169</v>
-      </c>
-      <c r="C26" s="26" t="s">
-        <v>170</v>
-      </c>
-      <c r="D26" s="26" t="s">
-        <v>98</v>
-      </c>
-      <c r="E26" s="26" t="s">
-        <v>182</v>
-      </c>
-      <c r="F26" s="27" t="n">
-        <v>200</v>
-      </c>
-      <c r="G26" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="H26" s="26" t="s">
-        <v>183</v>
+      <c r="H26" s="28" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="26" t="s">
-        <v>101</v>
-      </c>
-      <c r="B27" s="26" t="s">
-        <v>184</v>
-      </c>
-      <c r="C27" s="26" t="s">
-        <v>185</v>
-      </c>
-      <c r="D27" s="26" t="s">
-        <v>102</v>
-      </c>
-      <c r="E27" s="26" t="s">
-        <v>186</v>
-      </c>
-      <c r="F27" s="27" t="n">
+      <c r="A27" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="B27" s="28" t="s">
+        <v>191</v>
+      </c>
+      <c r="C27" s="28" t="s">
+        <v>192</v>
+      </c>
+      <c r="D27" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="E27" s="28" t="s">
+        <v>193</v>
+      </c>
+      <c r="F27" s="29" t="n">
         <v>500</v>
       </c>
-      <c r="G27" s="32" t="n">
+      <c r="G27" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="H27" s="26" t="s">
-        <v>187</v>
+      <c r="H27" s="28" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
@@ -5035,363 +5191,363 @@
       <c r="H29" s="3"/>
     </row>
     <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="18" t="s">
-        <v>189</v>
-      </c>
-      <c r="B30" s="18" t="s">
-        <v>190</v>
-      </c>
-      <c r="C30" s="18" t="s">
-        <v>191</v>
-      </c>
-      <c r="D30" s="18" t="s">
-        <v>192</v>
-      </c>
-      <c r="E30" s="18" t="s">
-        <v>193</v>
-      </c>
-      <c r="F30" s="18" t="s">
-        <v>194</v>
+      <c r="A30" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="B30" s="19" t="s">
+        <v>197</v>
+      </c>
+      <c r="C30" s="19" t="s">
+        <v>198</v>
+      </c>
+      <c r="D30" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="E30" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="F30" s="19" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="26" t="s">
-        <v>164</v>
-      </c>
-      <c r="B31" s="26" t="s">
-        <v>83</v>
-      </c>
-      <c r="C31" s="33" t="n">
+      <c r="A31" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="B31" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="C31" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="D31" s="34" t="n">
+      <c r="D31" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="E31" s="35" t="n">
+      <c r="E31" s="37" t="n">
         <f aca="false">D31/7</f>
         <v>0.714285714285714</v>
       </c>
-      <c r="F31" s="19" t="str">
+      <c r="F31" s="20" t="str">
         <f aca="false">A31&amp;"|"&amp;B31</f>
         <v>Shenzhen|US</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="26" t="s">
-        <v>164</v>
-      </c>
-      <c r="B32" s="26" t="s">
-        <v>138</v>
-      </c>
-      <c r="C32" s="33" t="n">
+      <c r="A32" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="B32" s="28" t="s">
+        <v>145</v>
+      </c>
+      <c r="C32" s="35" t="n">
         <v>5</v>
       </c>
-      <c r="D32" s="34" t="n">
+      <c r="D32" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="E32" s="35" t="n">
+      <c r="E32" s="37" t="n">
         <f aca="false">D32/7</f>
         <v>1</v>
       </c>
-      <c r="F32" s="19" t="str">
+      <c r="F32" s="20" t="str">
         <f aca="false">A32&amp;"|"&amp;B32</f>
         <v>Shenzhen|UK</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="26" t="s">
-        <v>164</v>
-      </c>
-      <c r="B33" s="26" t="s">
-        <v>78</v>
-      </c>
-      <c r="C33" s="33" t="n">
+      <c r="A33" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="B33" s="28" t="s">
+        <v>84</v>
+      </c>
+      <c r="C33" s="35" t="n">
         <v>0.285714285714286</v>
       </c>
-      <c r="D33" s="34" t="n">
+      <c r="D33" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="E33" s="35" t="n">
+      <c r="E33" s="37" t="n">
         <f aca="false">D33/7</f>
         <v>0.142857142857143</v>
       </c>
-      <c r="F33" s="19" t="str">
+      <c r="F33" s="20" t="str">
         <f aca="false">A33&amp;"|"&amp;B33</f>
         <v>Shenzhen|HK</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="26" t="s">
-        <v>169</v>
-      </c>
-      <c r="B34" s="26" t="s">
-        <v>83</v>
-      </c>
-      <c r="C34" s="33" t="n">
+      <c r="A34" s="28" t="s">
+        <v>176</v>
+      </c>
+      <c r="B34" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="C34" s="35" t="n">
         <v>4.5</v>
       </c>
-      <c r="D34" s="34" t="n">
+      <c r="D34" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="E34" s="35" t="n">
+      <c r="E34" s="37" t="n">
         <f aca="false">D34/7</f>
         <v>0.857142857142857</v>
       </c>
-      <c r="F34" s="19" t="str">
+      <c r="F34" s="20" t="str">
         <f aca="false">A34&amp;"|"&amp;B34</f>
         <v>Chiang Mai|US</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="26" t="s">
-        <v>169</v>
-      </c>
-      <c r="B35" s="26" t="s">
-        <v>138</v>
-      </c>
-      <c r="C35" s="33" t="n">
+      <c r="A35" s="28" t="s">
+        <v>176</v>
+      </c>
+      <c r="B35" s="28" t="s">
+        <v>145</v>
+      </c>
+      <c r="C35" s="35" t="n">
         <v>4.5</v>
       </c>
-      <c r="D35" s="34" t="n">
+      <c r="D35" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="E35" s="35" t="n">
+      <c r="E35" s="37" t="n">
         <f aca="false">D35/7</f>
         <v>1</v>
       </c>
-      <c r="F35" s="19" t="str">
+      <c r="F35" s="20" t="str">
         <f aca="false">A35&amp;"|"&amp;B35</f>
         <v>Chiang Mai|UK</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="26" t="s">
-        <v>169</v>
-      </c>
-      <c r="B36" s="26" t="s">
-        <v>78</v>
-      </c>
-      <c r="C36" s="33" t="n">
+      <c r="A36" s="28" t="s">
+        <v>176</v>
+      </c>
+      <c r="B36" s="28" t="s">
+        <v>84</v>
+      </c>
+      <c r="C36" s="35" t="n">
         <v>4</v>
       </c>
-      <c r="D36" s="34" t="n">
+      <c r="D36" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="E36" s="35" t="n">
+      <c r="E36" s="37" t="n">
         <f aca="false">D36/7</f>
         <v>0.285714285714286</v>
       </c>
-      <c r="F36" s="19" t="str">
+      <c r="F36" s="20" t="str">
         <f aca="false">A36&amp;"|"&amp;B36</f>
         <v>Chiang Mai|HK</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="26" t="s">
-        <v>173</v>
-      </c>
-      <c r="B37" s="26" t="s">
-        <v>83</v>
-      </c>
-      <c r="C37" s="33" t="n">
+      <c r="A37" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="B37" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="C37" s="35" t="n">
         <v>4</v>
       </c>
-      <c r="D37" s="34" t="n">
+      <c r="D37" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="E37" s="35" t="n">
+      <c r="E37" s="37" t="n">
         <f aca="false">D37/7</f>
         <v>0.857142857142857</v>
       </c>
-      <c r="F37" s="19" t="str">
+      <c r="F37" s="20" t="str">
         <f aca="false">A37&amp;"|"&amp;B37</f>
         <v>Jakarta|US</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="26" t="s">
-        <v>173</v>
-      </c>
-      <c r="B38" s="26" t="s">
-        <v>138</v>
-      </c>
-      <c r="C38" s="33" t="n">
+      <c r="A38" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="B38" s="28" t="s">
+        <v>145</v>
+      </c>
+      <c r="C38" s="35" t="n">
         <v>5</v>
       </c>
-      <c r="D38" s="34" t="n">
+      <c r="D38" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="E38" s="35" t="n">
+      <c r="E38" s="37" t="n">
         <f aca="false">D38/7</f>
         <v>1</v>
       </c>
-      <c r="F38" s="19" t="str">
+      <c r="F38" s="20" t="str">
         <f aca="false">A38&amp;"|"&amp;B38</f>
         <v>Jakarta|UK</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="26" t="s">
-        <v>173</v>
-      </c>
-      <c r="B39" s="26" t="s">
-        <v>78</v>
-      </c>
-      <c r="C39" s="33" t="n">
+      <c r="A39" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="B39" s="28" t="s">
+        <v>84</v>
+      </c>
+      <c r="C39" s="35" t="n">
         <v>4</v>
       </c>
-      <c r="D39" s="34" t="n">
+      <c r="D39" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="E39" s="35" t="n">
+      <c r="E39" s="37" t="n">
         <f aca="false">D39/7</f>
         <v>0.285714285714286</v>
       </c>
-      <c r="F39" s="19" t="str">
+      <c r="F39" s="20" t="str">
         <f aca="false">A39&amp;"|"&amp;B39</f>
         <v>Jakarta|HK</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="26" t="s">
-        <v>178</v>
-      </c>
-      <c r="B40" s="26" t="s">
-        <v>83</v>
-      </c>
-      <c r="C40" s="33" t="n">
+      <c r="A40" s="28" t="s">
+        <v>185</v>
+      </c>
+      <c r="B40" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="C40" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="D40" s="34" t="n">
+      <c r="D40" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="E40" s="35" t="n">
+      <c r="E40" s="37" t="n">
         <f aca="false">D40/7</f>
         <v>0.571428571428571</v>
       </c>
-      <c r="F40" s="19" t="str">
+      <c r="F40" s="20" t="str">
         <f aca="false">A40&amp;"|"&amp;B40</f>
         <v>Taipei|US</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="26" t="s">
-        <v>178</v>
-      </c>
-      <c r="B41" s="26" t="s">
-        <v>138</v>
-      </c>
-      <c r="C41" s="33" t="n">
+      <c r="A41" s="28" t="s">
+        <v>185</v>
+      </c>
+      <c r="B41" s="28" t="s">
+        <v>145</v>
+      </c>
+      <c r="C41" s="35" t="n">
         <v>5</v>
       </c>
-      <c r="D41" s="34" t="n">
+      <c r="D41" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="E41" s="35" t="n">
+      <c r="E41" s="37" t="n">
         <f aca="false">D41/7</f>
         <v>0.857142857142857</v>
       </c>
-      <c r="F41" s="19" t="str">
+      <c r="F41" s="20" t="str">
         <f aca="false">A41&amp;"|"&amp;B41</f>
         <v>Taipei|UK</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="26" t="s">
-        <v>178</v>
-      </c>
-      <c r="B42" s="26" t="s">
-        <v>78</v>
-      </c>
-      <c r="C42" s="33" t="n">
+      <c r="A42" s="28" t="s">
+        <v>185</v>
+      </c>
+      <c r="B42" s="28" t="s">
+        <v>84</v>
+      </c>
+      <c r="C42" s="35" t="n">
         <v>0.285714285714286</v>
       </c>
-      <c r="D42" s="34" t="n">
+      <c r="D42" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="E42" s="35" t="n">
+      <c r="E42" s="37" t="n">
         <f aca="false">D42/7</f>
         <v>0.142857142857143</v>
       </c>
-      <c r="F42" s="19" t="str">
+      <c r="F42" s="20" t="str">
         <f aca="false">A42&amp;"|"&amp;B42</f>
         <v>Taipei|HK</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="26" t="s">
-        <v>184</v>
-      </c>
-      <c r="B43" s="26" t="s">
-        <v>83</v>
-      </c>
-      <c r="C43" s="33" t="n">
+      <c r="A43" s="28" t="s">
+        <v>191</v>
+      </c>
+      <c r="B43" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="C43" s="35" t="n">
         <v>3.5</v>
       </c>
-      <c r="D43" s="34" t="n">
+      <c r="D43" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="E43" s="35" t="n">
+      <c r="E43" s="37" t="n">
         <f aca="false">D43/7</f>
         <v>0.714285714285714</v>
       </c>
-      <c r="F43" s="19" t="str">
+      <c r="F43" s="20" t="str">
         <f aca="false">A43&amp;"|"&amp;B43</f>
         <v>Ho Chi Minh City|US</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="26" t="s">
-        <v>184</v>
-      </c>
-      <c r="B44" s="26" t="s">
-        <v>138</v>
-      </c>
-      <c r="C44" s="33" t="n">
+      <c r="A44" s="28" t="s">
+        <v>191</v>
+      </c>
+      <c r="B44" s="28" t="s">
+        <v>145</v>
+      </c>
+      <c r="C44" s="35" t="n">
         <v>5</v>
       </c>
-      <c r="D44" s="34" t="n">
+      <c r="D44" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="E44" s="35" t="n">
+      <c r="E44" s="37" t="n">
         <f aca="false">D44/7</f>
         <v>1</v>
       </c>
-      <c r="F44" s="19" t="str">
+      <c r="F44" s="20" t="str">
         <f aca="false">A44&amp;"|"&amp;B44</f>
         <v>Ho Chi Minh City|UK</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="26" t="s">
-        <v>184</v>
-      </c>
-      <c r="B45" s="26" t="s">
-        <v>78</v>
-      </c>
-      <c r="C45" s="33" t="n">
+      <c r="A45" s="28" t="s">
+        <v>191</v>
+      </c>
+      <c r="B45" s="28" t="s">
+        <v>84</v>
+      </c>
+      <c r="C45" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="D45" s="34" t="n">
+      <c r="D45" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="E45" s="35" t="n">
+      <c r="E45" s="37" t="n">
         <f aca="false">D45/7</f>
         <v>0.142857142857143</v>
       </c>
-      <c r="F45" s="19" t="str">
+      <c r="F45" s="20" t="str">
         <f aca="false">A45&amp;"|"&amp;B45</f>
         <v>Ho Chi Minh City|HK</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="11" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="B48" s="11"/>
       <c r="C48" s="11"/>
@@ -5403,7 +5559,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="11" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="B49" s="11"/>
       <c r="C49" s="11"/>
@@ -5415,7 +5571,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="11" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="B50" s="11"/>
       <c r="C50" s="11"/>
@@ -5427,7 +5583,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="11" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="B51" s="11"/>
       <c r="C51" s="11"/>
@@ -5439,7 +5595,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="11" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="B52" s="11"/>
       <c r="C52" s="11"/>

--- a/UK_Restock_Plan.xlsx
+++ b/UK_Restock_Plan.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="208">
   <si>
     <t xml:space="preserve">UK Restock Plan — Summary</t>
   </si>
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Launch Assumptions (editable):</t>
   </si>
   <si>
-    <t xml:space="preserve">3 new UK retail partners launch in 6 weeks (from 2026-08-10) — edit if the date shifts</t>
+    <t xml:space="preserve">UPDATED per retail partner request: moved up 2 weeks from 2026-09-21 (marketing campaign ready early) — was originally 6 weeks out from 2026-08-10</t>
   </si>
   <si>
     <t xml:space="preserve">Target Weeks of Cover at Launch</t>
@@ -308,22 +308,25 @@
     <t xml:space="preserve">HN-RB-300</t>
   </si>
   <si>
+    <t xml:space="preserve">Production delayed — power outage at factory (2-week delay)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ships to HK, ETA revised to 5.5 weeks (originally 3.5 weeks; +2 weeks for power-outage delay per factory email)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PO-411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HN-NC-075</t>
+  </si>
+  <si>
     <t xml:space="preserve">In production — on track</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ships to HK, ETA 3.5 weeks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PO-411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HN-NC-075</t>
   </si>
   <si>
     <t xml:space="preserve">US</t>
@@ -1404,7 +1407,7 @@
     <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="str">
         <f aca="false">"Purchase Order Risk: "&amp;COUNTIF('Purchase Orders'!O6:O11,"High Risk")&amp;" of "&amp;COUNTA('Purchase Orders'!A6:A11)&amp;" open PO(s) are flagged High Risk and require follow-up."</f>
-        <v>Purchase Order Risk: 2 of 6 open PO(s) are flagged High Risk and require follow-up.</v>
+        <v>Purchase Order Risk: 3 of 6 open PO(s) are flagged High Risk and require follow-up.</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -1438,7 +1441,7 @@
       </c>
       <c r="B11" s="6" t="n">
         <f aca="false">'UK Restock Plan'!B4</f>
-        <v>46286</v>
+        <v>46272</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1447,7 +1450,7 @@
       </c>
       <c r="B12" s="7" t="n">
         <f aca="false">'UK Restock Plan'!B8</f>
-        <v>5.85714285714286</v>
+        <v>3.85714285714286</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1483,7 +1486,7 @@
       </c>
       <c r="B16" s="9" t="n">
         <f aca="false">COUNTIF('UK Restock Plan'!W11:W19,"Expedite Required")</f>
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1492,7 +1495,7 @@
       </c>
       <c r="B17" s="9" t="n">
         <f aca="false">COUNTIF('UK Restock Plan'!W11:W19,"Critical — May Miss Launch")</f>
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1501,7 +1504,7 @@
       </c>
       <c r="B18" s="9" t="n">
         <f aca="false">COUNTIF('PO Follow-Ups'!J6:J11,"Yes")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1635,7 +1638,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="13" t="n">
-        <v>46286</v>
+        <v>46272</v>
       </c>
       <c r="C4" s="14" t="s">
         <v>18</v>
@@ -1678,7 +1681,7 @@
       </c>
       <c r="B8" s="18" t="n">
         <f aca="false">($B$4-$B$7)/7</f>
-        <v>5.85714285714286</v>
+        <v>3.85714285714286</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1834,15 +1837,15 @@
       </c>
       <c r="U11" s="23" t="str">
         <f aca="false">IF($O11=0,"No Order Needed",IF($S11&lt;=$B$8,"Sea",IF($T11&lt;=$B$8,"Air — Expedite","Air — Still At Risk")))</f>
-        <v>Air — Expedite</v>
+        <v>Air — Still At Risk</v>
       </c>
       <c r="V11" s="17" t="n">
         <f aca="false">IF($O11=0,"N/A",$B$4-IF($U11="Sea",$S11,$T11)*7)</f>
-        <v>46258</v>
+        <v>46244</v>
       </c>
       <c r="W11" s="23" t="str">
         <f aca="false">IF($O11=0,"No Restock Needed",IF($U11="Sea","On Track",IF($U11="Air — Expedite","Expedite Required","Critical — May Miss Launch")))</f>
-        <v>Expedite Required</v>
+        <v>Critical — May Miss Launch</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1927,15 +1930,15 @@
       </c>
       <c r="U12" s="23" t="str">
         <f aca="false">IF($O12=0,"No Order Needed",IF($S12&lt;=$B$8,"Sea",IF($T12&lt;=$B$8,"Air — Expedite","Air — Still At Risk")))</f>
-        <v>Air — Expedite</v>
+        <v>Air — Still At Risk</v>
       </c>
       <c r="V12" s="17" t="n">
         <f aca="false">IF($O12=0,"N/A",$B$4-IF($U12="Sea",$S12,$T12)*7)</f>
-        <v>46258</v>
+        <v>46244</v>
       </c>
       <c r="W12" s="23" t="str">
         <f aca="false">IF($O12=0,"No Restock Needed",IF($U12="Sea","On Track",IF($U12="Air — Expedite","Expedite Required","Critical — May Miss Launch")))</f>
-        <v>Expedite Required</v>
+        <v>Critical — May Miss Launch</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2024,7 +2027,7 @@
       </c>
       <c r="V13" s="17" t="n">
         <f aca="false">IF($O13=0,"N/A",$B$4-IF($U13="Sea",$S13,$T13)*7)</f>
-        <v>46261.5</v>
+        <v>46247.5</v>
       </c>
       <c r="W13" s="23" t="str">
         <f aca="false">IF($O13=0,"No Restock Needed",IF($U13="Sea","On Track",IF($U13="Air — Expedite","Expedite Required","Critical — May Miss Launch")))</f>
@@ -2113,15 +2116,15 @@
       </c>
       <c r="U14" s="23" t="str">
         <f aca="false">IF($O14=0,"No Order Needed",IF($S14&lt;=$B$8,"Sea",IF($T14&lt;=$B$8,"Air — Expedite","Air — Still At Risk")))</f>
-        <v>Air — Expedite</v>
+        <v>Air — Still At Risk</v>
       </c>
       <c r="V14" s="17" t="n">
         <f aca="false">IF($O14=0,"N/A",$B$4-IF($U14="Sea",$S14,$T14)*7)</f>
-        <v>46258</v>
+        <v>46244</v>
       </c>
       <c r="W14" s="23" t="str">
         <f aca="false">IF($O14=0,"No Restock Needed",IF($U14="Sea","On Track",IF($U14="Air — Expedite","Expedite Required","Critical — May Miss Launch")))</f>
-        <v>Expedite Required</v>
+        <v>Critical — May Miss Launch</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2210,7 +2213,7 @@
       </c>
       <c r="V15" s="17" t="n">
         <f aca="false">IF($O15=0,"N/A",$B$4-IF($U15="Sea",$S15,$T15)*7)</f>
-        <v>46266</v>
+        <v>46252</v>
       </c>
       <c r="W15" s="23" t="str">
         <f aca="false">IF($O15=0,"No Restock Needed",IF($U15="Sea","On Track",IF($U15="Air — Expedite","Expedite Required","Critical — May Miss Launch")))</f>
@@ -2299,15 +2302,15 @@
       </c>
       <c r="U16" s="23" t="str">
         <f aca="false">IF($O16=0,"No Order Needed",IF($S16&lt;=$B$8,"Sea",IF($T16&lt;=$B$8,"Air — Expedite","Air — Still At Risk")))</f>
-        <v>Air — Expedite</v>
+        <v>Air — Still At Risk</v>
       </c>
       <c r="V16" s="17" t="n">
         <f aca="false">IF($O16=0,"N/A",$B$4-IF($U16="Sea",$S16,$T16)*7)</f>
-        <v>46258</v>
+        <v>46244</v>
       </c>
       <c r="W16" s="23" t="str">
         <f aca="false">IF($O16=0,"No Restock Needed",IF($U16="Sea","On Track",IF($U16="Air — Expedite","Expedite Required","Critical — May Miss Launch")))</f>
-        <v>Expedite Required</v>
+        <v>Critical — May Miss Launch</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2396,7 +2399,7 @@
       </c>
       <c r="V17" s="17" t="n">
         <f aca="false">IF($O17=0,"N/A",$B$4-IF($U17="Sea",$S17,$T17)*7)</f>
-        <v>46265</v>
+        <v>46251</v>
       </c>
       <c r="W17" s="23" t="str">
         <f aca="false">IF($O17=0,"No Restock Needed",IF($U17="Sea","On Track",IF($U17="Air — Expedite","Expedite Required","Critical — May Miss Launch")))</f>
@@ -2485,15 +2488,15 @@
       </c>
       <c r="U18" s="23" t="str">
         <f aca="false">IF($O18=0,"No Order Needed",IF($S18&lt;=$B$8,"Sea",IF($T18&lt;=$B$8,"Air — Expedite","Air — Still At Risk")))</f>
-        <v>Air — Expedite</v>
+        <v>Air — Still At Risk</v>
       </c>
       <c r="V18" s="17" t="n">
         <f aca="false">IF($O18=0,"N/A",$B$4-IF($U18="Sea",$S18,$T18)*7)</f>
-        <v>46251</v>
+        <v>46237</v>
       </c>
       <c r="W18" s="23" t="str">
         <f aca="false">IF($O18=0,"No Restock Needed",IF($U18="Sea","On Track",IF($U18="Air — Expedite","Expedite Required","Critical — May Miss Launch")))</f>
-        <v>Expedite Required</v>
+        <v>Critical — May Miss Launch</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2578,15 +2581,15 @@
       </c>
       <c r="U19" s="23" t="str">
         <f aca="false">IF($O19=0,"No Order Needed",IF($S19&lt;=$B$8,"Sea",IF($T19&lt;=$B$8,"Air — Expedite","Air — Still At Risk")))</f>
-        <v>Air — Expedite</v>
+        <v>Air — Still At Risk</v>
       </c>
       <c r="V19" s="17" t="n">
         <f aca="false">IF($O19=0,"N/A",$B$4-IF($U19="Sea",$S19,$T19)*7)</f>
-        <v>46258</v>
+        <v>46244</v>
       </c>
       <c r="W19" s="23" t="str">
         <f aca="false">IF($O19=0,"No Restock Needed",IF($U19="Sea","On Track",IF($U19="Air — Expedite","Expedite Required","Critical — May Miss Launch")))</f>
-        <v>Expedite Required</v>
+        <v>Critical — May Miss Launch</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2980,11 +2983,11 @@
       </c>
       <c r="F6" s="20" t="str">
         <f aca="false">'Purchase Orders'!G6</f>
-        <v>In production — on track</v>
+        <v>Production delayed — power outage at factory (2-week delay)</v>
       </c>
       <c r="G6" s="23" t="str">
         <f aca="false">'Purchase Orders'!O6</f>
-        <v>Low Risk</v>
+        <v>High Risk</v>
       </c>
       <c r="H6" s="23" t="str">
         <f aca="false">'Purchase Orders'!H6</f>
@@ -2996,15 +2999,15 @@
       </c>
       <c r="J6" s="23" t="str">
         <f aca="false">IF($G6="Low Risk","No","Yes")</f>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="K6" s="20" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH("delayed",$F6)),"Contact factory for a revised production timeline. If this is a UK-critical SKU, evaluate air freight or a backup factory to recover schedule.",IF(ISNUMBER(SEARCH("Unconfirmed",$F6)),"Escalate to factory immediately — no confirmation received. Confirm the production slot or reallocate the PO to a backup factory.",IF(ISNUMBER(SEARCH("Completed",$F6)),"Issue shipping instructions now. Goods are finished and awaiting dispatch — assign a destination and carrier immediately to avoid storage delays.",IF(ISNUMBER(SEARCH("on track",$F6)),"No follow-up needed — monitor for on-time delivery.","Review PO status manually."))))</f>
-        <v>No follow-up needed — monitor for on-time delivery.</v>
+        <v>Contact factory for a revised production timeline. If this is a UK-critical SKU, evaluate air freight or a backup factory to recover schedule.</v>
       </c>
       <c r="L6" s="23" t="str">
         <f aca="false">IF(AND($G6&lt;&gt;"Low Risk",$I6="Yes — UK Critical SKU"),"Urgent — UK Launch Impact",IF($G6="High Risk","High",IF($G6="Medium Risk","Medium","Low")))</f>
-        <v>Low</v>
+        <v>Urgent — UK Launch Impact</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3514,7 +3517,7 @@
         <v>86</v>
       </c>
       <c r="K6" s="31" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="L6" s="32" t="n">
         <f aca="false">IFERROR(INDEX('Reference Data'!$C$31:$C$45,MATCH($C6&amp;"|"&amp;$H6,'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
@@ -3530,7 +3533,7 @@
       </c>
       <c r="O6" s="23" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH("delayed",G6)),"High Risk",IF(ISNUMBER(SEARCH("Unconfirmed",G6)),"High Risk",IF(ISNUMBER(SEARCH("Completed",G6)),"Medium Risk",IF(ISNUMBER(SEARCH("on track",G6)),"Low Risk","Review"))))</f>
-        <v>Low Risk</v>
+        <v>High Risk</v>
       </c>
       <c r="P6" s="23" t="str">
         <f aca="false">IF(H6="UK","Yes","No")</f>
@@ -3559,16 +3562,16 @@
         <v>500</v>
       </c>
       <c r="G7" s="28" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="H7" s="30" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I7" s="30" t="s">
         <v>85</v>
       </c>
       <c r="J7" s="28" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K7" s="31" t="n">
         <v>4</v>
@@ -3596,17 +3599,17 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="28" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B8" s="28" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C8" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$B$22:$B$27,MATCH(B8,'Reference Data'!$A$22:$A$27,0)),"N/A")</f>
         <v>Jakarta</v>
       </c>
       <c r="D8" s="28" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E8" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$B$10:$B$18,MATCH(D8,'Reference Data'!$A$10:$A$18,0)),"N/A")</f>
@@ -3616,19 +3619,19 @@
         <v>300</v>
       </c>
       <c r="G8" s="28" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H8" s="30" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I8" s="30" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J8" s="28" t="s">
+        <v>97</v>
+      </c>
+      <c r="K8" s="30" t="s">
         <v>96</v>
-      </c>
-      <c r="K8" s="30" t="s">
-        <v>95</v>
       </c>
       <c r="L8" s="32" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$C$31:$C$45,MATCH($C8&amp;"|"&amp;$H8,'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
@@ -3653,17 +3656,17 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="28" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B9" s="28" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C9" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$B$22:$B$27,MATCH(B9,'Reference Data'!$A$22:$A$27,0)),"N/A")</f>
         <v>Taipei</v>
       </c>
       <c r="D9" s="28" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E9" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$B$10:$B$18,MATCH(D9,'Reference Data'!$A$10:$A$18,0)),"N/A")</f>
@@ -3673,19 +3676,19 @@
         <v>1000</v>
       </c>
       <c r="G9" s="28" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H9" s="30" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I9" s="30" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J9" s="28" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K9" s="30" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L9" s="32" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$C$31:$C$45,MATCH($C9&amp;"|"&amp;$H9,'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
@@ -3710,17 +3713,17 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="28" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B10" s="28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C10" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$B$22:$B$27,MATCH(B10,'Reference Data'!$A$22:$A$27,0)),"N/A")</f>
         <v>Chiang Mai</v>
       </c>
       <c r="D10" s="28" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E10" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$B$10:$B$18,MATCH(D10,'Reference Data'!$A$10:$A$18,0)),"N/A")</f>
@@ -3730,19 +3733,19 @@
         <v>200</v>
       </c>
       <c r="G10" s="28" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H10" s="30" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I10" s="30" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J10" s="28" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K10" s="30" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L10" s="32" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$C$31:$C$45,MATCH($C10&amp;"|"&amp;$H10,'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
@@ -3767,17 +3770,17 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="28" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B11" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C11" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$B$22:$B$27,MATCH(B11,'Reference Data'!$A$22:$A$27,0)),"N/A")</f>
         <v>Ho Chi Minh City</v>
       </c>
       <c r="D11" s="28" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E11" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$B$10:$B$18,MATCH(D11,'Reference Data'!$A$10:$A$18,0)),"N/A")</f>
@@ -3787,16 +3790,16 @@
         <v>500</v>
       </c>
       <c r="G11" s="28" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="H11" s="30" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I11" s="30" t="s">
         <v>85</v>
       </c>
       <c r="J11" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K11" s="31" t="n">
         <v>6</v>
@@ -3852,7 +3855,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -3872,7 +3875,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -3892,7 +3895,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -3912,7 +3915,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -3987,7 +3990,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4006,12 +4009,12 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B4" s="15" t="n">
         <v>4</v>
@@ -4019,13 +4022,13 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B5" s="15" t="n">
         <v>8</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4036,40 +4039,40 @@
         <v>25</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G7" s="19" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H7" s="19" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I7" s="19" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J7" s="19" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K7" s="19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L7" s="19" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M7" s="19" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="N7" s="19" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O7" s="19" t="s">
         <v>30</v>
@@ -4134,7 +4137,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="28" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B9" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$B$10:$B$18,MATCH($A9,'Reference Data'!$A$10:$A$18,0)),"N/A")</f>
@@ -4191,7 +4194,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="28" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B10" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$B$10:$B$18,MATCH($A10,'Reference Data'!$A$10:$A$18,0)),"N/A")</f>
@@ -4248,7 +4251,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="28" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B11" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$B$10:$B$18,MATCH($A11,'Reference Data'!$A$10:$A$18,0)),"N/A")</f>
@@ -4305,7 +4308,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="28" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B12" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$B$10:$B$18,MATCH($A12,'Reference Data'!$A$10:$A$18,0)),"N/A")</f>
@@ -4362,7 +4365,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="28" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B13" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$B$10:$B$18,MATCH($A13,'Reference Data'!$A$10:$A$18,0)),"N/A")</f>
@@ -4419,7 +4422,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="28" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B14" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$B$10:$B$18,MATCH($A14,'Reference Data'!$A$10:$A$18,0)),"N/A")</f>
@@ -4476,7 +4479,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="28" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B15" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$B$10:$B$18,MATCH($A15,'Reference Data'!$A$10:$A$18,0)),"N/A")</f>
@@ -4632,7 +4635,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -4651,7 +4654,7 @@
     </row>
     <row r="21" customFormat="false" ht="22.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -4670,7 +4673,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -4689,7 +4692,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -4766,7 +4769,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4778,7 +4781,7 @@
     </row>
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -4790,35 +4793,35 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="19" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="28" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B5" s="28" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="28" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B6" s="28" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C6" s="28" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4826,15 +4829,15 @@
         <v>84</v>
       </c>
       <c r="B7" s="28" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C7" s="28" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -4852,10 +4855,10 @@
         <v>25</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4863,10 +4866,10 @@
         <v>82</v>
       </c>
       <c r="B10" s="28" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C10" s="28" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D10" s="28" t="s">
         <v>81</v>
@@ -4874,13 +4877,13 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="28" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B11" s="28" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C11" s="28" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D11" s="28" t="s">
         <v>81</v>
@@ -4888,86 +4891,86 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="28" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B12" s="28" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C12" s="28" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D12" s="28" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="B13" s="28" t="s">
+        <v>158</v>
+      </c>
+      <c r="C13" s="28" t="s">
+        <v>159</v>
+      </c>
+      <c r="D13" s="28" t="s">
         <v>93</v>
-      </c>
-      <c r="B13" s="28" t="s">
-        <v>157</v>
-      </c>
-      <c r="C13" s="28" t="s">
-        <v>158</v>
-      </c>
-      <c r="D13" s="28" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="B14" s="28" t="s">
+        <v>160</v>
+      </c>
+      <c r="C14" s="28" t="s">
+        <v>155</v>
+      </c>
+      <c r="D14" s="28" t="s">
         <v>99</v>
-      </c>
-      <c r="B14" s="28" t="s">
-        <v>159</v>
-      </c>
-      <c r="C14" s="28" t="s">
-        <v>154</v>
-      </c>
-      <c r="D14" s="28" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="28" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B15" s="28" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C15" s="28" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D15" s="28" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="28" t="s">
+        <v>105</v>
+      </c>
+      <c r="B16" s="28" t="s">
+        <v>162</v>
+      </c>
+      <c r="C16" s="28" t="s">
+        <v>163</v>
+      </c>
+      <c r="D16" s="28" t="s">
         <v>104</v>
-      </c>
-      <c r="B16" s="28" t="s">
-        <v>161</v>
-      </c>
-      <c r="C16" s="28" t="s">
-        <v>162</v>
-      </c>
-      <c r="D16" s="28" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="B17" s="28" t="s">
+        <v>164</v>
+      </c>
+      <c r="C17" s="28" t="s">
+        <v>153</v>
+      </c>
+      <c r="D17" s="28" t="s">
         <v>108</v>
-      </c>
-      <c r="B17" s="28" t="s">
-        <v>163</v>
-      </c>
-      <c r="C17" s="28" t="s">
-        <v>152</v>
-      </c>
-      <c r="D17" s="28" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4975,10 +4978,10 @@
         <v>88</v>
       </c>
       <c r="B18" s="28" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C18" s="28" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D18" s="28" t="s">
         <v>81</v>
@@ -4986,7 +4989,7 @@
     </row>
     <row r="20" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -5001,22 +5004,22 @@
         <v>26</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D21" s="19" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E21" s="19" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F21" s="19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G21" s="19" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H21" s="19" t="s">
         <v>59</v>
@@ -5027,16 +5030,16 @@
         <v>81</v>
       </c>
       <c r="B22" s="28" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C22" s="28" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D22" s="28" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E22" s="28" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F22" s="29" t="n">
         <v>500</v>
@@ -5045,24 +5048,24 @@
         <v>3</v>
       </c>
       <c r="H22" s="28" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="28" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B23" s="28" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C23" s="28" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D23" s="28" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E23" s="28" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F23" s="29" t="n">
         <v>400</v>
@@ -5071,24 +5074,24 @@
         <v>2.5</v>
       </c>
       <c r="H23" s="28" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="28" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B24" s="28" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C24" s="28" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D24" s="28" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E24" s="28" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F24" s="29" t="n">
         <v>300</v>
@@ -5097,24 +5100,24 @@
         <v>3</v>
       </c>
       <c r="H24" s="28" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="28" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B25" s="28" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C25" s="28" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D25" s="28" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E25" s="28" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F25" s="29" t="n">
         <v>1000</v>
@@ -5123,24 +5126,24 @@
         <v>2</v>
       </c>
       <c r="H25" s="28" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B26" s="28" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C26" s="28" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D26" s="28" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E26" s="28" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F26" s="29" t="n">
         <v>200</v>
@@ -5149,24 +5152,24 @@
         <v>2</v>
       </c>
       <c r="H26" s="28" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B27" s="28" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C27" s="28" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D27" s="28" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E27" s="28" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F27" s="29" t="n">
         <v>500</v>
@@ -5175,12 +5178,12 @@
         <v>4</v>
       </c>
       <c r="H27" s="28" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
@@ -5192,30 +5195,30 @@
     </row>
     <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="19" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D30" s="19" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E30" s="19" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F30" s="19" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="28" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B31" s="28" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C31" s="35" t="n">
         <v>3</v>
@@ -5234,10 +5237,10 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="28" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B32" s="28" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C32" s="35" t="n">
         <v>5</v>
@@ -5256,7 +5259,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="28" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B33" s="28" t="s">
         <v>84</v>
@@ -5278,10 +5281,10 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="28" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B34" s="28" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C34" s="35" t="n">
         <v>4.5</v>
@@ -5300,10 +5303,10 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="28" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B35" s="28" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C35" s="35" t="n">
         <v>4.5</v>
@@ -5322,7 +5325,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="28" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B36" s="28" t="s">
         <v>84</v>
@@ -5344,10 +5347,10 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="28" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B37" s="28" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C37" s="35" t="n">
         <v>4</v>
@@ -5366,10 +5369,10 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="28" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B38" s="28" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C38" s="35" t="n">
         <v>5</v>
@@ -5388,7 +5391,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="28" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B39" s="28" t="s">
         <v>84</v>
@@ -5410,10 +5413,10 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="28" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B40" s="28" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C40" s="35" t="n">
         <v>3</v>
@@ -5432,10 +5435,10 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="28" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B41" s="28" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C41" s="35" t="n">
         <v>5</v>
@@ -5454,7 +5457,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="28" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B42" s="28" t="s">
         <v>84</v>
@@ -5476,10 +5479,10 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="28" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B43" s="28" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C43" s="35" t="n">
         <v>3.5</v>
@@ -5498,10 +5501,10 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="28" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B44" s="28" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C44" s="35" t="n">
         <v>5</v>
@@ -5520,7 +5523,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="28" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B45" s="28" t="s">
         <v>84</v>
@@ -5547,7 +5550,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="11" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B48" s="11"/>
       <c r="C48" s="11"/>
@@ -5559,7 +5562,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="11" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B49" s="11"/>
       <c r="C49" s="11"/>
@@ -5571,7 +5574,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="11" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B50" s="11"/>
       <c r="C50" s="11"/>
@@ -5583,7 +5586,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B51" s="11"/>
       <c r="C51" s="11"/>
@@ -5595,7 +5598,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="11" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B52" s="11"/>
       <c r="C52" s="11"/>

--- a/UK_Restock_Plan.xlsx
+++ b/UK_Restock_Plan.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="211">
   <si>
     <t xml:space="preserve">UK Restock Plan — Summary</t>
   </si>
@@ -166,10 +166,18 @@
 to UK (Wks)</t>
   </si>
   <si>
+    <t xml:space="preserve">Sea Transit
+to UK (Days)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Air Transit
 to UK (Wks)</t>
   </si>
   <si>
+    <t xml:space="preserve">Air Transit
+to UK (Days)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Total Lead
 Time — Sea</t>
   </si>
@@ -206,6 +214,9 @@
   </si>
   <si>
     <t xml:space="preserve">• Recommended Ship Method / Launch Readiness compare each lead-time option (Production Lead Time + Sea or Air transit to UK) against Weeks Until Launch: Sea if it fits, Air if only Air fits, otherwise flagged Critical even with Air.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Sea/Air Transit to UK are shown in both weeks and days (Days = Weeks × 7) per standing instruction, so shipping windows can be planned at day-level precision, not just whole weeks.</t>
   </si>
   <si>
     <t xml:space="preserve">• Order-By Date = Launch Date minus the recommended method's total lead time. If this date is already in the past, that order is overdue and should be placed immediately.</t>
@@ -1476,7 +1487,7 @@
         <v>8</v>
       </c>
       <c r="B15" s="9" t="n">
-        <f aca="false">COUNTIF('UK Restock Plan'!W11:W19,"On Track")</f>
+        <f aca="false">COUNTIF('UK Restock Plan'!Y11:Y19,"On Track")</f>
         <v>0</v>
       </c>
     </row>
@@ -1485,7 +1496,7 @@
         <v>9</v>
       </c>
       <c r="B16" s="9" t="n">
-        <f aca="false">COUNTIF('UK Restock Plan'!W11:W19,"Expedite Required")</f>
+        <f aca="false">COUNTIF('UK Restock Plan'!Y11:Y19,"Expedite Required")</f>
         <v>3</v>
       </c>
     </row>
@@ -1494,7 +1505,7 @@
         <v>10</v>
       </c>
       <c r="B17" s="9" t="n">
-        <f aca="false">COUNTIF('UK Restock Plan'!W11:W19,"Critical — May Miss Launch")</f>
+        <f aca="false">COUNTIF('UK Restock Plan'!Y11:Y19,"Critical — May Miss Launch")</f>
         <v>6</v>
       </c>
     </row>
@@ -1579,7 +1590,7 @@
     <tabColor rgb="FFC00000"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:W29"/>
+  <dimension ref="A1:Y30"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
@@ -1594,11 +1605,11 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="16" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="19" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="16" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="21" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="0" width="20"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1627,6 +1638,8 @@
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
       <c r="W1" s="1"/>
+      <c r="X1" s="1"/>
+      <c r="Y1" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
@@ -1753,6 +1766,12 @@
       </c>
       <c r="W10" s="19" t="s">
         <v>46</v>
+      </c>
+      <c r="X10" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y10" s="19" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1823,28 +1842,36 @@
         <f aca="false">IFERROR(INDEX('Reference Data'!$C$31:$C$45,MATCH($D11&amp;"|UK",'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
         <v>5</v>
       </c>
-      <c r="R11" s="25" t="n">
+      <c r="R11" s="22" t="n">
+        <f aca="false">IFERROR($Q11*7,"N/A")</f>
+        <v>35</v>
+      </c>
+      <c r="S11" s="25" t="n">
         <f aca="false">IFERROR(INDEX('Reference Data'!$E$31:$E$45,MATCH($D11&amp;"|UK",'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
         <v>1</v>
       </c>
-      <c r="S11" s="25" t="n">
+      <c r="T11" s="22" t="n">
+        <f aca="false">IFERROR($S11*7,"N/A")</f>
+        <v>7</v>
+      </c>
+      <c r="U11" s="25" t="n">
         <f aca="false">$P11+$Q11</f>
         <v>8</v>
       </c>
-      <c r="T11" s="25" t="n">
-        <f aca="false">$P11+$R11</f>
+      <c r="V11" s="25" t="n">
+        <f aca="false">$P11+$S11</f>
         <v>4</v>
       </c>
-      <c r="U11" s="23" t="str">
-        <f aca="false">IF($O11=0,"No Order Needed",IF($S11&lt;=$B$8,"Sea",IF($T11&lt;=$B$8,"Air — Expedite","Air — Still At Risk")))</f>
+      <c r="W11" s="23" t="str">
+        <f aca="false">IF($O11=0,"No Order Needed",IF($U11&lt;=$B$8,"Sea",IF($V11&lt;=$B$8,"Air — Expedite","Air — Still At Risk")))</f>
         <v>Air — Still At Risk</v>
       </c>
-      <c r="V11" s="17" t="n">
-        <f aca="false">IF($O11=0,"N/A",$B$4-IF($U11="Sea",$S11,$T11)*7)</f>
+      <c r="X11" s="17" t="n">
+        <f aca="false">IF($O11=0,"N/A",$B$4-IF($W11="Sea",$U11,$V11)*7)</f>
         <v>46244</v>
       </c>
-      <c r="W11" s="23" t="str">
-        <f aca="false">IF($O11=0,"No Restock Needed",IF($U11="Sea","On Track",IF($U11="Air — Expedite","Expedite Required","Critical — May Miss Launch")))</f>
+      <c r="Y11" s="23" t="str">
+        <f aca="false">IF($O11=0,"No Restock Needed",IF($W11="Sea","On Track",IF($W11="Air — Expedite","Expedite Required","Critical — May Miss Launch")))</f>
         <v>Critical — May Miss Launch</v>
       </c>
     </row>
@@ -1916,28 +1943,36 @@
         <f aca="false">IFERROR(INDEX('Reference Data'!$C$31:$C$45,MATCH($D12&amp;"|UK",'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
         <v>5</v>
       </c>
-      <c r="R12" s="25" t="n">
+      <c r="R12" s="22" t="n">
+        <f aca="false">IFERROR($Q12*7,"N/A")</f>
+        <v>35</v>
+      </c>
+      <c r="S12" s="25" t="n">
         <f aca="false">IFERROR(INDEX('Reference Data'!$E$31:$E$45,MATCH($D12&amp;"|UK",'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
         <v>1</v>
       </c>
-      <c r="S12" s="25" t="n">
+      <c r="T12" s="22" t="n">
+        <f aca="false">IFERROR($S12*7,"N/A")</f>
+        <v>7</v>
+      </c>
+      <c r="U12" s="25" t="n">
         <f aca="false">$P12+$Q12</f>
         <v>8</v>
       </c>
-      <c r="T12" s="25" t="n">
-        <f aca="false">$P12+$R12</f>
+      <c r="V12" s="25" t="n">
+        <f aca="false">$P12+$S12</f>
         <v>4</v>
       </c>
-      <c r="U12" s="23" t="str">
-        <f aca="false">IF($O12=0,"No Order Needed",IF($S12&lt;=$B$8,"Sea",IF($T12&lt;=$B$8,"Air — Expedite","Air — Still At Risk")))</f>
+      <c r="W12" s="23" t="str">
+        <f aca="false">IF($O12=0,"No Order Needed",IF($U12&lt;=$B$8,"Sea",IF($V12&lt;=$B$8,"Air — Expedite","Air — Still At Risk")))</f>
         <v>Air — Still At Risk</v>
       </c>
-      <c r="V12" s="17" t="n">
-        <f aca="false">IF($O12=0,"N/A",$B$4-IF($U12="Sea",$S12,$T12)*7)</f>
+      <c r="X12" s="17" t="n">
+        <f aca="false">IF($O12=0,"N/A",$B$4-IF($W12="Sea",$U12,$V12)*7)</f>
         <v>46244</v>
       </c>
-      <c r="W12" s="23" t="str">
-        <f aca="false">IF($O12=0,"No Restock Needed",IF($U12="Sea","On Track",IF($U12="Air — Expedite","Expedite Required","Critical — May Miss Launch")))</f>
+      <c r="Y12" s="23" t="str">
+        <f aca="false">IF($O12=0,"No Restock Needed",IF($W12="Sea","On Track",IF($W12="Air — Expedite","Expedite Required","Critical — May Miss Launch")))</f>
         <v>Critical — May Miss Launch</v>
       </c>
     </row>
@@ -2009,28 +2044,36 @@
         <f aca="false">IFERROR(INDEX('Reference Data'!$C$31:$C$45,MATCH($D13&amp;"|UK",'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
         <v>4.5</v>
       </c>
-      <c r="R13" s="25" t="n">
+      <c r="R13" s="22" t="n">
+        <f aca="false">IFERROR($Q13*7,"N/A")</f>
+        <v>31.5</v>
+      </c>
+      <c r="S13" s="25" t="n">
         <f aca="false">IFERROR(INDEX('Reference Data'!$E$31:$E$45,MATCH($D13&amp;"|UK",'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
         <v>1</v>
       </c>
-      <c r="S13" s="25" t="n">
+      <c r="T13" s="22" t="n">
+        <f aca="false">IFERROR($S13*7,"N/A")</f>
+        <v>7</v>
+      </c>
+      <c r="U13" s="25" t="n">
         <f aca="false">$P13+$Q13</f>
         <v>7</v>
       </c>
-      <c r="T13" s="25" t="n">
-        <f aca="false">$P13+$R13</f>
+      <c r="V13" s="25" t="n">
+        <f aca="false">$P13+$S13</f>
         <v>3.5</v>
       </c>
-      <c r="U13" s="23" t="str">
-        <f aca="false">IF($O13=0,"No Order Needed",IF($S13&lt;=$B$8,"Sea",IF($T13&lt;=$B$8,"Air — Expedite","Air — Still At Risk")))</f>
+      <c r="W13" s="23" t="str">
+        <f aca="false">IF($O13=0,"No Order Needed",IF($U13&lt;=$B$8,"Sea",IF($V13&lt;=$B$8,"Air — Expedite","Air — Still At Risk")))</f>
         <v>Air — Expedite</v>
       </c>
-      <c r="V13" s="17" t="n">
-        <f aca="false">IF($O13=0,"N/A",$B$4-IF($U13="Sea",$S13,$T13)*7)</f>
+      <c r="X13" s="17" t="n">
+        <f aca="false">IF($O13=0,"N/A",$B$4-IF($W13="Sea",$U13,$V13)*7)</f>
         <v>46247.5</v>
       </c>
-      <c r="W13" s="23" t="str">
-        <f aca="false">IF($O13=0,"No Restock Needed",IF($U13="Sea","On Track",IF($U13="Air — Expedite","Expedite Required","Critical — May Miss Launch")))</f>
+      <c r="Y13" s="23" t="str">
+        <f aca="false">IF($O13=0,"No Restock Needed",IF($W13="Sea","On Track",IF($W13="Air — Expedite","Expedite Required","Critical — May Miss Launch")))</f>
         <v>Expedite Required</v>
       </c>
     </row>
@@ -2102,28 +2145,36 @@
         <f aca="false">IFERROR(INDEX('Reference Data'!$C$31:$C$45,MATCH($D14&amp;"|UK",'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
         <v>5</v>
       </c>
-      <c r="R14" s="25" t="n">
+      <c r="R14" s="22" t="n">
+        <f aca="false">IFERROR($Q14*7,"N/A")</f>
+        <v>35</v>
+      </c>
+      <c r="S14" s="25" t="n">
         <f aca="false">IFERROR(INDEX('Reference Data'!$E$31:$E$45,MATCH($D14&amp;"|UK",'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
         <v>1</v>
       </c>
-      <c r="S14" s="25" t="n">
+      <c r="T14" s="22" t="n">
+        <f aca="false">IFERROR($S14*7,"N/A")</f>
+        <v>7</v>
+      </c>
+      <c r="U14" s="25" t="n">
         <f aca="false">$P14+$Q14</f>
         <v>8</v>
       </c>
-      <c r="T14" s="25" t="n">
-        <f aca="false">$P14+$R14</f>
+      <c r="V14" s="25" t="n">
+        <f aca="false">$P14+$S14</f>
         <v>4</v>
       </c>
-      <c r="U14" s="23" t="str">
-        <f aca="false">IF($O14=0,"No Order Needed",IF($S14&lt;=$B$8,"Sea",IF($T14&lt;=$B$8,"Air — Expedite","Air — Still At Risk")))</f>
+      <c r="W14" s="23" t="str">
+        <f aca="false">IF($O14=0,"No Order Needed",IF($U14&lt;=$B$8,"Sea",IF($V14&lt;=$B$8,"Air — Expedite","Air — Still At Risk")))</f>
         <v>Air — Still At Risk</v>
       </c>
-      <c r="V14" s="17" t="n">
-        <f aca="false">IF($O14=0,"N/A",$B$4-IF($U14="Sea",$S14,$T14)*7)</f>
+      <c r="X14" s="17" t="n">
+        <f aca="false">IF($O14=0,"N/A",$B$4-IF($W14="Sea",$U14,$V14)*7)</f>
         <v>46244</v>
       </c>
-      <c r="W14" s="23" t="str">
-        <f aca="false">IF($O14=0,"No Restock Needed",IF($U14="Sea","On Track",IF($U14="Air — Expedite","Expedite Required","Critical — May Miss Launch")))</f>
+      <c r="Y14" s="23" t="str">
+        <f aca="false">IF($O14=0,"No Restock Needed",IF($W14="Sea","On Track",IF($W14="Air — Expedite","Expedite Required","Critical — May Miss Launch")))</f>
         <v>Critical — May Miss Launch</v>
       </c>
     </row>
@@ -2195,28 +2246,36 @@
         <f aca="false">IFERROR(INDEX('Reference Data'!$C$31:$C$45,MATCH($D15&amp;"|UK",'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
         <v>5</v>
       </c>
-      <c r="R15" s="25" t="n">
+      <c r="R15" s="22" t="n">
+        <f aca="false">IFERROR($Q15*7,"N/A")</f>
+        <v>35</v>
+      </c>
+      <c r="S15" s="25" t="n">
         <f aca="false">IFERROR(INDEX('Reference Data'!$E$31:$E$45,MATCH($D15&amp;"|UK",'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
         <v>0.857142857142857</v>
       </c>
-      <c r="S15" s="25" t="n">
+      <c r="T15" s="22" t="n">
+        <f aca="false">IFERROR($S15*7,"N/A")</f>
+        <v>6</v>
+      </c>
+      <c r="U15" s="25" t="n">
         <f aca="false">$P15+$Q15</f>
         <v>7</v>
       </c>
-      <c r="T15" s="25" t="n">
-        <f aca="false">$P15+$R15</f>
+      <c r="V15" s="25" t="n">
+        <f aca="false">$P15+$S15</f>
         <v>2.85714285714286</v>
       </c>
-      <c r="U15" s="23" t="str">
-        <f aca="false">IF($O15=0,"No Order Needed",IF($S15&lt;=$B$8,"Sea",IF($T15&lt;=$B$8,"Air — Expedite","Air — Still At Risk")))</f>
+      <c r="W15" s="23" t="str">
+        <f aca="false">IF($O15=0,"No Order Needed",IF($U15&lt;=$B$8,"Sea",IF($V15&lt;=$B$8,"Air — Expedite","Air — Still At Risk")))</f>
         <v>Air — Expedite</v>
       </c>
-      <c r="V15" s="17" t="n">
-        <f aca="false">IF($O15=0,"N/A",$B$4-IF($U15="Sea",$S15,$T15)*7)</f>
+      <c r="X15" s="17" t="n">
+        <f aca="false">IF($O15=0,"N/A",$B$4-IF($W15="Sea",$U15,$V15)*7)</f>
         <v>46252</v>
       </c>
-      <c r="W15" s="23" t="str">
-        <f aca="false">IF($O15=0,"No Restock Needed",IF($U15="Sea","On Track",IF($U15="Air — Expedite","Expedite Required","Critical — May Miss Launch")))</f>
+      <c r="Y15" s="23" t="str">
+        <f aca="false">IF($O15=0,"No Restock Needed",IF($W15="Sea","On Track",IF($W15="Air — Expedite","Expedite Required","Critical — May Miss Launch")))</f>
         <v>Expedite Required</v>
       </c>
     </row>
@@ -2288,28 +2347,36 @@
         <f aca="false">IFERROR(INDEX('Reference Data'!$C$31:$C$45,MATCH($D16&amp;"|UK",'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
         <v>5</v>
       </c>
-      <c r="R16" s="25" t="n">
+      <c r="R16" s="22" t="n">
+        <f aca="false">IFERROR($Q16*7,"N/A")</f>
+        <v>35</v>
+      </c>
+      <c r="S16" s="25" t="n">
         <f aca="false">IFERROR(INDEX('Reference Data'!$E$31:$E$45,MATCH($D16&amp;"|UK",'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
         <v>1</v>
       </c>
-      <c r="S16" s="25" t="n">
+      <c r="T16" s="22" t="n">
+        <f aca="false">IFERROR($S16*7,"N/A")</f>
+        <v>7</v>
+      </c>
+      <c r="U16" s="25" t="n">
         <f aca="false">$P16+$Q16</f>
         <v>8</v>
       </c>
-      <c r="T16" s="25" t="n">
-        <f aca="false">$P16+$R16</f>
+      <c r="V16" s="25" t="n">
+        <f aca="false">$P16+$S16</f>
         <v>4</v>
       </c>
-      <c r="U16" s="23" t="str">
-        <f aca="false">IF($O16=0,"No Order Needed",IF($S16&lt;=$B$8,"Sea",IF($T16&lt;=$B$8,"Air — Expedite","Air — Still At Risk")))</f>
+      <c r="W16" s="23" t="str">
+        <f aca="false">IF($O16=0,"No Order Needed",IF($U16&lt;=$B$8,"Sea",IF($V16&lt;=$B$8,"Air — Expedite","Air — Still At Risk")))</f>
         <v>Air — Still At Risk</v>
       </c>
-      <c r="V16" s="17" t="n">
-        <f aca="false">IF($O16=0,"N/A",$B$4-IF($U16="Sea",$S16,$T16)*7)</f>
+      <c r="X16" s="17" t="n">
+        <f aca="false">IF($O16=0,"N/A",$B$4-IF($W16="Sea",$U16,$V16)*7)</f>
         <v>46244</v>
       </c>
-      <c r="W16" s="23" t="str">
-        <f aca="false">IF($O16=0,"No Restock Needed",IF($U16="Sea","On Track",IF($U16="Air — Expedite","Expedite Required","Critical — May Miss Launch")))</f>
+      <c r="Y16" s="23" t="str">
+        <f aca="false">IF($O16=0,"No Restock Needed",IF($W16="Sea","On Track",IF($W16="Air — Expedite","Expedite Required","Critical — May Miss Launch")))</f>
         <v>Critical — May Miss Launch</v>
       </c>
     </row>
@@ -2381,28 +2448,36 @@
         <f aca="false">IFERROR(INDEX('Reference Data'!$C$31:$C$45,MATCH($D17&amp;"|UK",'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
         <v>4.5</v>
       </c>
-      <c r="R17" s="25" t="n">
+      <c r="R17" s="22" t="n">
+        <f aca="false">IFERROR($Q17*7,"N/A")</f>
+        <v>31.5</v>
+      </c>
+      <c r="S17" s="25" t="n">
         <f aca="false">IFERROR(INDEX('Reference Data'!$E$31:$E$45,MATCH($D17&amp;"|UK",'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
         <v>1</v>
       </c>
-      <c r="S17" s="25" t="n">
+      <c r="T17" s="22" t="n">
+        <f aca="false">IFERROR($S17*7,"N/A")</f>
+        <v>7</v>
+      </c>
+      <c r="U17" s="25" t="n">
         <f aca="false">$P17+$Q17</f>
         <v>6.5</v>
       </c>
-      <c r="T17" s="25" t="n">
-        <f aca="false">$P17+$R17</f>
+      <c r="V17" s="25" t="n">
+        <f aca="false">$P17+$S17</f>
         <v>3</v>
       </c>
-      <c r="U17" s="23" t="str">
-        <f aca="false">IF($O17=0,"No Order Needed",IF($S17&lt;=$B$8,"Sea",IF($T17&lt;=$B$8,"Air — Expedite","Air — Still At Risk")))</f>
+      <c r="W17" s="23" t="str">
+        <f aca="false">IF($O17=0,"No Order Needed",IF($U17&lt;=$B$8,"Sea",IF($V17&lt;=$B$8,"Air — Expedite","Air — Still At Risk")))</f>
         <v>Air — Expedite</v>
       </c>
-      <c r="V17" s="17" t="n">
-        <f aca="false">IF($O17=0,"N/A",$B$4-IF($U17="Sea",$S17,$T17)*7)</f>
+      <c r="X17" s="17" t="n">
+        <f aca="false">IF($O17=0,"N/A",$B$4-IF($W17="Sea",$U17,$V17)*7)</f>
         <v>46251</v>
       </c>
-      <c r="W17" s="23" t="str">
-        <f aca="false">IF($O17=0,"No Restock Needed",IF($U17="Sea","On Track",IF($U17="Air — Expedite","Expedite Required","Critical — May Miss Launch")))</f>
+      <c r="Y17" s="23" t="str">
+        <f aca="false">IF($O17=0,"No Restock Needed",IF($W17="Sea","On Track",IF($W17="Air — Expedite","Expedite Required","Critical — May Miss Launch")))</f>
         <v>Expedite Required</v>
       </c>
     </row>
@@ -2474,28 +2549,36 @@
         <f aca="false">IFERROR(INDEX('Reference Data'!$C$31:$C$45,MATCH($D18&amp;"|UK",'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
         <v>5</v>
       </c>
-      <c r="R18" s="25" t="n">
+      <c r="R18" s="22" t="n">
+        <f aca="false">IFERROR($Q18*7,"N/A")</f>
+        <v>35</v>
+      </c>
+      <c r="S18" s="25" t="n">
         <f aca="false">IFERROR(INDEX('Reference Data'!$E$31:$E$45,MATCH($D18&amp;"|UK",'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
         <v>1</v>
       </c>
-      <c r="S18" s="25" t="n">
+      <c r="T18" s="22" t="n">
+        <f aca="false">IFERROR($S18*7,"N/A")</f>
+        <v>7</v>
+      </c>
+      <c r="U18" s="25" t="n">
         <f aca="false">$P18+$Q18</f>
         <v>9</v>
       </c>
-      <c r="T18" s="25" t="n">
-        <f aca="false">$P18+$R18</f>
+      <c r="V18" s="25" t="n">
+        <f aca="false">$P18+$S18</f>
         <v>5</v>
       </c>
-      <c r="U18" s="23" t="str">
-        <f aca="false">IF($O18=0,"No Order Needed",IF($S18&lt;=$B$8,"Sea",IF($T18&lt;=$B$8,"Air — Expedite","Air — Still At Risk")))</f>
+      <c r="W18" s="23" t="str">
+        <f aca="false">IF($O18=0,"No Order Needed",IF($U18&lt;=$B$8,"Sea",IF($V18&lt;=$B$8,"Air — Expedite","Air — Still At Risk")))</f>
         <v>Air — Still At Risk</v>
       </c>
-      <c r="V18" s="17" t="n">
-        <f aca="false">IF($O18=0,"N/A",$B$4-IF($U18="Sea",$S18,$T18)*7)</f>
+      <c r="X18" s="17" t="n">
+        <f aca="false">IF($O18=0,"N/A",$B$4-IF($W18="Sea",$U18,$V18)*7)</f>
         <v>46237</v>
       </c>
-      <c r="W18" s="23" t="str">
-        <f aca="false">IF($O18=0,"No Restock Needed",IF($U18="Sea","On Track",IF($U18="Air — Expedite","Expedite Required","Critical — May Miss Launch")))</f>
+      <c r="Y18" s="23" t="str">
+        <f aca="false">IF($O18=0,"No Restock Needed",IF($W18="Sea","On Track",IF($W18="Air — Expedite","Expedite Required","Critical — May Miss Launch")))</f>
         <v>Critical — May Miss Launch</v>
       </c>
     </row>
@@ -2567,34 +2650,42 @@
         <f aca="false">IFERROR(INDEX('Reference Data'!$C$31:$C$45,MATCH($D19&amp;"|UK",'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
         <v>5</v>
       </c>
-      <c r="R19" s="25" t="n">
+      <c r="R19" s="22" t="n">
+        <f aca="false">IFERROR($Q19*7,"N/A")</f>
+        <v>35</v>
+      </c>
+      <c r="S19" s="25" t="n">
         <f aca="false">IFERROR(INDEX('Reference Data'!$E$31:$E$45,MATCH($D19&amp;"|UK",'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
         <v>1</v>
       </c>
-      <c r="S19" s="25" t="n">
+      <c r="T19" s="22" t="n">
+        <f aca="false">IFERROR($S19*7,"N/A")</f>
+        <v>7</v>
+      </c>
+      <c r="U19" s="25" t="n">
         <f aca="false">$P19+$Q19</f>
         <v>8</v>
       </c>
-      <c r="T19" s="25" t="n">
-        <f aca="false">$P19+$R19</f>
+      <c r="V19" s="25" t="n">
+        <f aca="false">$P19+$S19</f>
         <v>4</v>
       </c>
-      <c r="U19" s="23" t="str">
-        <f aca="false">IF($O19=0,"No Order Needed",IF($S19&lt;=$B$8,"Sea",IF($T19&lt;=$B$8,"Air — Expedite","Air — Still At Risk")))</f>
+      <c r="W19" s="23" t="str">
+        <f aca="false">IF($O19=0,"No Order Needed",IF($U19&lt;=$B$8,"Sea",IF($V19&lt;=$B$8,"Air — Expedite","Air — Still At Risk")))</f>
         <v>Air — Still At Risk</v>
       </c>
-      <c r="V19" s="17" t="n">
-        <f aca="false">IF($O19=0,"N/A",$B$4-IF($U19="Sea",$S19,$T19)*7)</f>
+      <c r="X19" s="17" t="n">
+        <f aca="false">IF($O19=0,"N/A",$B$4-IF($W19="Sea",$U19,$V19)*7)</f>
         <v>46244</v>
       </c>
-      <c r="W19" s="23" t="str">
-        <f aca="false">IF($O19=0,"No Restock Needed",IF($U19="Sea","On Track",IF($U19="Air — Expedite","Expedite Required","Critical — May Miss Launch")))</f>
+      <c r="Y19" s="23" t="str">
+        <f aca="false">IF($O19=0,"No Restock Needed",IF($W19="Sea","On Track",IF($W19="Air — Expedite","Expedite Required","Critical — May Miss Launch")))</f>
         <v>Critical — May Miss Launch</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="26" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B20" s="27"/>
       <c r="C20" s="27"/>
@@ -2624,6 +2715,8 @@
       <c r="U20" s="27"/>
       <c r="V20" s="27"/>
       <c r="W20" s="27"/>
+      <c r="X20" s="27"/>
+      <c r="Y20" s="27"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="10" t="s">
@@ -2632,7 +2725,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -2656,10 +2749,12 @@
       <c r="U23" s="11"/>
       <c r="V23" s="11"/>
       <c r="W23" s="11"/>
+      <c r="X23" s="11"/>
+      <c r="Y23" s="11"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -2683,10 +2778,12 @@
       <c r="U24" s="11"/>
       <c r="V24" s="11"/>
       <c r="W24" s="11"/>
+      <c r="X24" s="11"/>
+      <c r="Y24" s="11"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -2710,10 +2807,12 @@
       <c r="U25" s="11"/>
       <c r="V25" s="11"/>
       <c r="W25" s="11"/>
+      <c r="X25" s="11"/>
+      <c r="Y25" s="11"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -2737,10 +2836,12 @@
       <c r="U26" s="11"/>
       <c r="V26" s="11"/>
       <c r="W26" s="11"/>
+      <c r="X26" s="11"/>
+      <c r="Y26" s="11"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -2764,10 +2865,12 @@
       <c r="U27" s="11"/>
       <c r="V27" s="11"/>
       <c r="W27" s="11"/>
+      <c r="X27" s="11"/>
+      <c r="Y27" s="11"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -2791,10 +2894,12 @@
       <c r="U28" s="11"/>
       <c r="V28" s="11"/>
       <c r="W28" s="11"/>
+      <c r="X28" s="11"/>
+      <c r="Y28" s="11"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -2818,17 +2923,49 @@
       <c r="U29" s="11"/>
       <c r="V29" s="11"/>
       <c r="W29" s="11"/>
+      <c r="X29" s="11"/>
+      <c r="Y29" s="11"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="11"/>
+      <c r="J30" s="11"/>
+      <c r="K30" s="11"/>
+      <c r="L30" s="11"/>
+      <c r="M30" s="11"/>
+      <c r="N30" s="11"/>
+      <c r="O30" s="11"/>
+      <c r="P30" s="11"/>
+      <c r="Q30" s="11"/>
+      <c r="R30" s="11"/>
+      <c r="S30" s="11"/>
+      <c r="T30" s="11"/>
+      <c r="U30" s="11"/>
+      <c r="V30" s="11"/>
+      <c r="W30" s="11"/>
+      <c r="X30" s="11"/>
+      <c r="Y30" s="11"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A1:W1"/>
-    <mergeCell ref="A23:W23"/>
-    <mergeCell ref="A24:W24"/>
-    <mergeCell ref="A25:W25"/>
-    <mergeCell ref="A26:W26"/>
-    <mergeCell ref="A27:W27"/>
-    <mergeCell ref="A28:W28"/>
-    <mergeCell ref="A29:W29"/>
+  <mergeCells count="9">
+    <mergeCell ref="A1:Y1"/>
+    <mergeCell ref="A23:Y23"/>
+    <mergeCell ref="A24:Y24"/>
+    <mergeCell ref="A25:Y25"/>
+    <mergeCell ref="A26:Y26"/>
+    <mergeCell ref="A27:Y27"/>
+    <mergeCell ref="A28:Y28"/>
+    <mergeCell ref="A29:Y29"/>
+    <mergeCell ref="A30:Y30"/>
   </mergeCells>
   <conditionalFormatting sqref="I11:I19">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
@@ -2841,7 +2978,7 @@
       <formula>"Low Risk"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="W11:W19">
+  <conditionalFormatting sqref="Y11:Y19">
     <cfRule type="cellIs" priority="5" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>"On Track"</formula>
     </cfRule>
@@ -2892,7 +3029,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2908,7 +3045,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -2924,7 +3061,7 @@
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="19" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B5" s="19" t="s">
         <v>26</v>
@@ -2936,28 +3073,28 @@
         <v>25</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G5" s="19" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="H5" s="19" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="I5" s="19" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="J5" s="19" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K5" s="19" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="L5" s="19" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3267,7 +3404,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -3283,7 +3420,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -3299,7 +3436,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -3315,7 +3452,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -3395,7 +3532,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3415,7 +3552,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -3435,7 +3572,7 @@
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="19" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B5" s="19" t="s">
         <v>26</v>
@@ -3450,52 +3587,52 @@
         <v>25</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G5" s="19" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H5" s="19" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="I5" s="19" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="J5" s="19" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="K5" s="19" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="L5" s="19" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="M5" s="19" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="N5" s="19" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="O5" s="19" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="P5" s="19" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="28" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B6" s="28" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C6" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$B$22:$B$27,MATCH(B6,'Reference Data'!$A$22:$A$27,0)),"N/A")</f>
         <v>Shenzhen</v>
       </c>
       <c r="D6" s="28" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E6" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$B$10:$B$18,MATCH(D6,'Reference Data'!$A$10:$A$18,0)),"N/A")</f>
@@ -3505,16 +3642,16 @@
         <v>500</v>
       </c>
       <c r="G6" s="28" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="H6" s="30" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="I6" s="30" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="J6" s="28" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="K6" s="31" t="n">
         <v>5.5</v>
@@ -3542,17 +3679,17 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="28" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B7" s="28" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C7" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$B$22:$B$27,MATCH(B7,'Reference Data'!$A$22:$A$27,0)),"N/A")</f>
         <v>Shenzhen</v>
       </c>
       <c r="D7" s="28" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E7" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$B$10:$B$18,MATCH(D7,'Reference Data'!$A$10:$A$18,0)),"N/A")</f>
@@ -3562,16 +3699,16 @@
         <v>500</v>
       </c>
       <c r="G7" s="28" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H7" s="30" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="I7" s="30" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="J7" s="28" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K7" s="31" t="n">
         <v>4</v>
@@ -3599,17 +3736,17 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="28" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B8" s="28" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C8" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$B$22:$B$27,MATCH(B8,'Reference Data'!$A$22:$A$27,0)),"N/A")</f>
         <v>Jakarta</v>
       </c>
       <c r="D8" s="28" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E8" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$B$10:$B$18,MATCH(D8,'Reference Data'!$A$10:$A$18,0)),"N/A")</f>
@@ -3619,19 +3756,19 @@
         <v>300</v>
       </c>
       <c r="G8" s="28" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="H8" s="30" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="I8" s="30" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="J8" s="28" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="K8" s="30" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="L8" s="32" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$C$31:$C$45,MATCH($C8&amp;"|"&amp;$H8,'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
@@ -3656,17 +3793,17 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="28" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B9" s="28" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C9" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$B$22:$B$27,MATCH(B9,'Reference Data'!$A$22:$A$27,0)),"N/A")</f>
         <v>Taipei</v>
       </c>
       <c r="D9" s="28" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E9" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$B$10:$B$18,MATCH(D9,'Reference Data'!$A$10:$A$18,0)),"N/A")</f>
@@ -3676,19 +3813,19 @@
         <v>1000</v>
       </c>
       <c r="G9" s="28" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="H9" s="30" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="I9" s="30" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="J9" s="28" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="K9" s="30" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="L9" s="32" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$C$31:$C$45,MATCH($C9&amp;"|"&amp;$H9,'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
@@ -3713,17 +3850,17 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="28" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B10" s="28" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C10" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$B$22:$B$27,MATCH(B10,'Reference Data'!$A$22:$A$27,0)),"N/A")</f>
         <v>Chiang Mai</v>
       </c>
       <c r="D10" s="28" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E10" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$B$10:$B$18,MATCH(D10,'Reference Data'!$A$10:$A$18,0)),"N/A")</f>
@@ -3733,19 +3870,19 @@
         <v>200</v>
       </c>
       <c r="G10" s="28" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="H10" s="30" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="I10" s="30" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="J10" s="28" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="K10" s="30" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="L10" s="32" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$C$31:$C$45,MATCH($C10&amp;"|"&amp;$H10,'Reference Data'!$F$31:$F$45,0)),"N/A")</f>
@@ -3770,17 +3907,17 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="28" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B11" s="28" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C11" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$B$22:$B$27,MATCH(B11,'Reference Data'!$A$22:$A$27,0)),"N/A")</f>
         <v>Ho Chi Minh City</v>
       </c>
       <c r="D11" s="28" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E11" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$B$10:$B$18,MATCH(D11,'Reference Data'!$A$10:$A$18,0)),"N/A")</f>
@@ -3790,16 +3927,16 @@
         <v>500</v>
       </c>
       <c r="G11" s="28" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H11" s="30" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="I11" s="30" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="J11" s="28" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="K11" s="31" t="n">
         <v>6</v>
@@ -3827,7 +3964,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="26" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B12" s="27"/>
       <c r="C12" s="27"/>
@@ -3855,7 +3992,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -3875,7 +4012,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -3895,7 +4032,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -3915,7 +4052,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -3990,7 +4127,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4009,12 +4146,12 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B4" s="15" t="n">
         <v>4</v>
@@ -4022,13 +4159,13 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B5" s="15" t="n">
         <v>8</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4039,40 +4176,40 @@
         <v>25</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="G7" s="19" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="H7" s="19" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="I7" s="19" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="J7" s="19" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="K7" s="19" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="L7" s="19" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="M7" s="19" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="N7" s="19" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="O7" s="19" t="s">
         <v>30</v>
@@ -4080,7 +4217,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="28" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B8" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$B$10:$B$18,MATCH($A8,'Reference Data'!$A$10:$A$18,0)),"N/A")</f>
@@ -4137,7 +4274,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="28" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B9" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$B$10:$B$18,MATCH($A9,'Reference Data'!$A$10:$A$18,0)),"N/A")</f>
@@ -4194,7 +4331,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="28" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B10" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$B$10:$B$18,MATCH($A10,'Reference Data'!$A$10:$A$18,0)),"N/A")</f>
@@ -4251,7 +4388,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="28" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B11" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$B$10:$B$18,MATCH($A11,'Reference Data'!$A$10:$A$18,0)),"N/A")</f>
@@ -4308,7 +4445,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="28" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B12" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$B$10:$B$18,MATCH($A12,'Reference Data'!$A$10:$A$18,0)),"N/A")</f>
@@ -4365,7 +4502,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="28" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B13" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$B$10:$B$18,MATCH($A13,'Reference Data'!$A$10:$A$18,0)),"N/A")</f>
@@ -4422,7 +4559,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="28" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B14" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$B$10:$B$18,MATCH($A14,'Reference Data'!$A$10:$A$18,0)),"N/A")</f>
@@ -4479,7 +4616,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="28" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B15" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$B$10:$B$18,MATCH($A15,'Reference Data'!$A$10:$A$18,0)),"N/A")</f>
@@ -4536,7 +4673,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="28" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B16" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Reference Data'!$B$10:$B$18,MATCH($A16,'Reference Data'!$A$10:$A$18,0)),"N/A")</f>
@@ -4593,7 +4730,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="26" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B17" s="27"/>
       <c r="C17" s="27"/>
@@ -4635,7 +4772,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -4654,7 +4791,7 @@
     </row>
     <row r="21" customFormat="false" ht="22.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -4673,7 +4810,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -4692,7 +4829,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -4769,7 +4906,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4781,7 +4918,7 @@
     </row>
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -4793,51 +4930,51 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="19" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="28" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B5" s="28" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="28" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B6" s="28" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C6" s="28" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="28" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B7" s="28" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C7" s="28" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -4855,141 +4992,141 @@
         <v>25</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="28" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B10" s="28" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C10" s="28" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D10" s="28" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="28" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B11" s="28" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C11" s="28" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D11" s="28" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="28" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B12" s="28" t="s">
+        <v>159</v>
+      </c>
+      <c r="C12" s="28" t="s">
         <v>156</v>
       </c>
-      <c r="C12" s="28" t="s">
-        <v>153</v>
-      </c>
       <c r="D12" s="28" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="28" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B13" s="28" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C13" s="28" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D13" s="28" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="28" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B14" s="28" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C14" s="28" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D14" s="28" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="28" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B15" s="28" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C15" s="28" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D15" s="28" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="28" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B16" s="28" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C16" s="28" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D16" s="28" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="28" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B17" s="28" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C17" s="28" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D17" s="28" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="28" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B18" s="28" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C18" s="28" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D18" s="28" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -5004,42 +5141,42 @@
         <v>26</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="D21" s="19" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="E21" s="19" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="F21" s="19" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="G21" s="19" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="H21" s="19" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="28" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B22" s="28" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C22" s="28" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D22" s="28" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E22" s="28" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="F22" s="29" t="n">
         <v>500</v>
@@ -5048,24 +5185,24 @@
         <v>3</v>
       </c>
       <c r="H22" s="28" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="28" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B23" s="28" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C23" s="28" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D23" s="28" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E23" s="28" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="F23" s="29" t="n">
         <v>400</v>
@@ -5074,24 +5211,24 @@
         <v>2.5</v>
       </c>
       <c r="H23" s="28" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="28" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B24" s="28" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C24" s="28" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D24" s="28" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="E24" s="28" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="F24" s="29" t="n">
         <v>300</v>
@@ -5100,24 +5237,24 @@
         <v>3</v>
       </c>
       <c r="H24" s="28" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="28" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B25" s="28" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C25" s="28" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D25" s="28" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E25" s="28" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F25" s="29" t="n">
         <v>1000</v>
@@ -5126,24 +5263,24 @@
         <v>2</v>
       </c>
       <c r="H25" s="28" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="28" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B26" s="28" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C26" s="28" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D26" s="28" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E26" s="28" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="F26" s="29" t="n">
         <v>200</v>
@@ -5152,24 +5289,24 @@
         <v>2</v>
       </c>
       <c r="H26" s="28" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="28" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B27" s="28" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C27" s="28" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="D27" s="28" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E27" s="28" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="F27" s="29" t="n">
         <v>500</v>
@@ -5178,12 +5315,12 @@
         <v>4</v>
       </c>
       <c r="H27" s="28" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
@@ -5195,30 +5332,30 @@
     </row>
     <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="19" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="D30" s="19" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="E30" s="19" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="F30" s="19" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="28" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B31" s="28" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C31" s="35" t="n">
         <v>3</v>
@@ -5237,10 +5374,10 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="28" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B32" s="28" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C32" s="35" t="n">
         <v>5</v>
@@ -5259,10 +5396,10 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="28" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B33" s="28" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C33" s="35" t="n">
         <v>0.285714285714286</v>
@@ -5281,10 +5418,10 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="28" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B34" s="28" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C34" s="35" t="n">
         <v>4.5</v>
@@ -5303,10 +5440,10 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="28" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B35" s="28" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C35" s="35" t="n">
         <v>4.5</v>
@@ -5325,10 +5462,10 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="28" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B36" s="28" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C36" s="35" t="n">
         <v>4</v>
@@ -5347,10 +5484,10 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="28" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B37" s="28" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C37" s="35" t="n">
         <v>4</v>
@@ -5369,10 +5506,10 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="28" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B38" s="28" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C38" s="35" t="n">
         <v>5</v>
@@ -5391,10 +5528,10 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="28" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B39" s="28" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C39" s="35" t="n">
         <v>4</v>
@@ -5413,10 +5550,10 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="28" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B40" s="28" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C40" s="35" t="n">
         <v>3</v>
@@ -5435,10 +5572,10 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="28" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B41" s="28" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C41" s="35" t="n">
         <v>5</v>
@@ -5457,10 +5594,10 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="28" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B42" s="28" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C42" s="35" t="n">
         <v>0.285714285714286</v>
@@ -5479,10 +5616,10 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="28" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B43" s="28" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C43" s="35" t="n">
         <v>3.5</v>
@@ -5501,10 +5638,10 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="28" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B44" s="28" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C44" s="35" t="n">
         <v>5</v>
@@ -5523,10 +5660,10 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="28" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B45" s="28" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C45" s="35" t="n">
         <v>3</v>
@@ -5550,7 +5687,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="11" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B48" s="11"/>
       <c r="C48" s="11"/>
@@ -5562,7 +5699,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="11" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B49" s="11"/>
       <c r="C49" s="11"/>
@@ -5574,7 +5711,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="11" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B50" s="11"/>
       <c r="C50" s="11"/>
@@ -5586,7 +5723,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="11" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B51" s="11"/>
       <c r="C51" s="11"/>
@@ -5598,7 +5735,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="11" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B52" s="11"/>
       <c r="C52" s="11"/>
